--- a/Template/gt/bao_ve_template.xlsx
+++ b/Template/gt/bao_ve_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Scan2Excel AI\Template\gt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C750FAC4-041B-47D7-974A-72E4539B4A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D0862F-6F4A-4741-881F-5A514993EB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bang TH nop" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
   <si>
     <t>TT</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Ngày 15  tháng 05 năm 2026</t>
+  </si>
+  <si>
+    <t>Ca ba lễ tết</t>
   </si>
 </sst>
 </file>
@@ -686,7 +689,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -943,122 +946,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="11" fillId="3" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1071,6 +962,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1100,8 +994,120 @@
     <xf numFmtId="166" fontId="9" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -24967,11 +24973,11 @@
       </c>
     </row>
     <row r="2" spans="1:19" s="3" customFormat="1" ht="37.5" customHeight="1">
-      <c r="A2" s="132" t="s">
+      <c r="A2" s="170" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
+      <c r="B2" s="170"/>
+      <c r="C2" s="170"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -24990,9 +24996,9 @@
       <c r="S2" s="2"/>
     </row>
     <row r="3" spans="1:19" ht="18" customHeight="1">
-      <c r="A3" s="133"/>
-      <c r="B3" s="133"/>
-      <c r="C3" s="133"/>
+      <c r="A3" s="171"/>
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
     </row>
     <row r="4" spans="1:19" ht="18" customHeight="1">
       <c r="D4" s="4"/>
@@ -25007,84 +25013,84 @@
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:19" ht="29.25" customHeight="1">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="134" t="s">
+      <c r="B5" s="172" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="134" t="s">
+      <c r="C5" s="172" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="127" t="s">
+      <c r="D5" s="174" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="130" t="s">
+      <c r="E5" s="176" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="131" t="s">
+      <c r="F5" s="177" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="131" t="s">
+      <c r="G5" s="177" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="131" t="s">
+      <c r="H5" s="177" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="131" t="s">
+      <c r="I5" s="177" t="s">
         <v>6</v>
       </c>
-      <c r="J5" s="131" t="s">
+      <c r="J5" s="177" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="131" t="s">
+      <c r="K5" s="177" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="131" t="s">
+      <c r="L5" s="177" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="127" t="s">
+      <c r="M5" s="174" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="127" t="s">
+      <c r="N5" s="174" t="s">
         <v>11</v>
       </c>
-      <c r="O5" s="128" t="s">
+      <c r="O5" s="179" t="s">
         <v>17</v>
       </c>
-      <c r="P5" s="126" t="s">
+      <c r="P5" s="178" t="s">
         <v>37</v>
       </c>
-      <c r="Q5" s="126" t="s">
+      <c r="Q5" s="178" t="s">
         <v>40</v>
       </c>
-      <c r="R5" s="126" t="s">
+      <c r="R5" s="178" t="s">
         <v>28</v>
       </c>
-      <c r="S5" s="126" t="s">
+      <c r="S5" s="178" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="18" customHeight="1">
-      <c r="A6" s="135"/>
-      <c r="B6" s="135"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="127"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="131"/>
-      <c r="G6" s="131"/>
-      <c r="H6" s="131"/>
-      <c r="I6" s="131"/>
-      <c r="J6" s="131"/>
-      <c r="K6" s="131"/>
-      <c r="L6" s="131"/>
-      <c r="M6" s="127"/>
-      <c r="N6" s="127"/>
-      <c r="O6" s="128"/>
-      <c r="P6" s="126"/>
-      <c r="Q6" s="126"/>
-      <c r="R6" s="126"/>
-      <c r="S6" s="126"/>
+      <c r="A6" s="173"/>
+      <c r="B6" s="173"/>
+      <c r="C6" s="173"/>
+      <c r="D6" s="174"/>
+      <c r="E6" s="176"/>
+      <c r="F6" s="177"/>
+      <c r="G6" s="177"/>
+      <c r="H6" s="177"/>
+      <c r="I6" s="177"/>
+      <c r="J6" s="177"/>
+      <c r="K6" s="177"/>
+      <c r="L6" s="177"/>
+      <c r="M6" s="174"/>
+      <c r="N6" s="174"/>
+      <c r="O6" s="179"/>
+      <c r="P6" s="178"/>
+      <c r="Q6" s="178"/>
+      <c r="R6" s="178"/>
+      <c r="S6" s="178"/>
     </row>
     <row r="7" spans="1:19" ht="18" hidden="1" customHeight="1">
       <c r="A7" s="26"/>
@@ -25102,10 +25108,10 @@
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
       <c r="O7" s="24"/>
-      <c r="P7" s="126"/>
-      <c r="Q7" s="126"/>
-      <c r="R7" s="126"/>
-      <c r="S7" s="126"/>
+      <c r="P7" s="178"/>
+      <c r="Q7" s="178"/>
+      <c r="R7" s="178"/>
+      <c r="S7" s="178"/>
     </row>
     <row r="8" spans="1:19" ht="18" customHeight="1">
       <c r="A8" s="10"/>
@@ -26910,10 +26916,10 @@
       <c r="L94" s="9"/>
     </row>
     <row r="95" spans="1:19" ht="18" customHeight="1">
-      <c r="A95" s="129" t="s">
+      <c r="A95" s="175" t="s">
         <v>15</v>
       </c>
-      <c r="B95" s="129"/>
+      <c r="B95" s="175"/>
       <c r="D95" s="8"/>
     </row>
     <row r="96" spans="1:19" ht="18" customHeight="1">
@@ -27844,11 +27850,12 @@
     <row r="296" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="S5:S7"/>
+    <mergeCell ref="Q5:Q7"/>
+    <mergeCell ref="R5:R7"/>
+    <mergeCell ref="P5:P7"/>
+    <mergeCell ref="N5:N6"/>
+    <mergeCell ref="O5:O6"/>
     <mergeCell ref="M5:M6"/>
     <mergeCell ref="A95:B95"/>
     <mergeCell ref="D5:D6"/>
@@ -27860,12 +27867,11 @@
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="K5:K6"/>
     <mergeCell ref="L5:L6"/>
-    <mergeCell ref="S5:S7"/>
-    <mergeCell ref="Q5:Q7"/>
-    <mergeCell ref="R5:R7"/>
-    <mergeCell ref="P5:P7"/>
-    <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -27875,7 +27881,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:XFA123"/>
+  <dimension ref="A1:XFB123"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="45" customWidth="1"/>
@@ -27888,1519 +27894,1519 @@
     <col min="9" max="9" width="5.5703125" style="45" customWidth="1"/>
     <col min="10" max="10" width="6.7109375" style="45" customWidth="1"/>
     <col min="11" max="11" width="5.5703125" style="45" customWidth="1"/>
-    <col min="12" max="12" width="8" style="45" customWidth="1"/>
-    <col min="13" max="13" width="7.140625" style="45" customWidth="1"/>
-    <col min="14" max="14" width="7.42578125" style="45" customWidth="1"/>
-    <col min="15" max="15" width="6.140625" style="45" customWidth="1"/>
-    <col min="16" max="16" width="7" style="50" customWidth="1"/>
-    <col min="17" max="17" width="8.140625" style="45" customWidth="1"/>
-    <col min="18" max="19" width="8.5703125" style="54" customWidth="1"/>
-    <col min="20" max="20" width="8.42578125" style="54" customWidth="1"/>
-    <col min="21" max="21" width="7.42578125" style="54" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" style="54" customWidth="1"/>
-    <col min="23" max="23" width="9.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.140625" style="57" customWidth="1"/>
-    <col min="25" max="25" width="11.140625" style="45" customWidth="1"/>
-    <col min="26" max="27" width="11.140625" style="45" bestFit="1" customWidth="1"/>
-    <col min="28" max="237" width="9.140625" style="45"/>
-    <col min="238" max="238" width="4.140625" style="45" customWidth="1"/>
-    <col min="239" max="239" width="15.5703125" style="45" customWidth="1"/>
-    <col min="240" max="240" width="7.28515625" style="45" customWidth="1"/>
-    <col min="241" max="241" width="4.85546875" style="45" customWidth="1"/>
-    <col min="242" max="242" width="4.42578125" style="45" customWidth="1"/>
-    <col min="243" max="248" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="249" max="249" width="9" style="45" customWidth="1"/>
-    <col min="250" max="250" width="4.85546875" style="45" customWidth="1"/>
-    <col min="251" max="252" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="253" max="254" width="4.85546875" style="45" customWidth="1"/>
-    <col min="255" max="255" width="6.140625" style="45" customWidth="1"/>
-    <col min="256" max="256" width="6.42578125" style="45" customWidth="1"/>
-    <col min="257" max="257" width="4.85546875" style="45" customWidth="1"/>
-    <col min="258" max="258" width="7.5703125" style="45" customWidth="1"/>
-    <col min="259" max="259" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="260" max="260" width="7.140625" style="45" customWidth="1"/>
-    <col min="261" max="261" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="262" max="262" width="6.85546875" style="45" customWidth="1"/>
-    <col min="263" max="263" width="9.28515625" style="45" customWidth="1"/>
-    <col min="264" max="264" width="5.85546875" style="45" customWidth="1"/>
-    <col min="265" max="265" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="266" max="266" width="10" style="45" customWidth="1"/>
-    <col min="267" max="272" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="273" max="493" width="9.140625" style="45"/>
-    <col min="494" max="494" width="4.140625" style="45" customWidth="1"/>
-    <col min="495" max="495" width="15.5703125" style="45" customWidth="1"/>
-    <col min="496" max="496" width="7.28515625" style="45" customWidth="1"/>
-    <col min="497" max="497" width="4.85546875" style="45" customWidth="1"/>
-    <col min="498" max="498" width="4.42578125" style="45" customWidth="1"/>
-    <col min="499" max="504" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="505" max="505" width="9" style="45" customWidth="1"/>
-    <col min="506" max="506" width="4.85546875" style="45" customWidth="1"/>
-    <col min="507" max="508" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="509" max="510" width="4.85546875" style="45" customWidth="1"/>
-    <col min="511" max="511" width="6.140625" style="45" customWidth="1"/>
-    <col min="512" max="512" width="6.42578125" style="45" customWidth="1"/>
-    <col min="513" max="513" width="4.85546875" style="45" customWidth="1"/>
-    <col min="514" max="514" width="7.5703125" style="45" customWidth="1"/>
-    <col min="515" max="515" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="516" max="516" width="7.140625" style="45" customWidth="1"/>
-    <col min="517" max="517" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="518" max="518" width="6.85546875" style="45" customWidth="1"/>
-    <col min="519" max="519" width="9.28515625" style="45" customWidth="1"/>
-    <col min="520" max="520" width="5.85546875" style="45" customWidth="1"/>
-    <col min="521" max="521" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="522" max="522" width="10" style="45" customWidth="1"/>
-    <col min="523" max="528" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="529" max="749" width="9.140625" style="45"/>
-    <col min="750" max="750" width="4.140625" style="45" customWidth="1"/>
-    <col min="751" max="751" width="15.5703125" style="45" customWidth="1"/>
-    <col min="752" max="752" width="7.28515625" style="45" customWidth="1"/>
-    <col min="753" max="753" width="4.85546875" style="45" customWidth="1"/>
-    <col min="754" max="754" width="4.42578125" style="45" customWidth="1"/>
-    <col min="755" max="760" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="761" max="761" width="9" style="45" customWidth="1"/>
-    <col min="762" max="762" width="4.85546875" style="45" customWidth="1"/>
-    <col min="763" max="764" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="765" max="766" width="4.85546875" style="45" customWidth="1"/>
-    <col min="767" max="767" width="6.140625" style="45" customWidth="1"/>
-    <col min="768" max="768" width="6.42578125" style="45" customWidth="1"/>
-    <col min="769" max="769" width="4.85546875" style="45" customWidth="1"/>
-    <col min="770" max="770" width="7.5703125" style="45" customWidth="1"/>
-    <col min="771" max="771" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="772" max="772" width="7.140625" style="45" customWidth="1"/>
-    <col min="773" max="773" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="774" max="774" width="6.85546875" style="45" customWidth="1"/>
-    <col min="775" max="775" width="9.28515625" style="45" customWidth="1"/>
-    <col min="776" max="776" width="5.85546875" style="45" customWidth="1"/>
-    <col min="777" max="777" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="778" max="778" width="10" style="45" customWidth="1"/>
-    <col min="779" max="784" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="785" max="1005" width="9.140625" style="45"/>
-    <col min="1006" max="1006" width="4.140625" style="45" customWidth="1"/>
-    <col min="1007" max="1007" width="15.5703125" style="45" customWidth="1"/>
-    <col min="1008" max="1008" width="7.28515625" style="45" customWidth="1"/>
-    <col min="1009" max="1009" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1010" max="1010" width="4.42578125" style="45" customWidth="1"/>
-    <col min="1011" max="1016" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1017" max="1017" width="9" style="45" customWidth="1"/>
-    <col min="1018" max="1018" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1019" max="1020" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1021" max="1022" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1023" max="1023" width="6.140625" style="45" customWidth="1"/>
-    <col min="1024" max="1024" width="6.42578125" style="45" customWidth="1"/>
-    <col min="1025" max="1025" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1026" max="1026" width="7.5703125" style="45" customWidth="1"/>
-    <col min="1027" max="1027" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1028" max="1028" width="7.140625" style="45" customWidth="1"/>
-    <col min="1029" max="1029" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1030" max="1030" width="6.85546875" style="45" customWidth="1"/>
-    <col min="1031" max="1031" width="9.28515625" style="45" customWidth="1"/>
-    <col min="1032" max="1032" width="5.85546875" style="45" customWidth="1"/>
-    <col min="1033" max="1033" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1034" max="1034" width="10" style="45" customWidth="1"/>
-    <col min="1035" max="1040" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1041" max="1261" width="9.140625" style="45"/>
-    <col min="1262" max="1262" width="4.140625" style="45" customWidth="1"/>
-    <col min="1263" max="1263" width="15.5703125" style="45" customWidth="1"/>
-    <col min="1264" max="1264" width="7.28515625" style="45" customWidth="1"/>
-    <col min="1265" max="1265" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1266" max="1266" width="4.42578125" style="45" customWidth="1"/>
-    <col min="1267" max="1272" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1273" max="1273" width="9" style="45" customWidth="1"/>
-    <col min="1274" max="1274" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1275" max="1276" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1277" max="1278" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1279" max="1279" width="6.140625" style="45" customWidth="1"/>
-    <col min="1280" max="1280" width="6.42578125" style="45" customWidth="1"/>
-    <col min="1281" max="1281" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1282" max="1282" width="7.5703125" style="45" customWidth="1"/>
-    <col min="1283" max="1283" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1284" max="1284" width="7.140625" style="45" customWidth="1"/>
-    <col min="1285" max="1285" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1286" max="1286" width="6.85546875" style="45" customWidth="1"/>
-    <col min="1287" max="1287" width="9.28515625" style="45" customWidth="1"/>
-    <col min="1288" max="1288" width="5.85546875" style="45" customWidth="1"/>
-    <col min="1289" max="1289" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1290" max="1290" width="10" style="45" customWidth="1"/>
-    <col min="1291" max="1296" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1297" max="1517" width="9.140625" style="45"/>
-    <col min="1518" max="1518" width="4.140625" style="45" customWidth="1"/>
-    <col min="1519" max="1519" width="15.5703125" style="45" customWidth="1"/>
-    <col min="1520" max="1520" width="7.28515625" style="45" customWidth="1"/>
-    <col min="1521" max="1521" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1522" max="1522" width="4.42578125" style="45" customWidth="1"/>
-    <col min="1523" max="1528" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1529" max="1529" width="9" style="45" customWidth="1"/>
-    <col min="1530" max="1530" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1531" max="1532" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1533" max="1534" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1535" max="1535" width="6.140625" style="45" customWidth="1"/>
-    <col min="1536" max="1536" width="6.42578125" style="45" customWidth="1"/>
-    <col min="1537" max="1537" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1538" max="1538" width="7.5703125" style="45" customWidth="1"/>
-    <col min="1539" max="1539" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1540" max="1540" width="7.140625" style="45" customWidth="1"/>
-    <col min="1541" max="1541" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1542" max="1542" width="6.85546875" style="45" customWidth="1"/>
-    <col min="1543" max="1543" width="9.28515625" style="45" customWidth="1"/>
-    <col min="1544" max="1544" width="5.85546875" style="45" customWidth="1"/>
-    <col min="1545" max="1545" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1546" max="1546" width="10" style="45" customWidth="1"/>
-    <col min="1547" max="1552" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1553" max="1773" width="9.140625" style="45"/>
-    <col min="1774" max="1774" width="4.140625" style="45" customWidth="1"/>
-    <col min="1775" max="1775" width="15.5703125" style="45" customWidth="1"/>
-    <col min="1776" max="1776" width="7.28515625" style="45" customWidth="1"/>
-    <col min="1777" max="1777" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1778" max="1778" width="4.42578125" style="45" customWidth="1"/>
-    <col min="1779" max="1784" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1785" max="1785" width="9" style="45" customWidth="1"/>
-    <col min="1786" max="1786" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1787" max="1788" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1789" max="1790" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1791" max="1791" width="6.140625" style="45" customWidth="1"/>
-    <col min="1792" max="1792" width="6.42578125" style="45" customWidth="1"/>
-    <col min="1793" max="1793" width="4.85546875" style="45" customWidth="1"/>
-    <col min="1794" max="1794" width="7.5703125" style="45" customWidth="1"/>
-    <col min="1795" max="1795" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1796" max="1796" width="7.140625" style="45" customWidth="1"/>
-    <col min="1797" max="1797" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1798" max="1798" width="6.85546875" style="45" customWidth="1"/>
-    <col min="1799" max="1799" width="9.28515625" style="45" customWidth="1"/>
-    <col min="1800" max="1800" width="5.85546875" style="45" customWidth="1"/>
-    <col min="1801" max="1801" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1802" max="1802" width="10" style="45" customWidth="1"/>
-    <col min="1803" max="1808" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="1809" max="2029" width="9.140625" style="45"/>
-    <col min="2030" max="2030" width="4.140625" style="45" customWidth="1"/>
-    <col min="2031" max="2031" width="15.5703125" style="45" customWidth="1"/>
-    <col min="2032" max="2032" width="7.28515625" style="45" customWidth="1"/>
-    <col min="2033" max="2033" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2034" max="2034" width="4.42578125" style="45" customWidth="1"/>
-    <col min="2035" max="2040" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2041" max="2041" width="9" style="45" customWidth="1"/>
-    <col min="2042" max="2042" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2043" max="2044" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2045" max="2046" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2047" max="2047" width="6.140625" style="45" customWidth="1"/>
-    <col min="2048" max="2048" width="6.42578125" style="45" customWidth="1"/>
-    <col min="2049" max="2049" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2050" max="2050" width="7.5703125" style="45" customWidth="1"/>
-    <col min="2051" max="2051" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2052" max="2052" width="7.140625" style="45" customWidth="1"/>
-    <col min="2053" max="2053" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2054" max="2054" width="6.85546875" style="45" customWidth="1"/>
-    <col min="2055" max="2055" width="9.28515625" style="45" customWidth="1"/>
-    <col min="2056" max="2056" width="5.85546875" style="45" customWidth="1"/>
-    <col min="2057" max="2057" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2058" max="2058" width="10" style="45" customWidth="1"/>
-    <col min="2059" max="2064" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2065" max="2285" width="9.140625" style="45"/>
-    <col min="2286" max="2286" width="4.140625" style="45" customWidth="1"/>
-    <col min="2287" max="2287" width="15.5703125" style="45" customWidth="1"/>
-    <col min="2288" max="2288" width="7.28515625" style="45" customWidth="1"/>
-    <col min="2289" max="2289" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2290" max="2290" width="4.42578125" style="45" customWidth="1"/>
-    <col min="2291" max="2296" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2297" max="2297" width="9" style="45" customWidth="1"/>
-    <col min="2298" max="2298" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2299" max="2300" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2301" max="2302" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2303" max="2303" width="6.140625" style="45" customWidth="1"/>
-    <col min="2304" max="2304" width="6.42578125" style="45" customWidth="1"/>
-    <col min="2305" max="2305" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2306" max="2306" width="7.5703125" style="45" customWidth="1"/>
-    <col min="2307" max="2307" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2308" max="2308" width="7.140625" style="45" customWidth="1"/>
-    <col min="2309" max="2309" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2310" max="2310" width="6.85546875" style="45" customWidth="1"/>
-    <col min="2311" max="2311" width="9.28515625" style="45" customWidth="1"/>
-    <col min="2312" max="2312" width="5.85546875" style="45" customWidth="1"/>
-    <col min="2313" max="2313" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2314" max="2314" width="10" style="45" customWidth="1"/>
-    <col min="2315" max="2320" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2321" max="2541" width="9.140625" style="45"/>
-    <col min="2542" max="2542" width="4.140625" style="45" customWidth="1"/>
-    <col min="2543" max="2543" width="15.5703125" style="45" customWidth="1"/>
-    <col min="2544" max="2544" width="7.28515625" style="45" customWidth="1"/>
-    <col min="2545" max="2545" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2546" max="2546" width="4.42578125" style="45" customWidth="1"/>
-    <col min="2547" max="2552" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2553" max="2553" width="9" style="45" customWidth="1"/>
-    <col min="2554" max="2554" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2555" max="2556" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2557" max="2558" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2559" max="2559" width="6.140625" style="45" customWidth="1"/>
-    <col min="2560" max="2560" width="6.42578125" style="45" customWidth="1"/>
-    <col min="2561" max="2561" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2562" max="2562" width="7.5703125" style="45" customWidth="1"/>
-    <col min="2563" max="2563" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2564" max="2564" width="7.140625" style="45" customWidth="1"/>
-    <col min="2565" max="2565" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2566" max="2566" width="6.85546875" style="45" customWidth="1"/>
-    <col min="2567" max="2567" width="9.28515625" style="45" customWidth="1"/>
-    <col min="2568" max="2568" width="5.85546875" style="45" customWidth="1"/>
-    <col min="2569" max="2569" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2570" max="2570" width="10" style="45" customWidth="1"/>
-    <col min="2571" max="2576" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2577" max="2797" width="9.140625" style="45"/>
-    <col min="2798" max="2798" width="4.140625" style="45" customWidth="1"/>
-    <col min="2799" max="2799" width="15.5703125" style="45" customWidth="1"/>
-    <col min="2800" max="2800" width="7.28515625" style="45" customWidth="1"/>
-    <col min="2801" max="2801" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2802" max="2802" width="4.42578125" style="45" customWidth="1"/>
-    <col min="2803" max="2808" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2809" max="2809" width="9" style="45" customWidth="1"/>
-    <col min="2810" max="2810" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2811" max="2812" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2813" max="2814" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2815" max="2815" width="6.140625" style="45" customWidth="1"/>
-    <col min="2816" max="2816" width="6.42578125" style="45" customWidth="1"/>
-    <col min="2817" max="2817" width="4.85546875" style="45" customWidth="1"/>
-    <col min="2818" max="2818" width="7.5703125" style="45" customWidth="1"/>
-    <col min="2819" max="2819" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2820" max="2820" width="7.140625" style="45" customWidth="1"/>
-    <col min="2821" max="2821" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2822" max="2822" width="6.85546875" style="45" customWidth="1"/>
-    <col min="2823" max="2823" width="9.28515625" style="45" customWidth="1"/>
-    <col min="2824" max="2824" width="5.85546875" style="45" customWidth="1"/>
-    <col min="2825" max="2825" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2826" max="2826" width="10" style="45" customWidth="1"/>
-    <col min="2827" max="2832" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="2833" max="3053" width="9.140625" style="45"/>
-    <col min="3054" max="3054" width="4.140625" style="45" customWidth="1"/>
-    <col min="3055" max="3055" width="15.5703125" style="45" customWidth="1"/>
-    <col min="3056" max="3056" width="7.28515625" style="45" customWidth="1"/>
-    <col min="3057" max="3057" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3058" max="3058" width="4.42578125" style="45" customWidth="1"/>
-    <col min="3059" max="3064" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3065" max="3065" width="9" style="45" customWidth="1"/>
-    <col min="3066" max="3066" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3067" max="3068" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3069" max="3070" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3071" max="3071" width="6.140625" style="45" customWidth="1"/>
-    <col min="3072" max="3072" width="6.42578125" style="45" customWidth="1"/>
-    <col min="3073" max="3073" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3074" max="3074" width="7.5703125" style="45" customWidth="1"/>
-    <col min="3075" max="3075" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3076" max="3076" width="7.140625" style="45" customWidth="1"/>
-    <col min="3077" max="3077" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3078" max="3078" width="6.85546875" style="45" customWidth="1"/>
-    <col min="3079" max="3079" width="9.28515625" style="45" customWidth="1"/>
-    <col min="3080" max="3080" width="5.85546875" style="45" customWidth="1"/>
-    <col min="3081" max="3081" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3082" max="3082" width="10" style="45" customWidth="1"/>
-    <col min="3083" max="3088" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3089" max="3309" width="9.140625" style="45"/>
-    <col min="3310" max="3310" width="4.140625" style="45" customWidth="1"/>
-    <col min="3311" max="3311" width="15.5703125" style="45" customWidth="1"/>
-    <col min="3312" max="3312" width="7.28515625" style="45" customWidth="1"/>
-    <col min="3313" max="3313" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3314" max="3314" width="4.42578125" style="45" customWidth="1"/>
-    <col min="3315" max="3320" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3321" max="3321" width="9" style="45" customWidth="1"/>
-    <col min="3322" max="3322" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3323" max="3324" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3325" max="3326" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3327" max="3327" width="6.140625" style="45" customWidth="1"/>
-    <col min="3328" max="3328" width="6.42578125" style="45" customWidth="1"/>
-    <col min="3329" max="3329" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3330" max="3330" width="7.5703125" style="45" customWidth="1"/>
-    <col min="3331" max="3331" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3332" max="3332" width="7.140625" style="45" customWidth="1"/>
-    <col min="3333" max="3333" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3334" max="3334" width="6.85546875" style="45" customWidth="1"/>
-    <col min="3335" max="3335" width="9.28515625" style="45" customWidth="1"/>
-    <col min="3336" max="3336" width="5.85546875" style="45" customWidth="1"/>
-    <col min="3337" max="3337" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3338" max="3338" width="10" style="45" customWidth="1"/>
-    <col min="3339" max="3344" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3345" max="3565" width="9.140625" style="45"/>
-    <col min="3566" max="3566" width="4.140625" style="45" customWidth="1"/>
-    <col min="3567" max="3567" width="15.5703125" style="45" customWidth="1"/>
-    <col min="3568" max="3568" width="7.28515625" style="45" customWidth="1"/>
-    <col min="3569" max="3569" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3570" max="3570" width="4.42578125" style="45" customWidth="1"/>
-    <col min="3571" max="3576" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3577" max="3577" width="9" style="45" customWidth="1"/>
-    <col min="3578" max="3578" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3579" max="3580" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3581" max="3582" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3583" max="3583" width="6.140625" style="45" customWidth="1"/>
-    <col min="3584" max="3584" width="6.42578125" style="45" customWidth="1"/>
-    <col min="3585" max="3585" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3586" max="3586" width="7.5703125" style="45" customWidth="1"/>
-    <col min="3587" max="3587" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3588" max="3588" width="7.140625" style="45" customWidth="1"/>
-    <col min="3589" max="3589" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3590" max="3590" width="6.85546875" style="45" customWidth="1"/>
-    <col min="3591" max="3591" width="9.28515625" style="45" customWidth="1"/>
-    <col min="3592" max="3592" width="5.85546875" style="45" customWidth="1"/>
-    <col min="3593" max="3593" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3594" max="3594" width="10" style="45" customWidth="1"/>
-    <col min="3595" max="3600" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3601" max="3821" width="9.140625" style="45"/>
-    <col min="3822" max="3822" width="4.140625" style="45" customWidth="1"/>
-    <col min="3823" max="3823" width="15.5703125" style="45" customWidth="1"/>
-    <col min="3824" max="3824" width="7.28515625" style="45" customWidth="1"/>
-    <col min="3825" max="3825" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3826" max="3826" width="4.42578125" style="45" customWidth="1"/>
-    <col min="3827" max="3832" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3833" max="3833" width="9" style="45" customWidth="1"/>
-    <col min="3834" max="3834" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3835" max="3836" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3837" max="3838" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3839" max="3839" width="6.140625" style="45" customWidth="1"/>
-    <col min="3840" max="3840" width="6.42578125" style="45" customWidth="1"/>
-    <col min="3841" max="3841" width="4.85546875" style="45" customWidth="1"/>
-    <col min="3842" max="3842" width="7.5703125" style="45" customWidth="1"/>
-    <col min="3843" max="3843" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3844" max="3844" width="7.140625" style="45" customWidth="1"/>
-    <col min="3845" max="3845" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3846" max="3846" width="6.85546875" style="45" customWidth="1"/>
-    <col min="3847" max="3847" width="9.28515625" style="45" customWidth="1"/>
-    <col min="3848" max="3848" width="5.85546875" style="45" customWidth="1"/>
-    <col min="3849" max="3849" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3850" max="3850" width="10" style="45" customWidth="1"/>
-    <col min="3851" max="3856" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="3857" max="4077" width="9.140625" style="45"/>
-    <col min="4078" max="4078" width="4.140625" style="45" customWidth="1"/>
-    <col min="4079" max="4079" width="15.5703125" style="45" customWidth="1"/>
-    <col min="4080" max="4080" width="7.28515625" style="45" customWidth="1"/>
-    <col min="4081" max="4081" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4082" max="4082" width="4.42578125" style="45" customWidth="1"/>
-    <col min="4083" max="4088" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4089" max="4089" width="9" style="45" customWidth="1"/>
-    <col min="4090" max="4090" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4091" max="4092" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4093" max="4094" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4095" max="4095" width="6.140625" style="45" customWidth="1"/>
-    <col min="4096" max="4096" width="6.42578125" style="45" customWidth="1"/>
-    <col min="4097" max="4097" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4098" max="4098" width="7.5703125" style="45" customWidth="1"/>
-    <col min="4099" max="4099" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4100" max="4100" width="7.140625" style="45" customWidth="1"/>
-    <col min="4101" max="4101" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4102" max="4102" width="6.85546875" style="45" customWidth="1"/>
-    <col min="4103" max="4103" width="9.28515625" style="45" customWidth="1"/>
-    <col min="4104" max="4104" width="5.85546875" style="45" customWidth="1"/>
-    <col min="4105" max="4105" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4106" max="4106" width="10" style="45" customWidth="1"/>
-    <col min="4107" max="4112" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4113" max="4333" width="9.140625" style="45"/>
-    <col min="4334" max="4334" width="4.140625" style="45" customWidth="1"/>
-    <col min="4335" max="4335" width="15.5703125" style="45" customWidth="1"/>
-    <col min="4336" max="4336" width="7.28515625" style="45" customWidth="1"/>
-    <col min="4337" max="4337" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4338" max="4338" width="4.42578125" style="45" customWidth="1"/>
-    <col min="4339" max="4344" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4345" max="4345" width="9" style="45" customWidth="1"/>
-    <col min="4346" max="4346" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4347" max="4348" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4349" max="4350" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4351" max="4351" width="6.140625" style="45" customWidth="1"/>
-    <col min="4352" max="4352" width="6.42578125" style="45" customWidth="1"/>
-    <col min="4353" max="4353" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4354" max="4354" width="7.5703125" style="45" customWidth="1"/>
-    <col min="4355" max="4355" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4356" max="4356" width="7.140625" style="45" customWidth="1"/>
-    <col min="4357" max="4357" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4358" max="4358" width="6.85546875" style="45" customWidth="1"/>
-    <col min="4359" max="4359" width="9.28515625" style="45" customWidth="1"/>
-    <col min="4360" max="4360" width="5.85546875" style="45" customWidth="1"/>
-    <col min="4361" max="4361" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4362" max="4362" width="10" style="45" customWidth="1"/>
-    <col min="4363" max="4368" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4369" max="4589" width="9.140625" style="45"/>
-    <col min="4590" max="4590" width="4.140625" style="45" customWidth="1"/>
-    <col min="4591" max="4591" width="15.5703125" style="45" customWidth="1"/>
-    <col min="4592" max="4592" width="7.28515625" style="45" customWidth="1"/>
-    <col min="4593" max="4593" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4594" max="4594" width="4.42578125" style="45" customWidth="1"/>
-    <col min="4595" max="4600" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4601" max="4601" width="9" style="45" customWidth="1"/>
-    <col min="4602" max="4602" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4603" max="4604" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4605" max="4606" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4607" max="4607" width="6.140625" style="45" customWidth="1"/>
-    <col min="4608" max="4608" width="6.42578125" style="45" customWidth="1"/>
-    <col min="4609" max="4609" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4610" max="4610" width="7.5703125" style="45" customWidth="1"/>
-    <col min="4611" max="4611" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4612" max="4612" width="7.140625" style="45" customWidth="1"/>
-    <col min="4613" max="4613" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4614" max="4614" width="6.85546875" style="45" customWidth="1"/>
-    <col min="4615" max="4615" width="9.28515625" style="45" customWidth="1"/>
-    <col min="4616" max="4616" width="5.85546875" style="45" customWidth="1"/>
-    <col min="4617" max="4617" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4618" max="4618" width="10" style="45" customWidth="1"/>
-    <col min="4619" max="4624" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4625" max="4845" width="9.140625" style="45"/>
-    <col min="4846" max="4846" width="4.140625" style="45" customWidth="1"/>
-    <col min="4847" max="4847" width="15.5703125" style="45" customWidth="1"/>
-    <col min="4848" max="4848" width="7.28515625" style="45" customWidth="1"/>
-    <col min="4849" max="4849" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4850" max="4850" width="4.42578125" style="45" customWidth="1"/>
-    <col min="4851" max="4856" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4857" max="4857" width="9" style="45" customWidth="1"/>
-    <col min="4858" max="4858" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4859" max="4860" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4861" max="4862" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4863" max="4863" width="6.140625" style="45" customWidth="1"/>
-    <col min="4864" max="4864" width="6.42578125" style="45" customWidth="1"/>
-    <col min="4865" max="4865" width="4.85546875" style="45" customWidth="1"/>
-    <col min="4866" max="4866" width="7.5703125" style="45" customWidth="1"/>
-    <col min="4867" max="4867" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4868" max="4868" width="7.140625" style="45" customWidth="1"/>
-    <col min="4869" max="4869" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4870" max="4870" width="6.85546875" style="45" customWidth="1"/>
-    <col min="4871" max="4871" width="9.28515625" style="45" customWidth="1"/>
-    <col min="4872" max="4872" width="5.85546875" style="45" customWidth="1"/>
-    <col min="4873" max="4873" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4874" max="4874" width="10" style="45" customWidth="1"/>
-    <col min="4875" max="4880" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="4881" max="5101" width="9.140625" style="45"/>
-    <col min="5102" max="5102" width="4.140625" style="45" customWidth="1"/>
-    <col min="5103" max="5103" width="15.5703125" style="45" customWidth="1"/>
-    <col min="5104" max="5104" width="7.28515625" style="45" customWidth="1"/>
-    <col min="5105" max="5105" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5106" max="5106" width="4.42578125" style="45" customWidth="1"/>
-    <col min="5107" max="5112" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5113" max="5113" width="9" style="45" customWidth="1"/>
-    <col min="5114" max="5114" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5115" max="5116" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5117" max="5118" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5119" max="5119" width="6.140625" style="45" customWidth="1"/>
-    <col min="5120" max="5120" width="6.42578125" style="45" customWidth="1"/>
-    <col min="5121" max="5121" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5122" max="5122" width="7.5703125" style="45" customWidth="1"/>
-    <col min="5123" max="5123" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5124" max="5124" width="7.140625" style="45" customWidth="1"/>
-    <col min="5125" max="5125" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5126" max="5126" width="6.85546875" style="45" customWidth="1"/>
-    <col min="5127" max="5127" width="9.28515625" style="45" customWidth="1"/>
-    <col min="5128" max="5128" width="5.85546875" style="45" customWidth="1"/>
-    <col min="5129" max="5129" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5130" max="5130" width="10" style="45" customWidth="1"/>
-    <col min="5131" max="5136" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5137" max="5357" width="9.140625" style="45"/>
-    <col min="5358" max="5358" width="4.140625" style="45" customWidth="1"/>
-    <col min="5359" max="5359" width="15.5703125" style="45" customWidth="1"/>
-    <col min="5360" max="5360" width="7.28515625" style="45" customWidth="1"/>
-    <col min="5361" max="5361" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5362" max="5362" width="4.42578125" style="45" customWidth="1"/>
-    <col min="5363" max="5368" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5369" max="5369" width="9" style="45" customWidth="1"/>
-    <col min="5370" max="5370" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5371" max="5372" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5373" max="5374" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5375" max="5375" width="6.140625" style="45" customWidth="1"/>
-    <col min="5376" max="5376" width="6.42578125" style="45" customWidth="1"/>
-    <col min="5377" max="5377" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5378" max="5378" width="7.5703125" style="45" customWidth="1"/>
-    <col min="5379" max="5379" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5380" max="5380" width="7.140625" style="45" customWidth="1"/>
-    <col min="5381" max="5381" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5382" max="5382" width="6.85546875" style="45" customWidth="1"/>
-    <col min="5383" max="5383" width="9.28515625" style="45" customWidth="1"/>
-    <col min="5384" max="5384" width="5.85546875" style="45" customWidth="1"/>
-    <col min="5385" max="5385" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5386" max="5386" width="10" style="45" customWidth="1"/>
-    <col min="5387" max="5392" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5393" max="5613" width="9.140625" style="45"/>
-    <col min="5614" max="5614" width="4.140625" style="45" customWidth="1"/>
-    <col min="5615" max="5615" width="15.5703125" style="45" customWidth="1"/>
-    <col min="5616" max="5616" width="7.28515625" style="45" customWidth="1"/>
-    <col min="5617" max="5617" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5618" max="5618" width="4.42578125" style="45" customWidth="1"/>
-    <col min="5619" max="5624" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5625" max="5625" width="9" style="45" customWidth="1"/>
-    <col min="5626" max="5626" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5627" max="5628" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5629" max="5630" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5631" max="5631" width="6.140625" style="45" customWidth="1"/>
-    <col min="5632" max="5632" width="6.42578125" style="45" customWidth="1"/>
-    <col min="5633" max="5633" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5634" max="5634" width="7.5703125" style="45" customWidth="1"/>
-    <col min="5635" max="5635" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5636" max="5636" width="7.140625" style="45" customWidth="1"/>
-    <col min="5637" max="5637" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5638" max="5638" width="6.85546875" style="45" customWidth="1"/>
-    <col min="5639" max="5639" width="9.28515625" style="45" customWidth="1"/>
-    <col min="5640" max="5640" width="5.85546875" style="45" customWidth="1"/>
-    <col min="5641" max="5641" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5642" max="5642" width="10" style="45" customWidth="1"/>
-    <col min="5643" max="5648" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5649" max="5869" width="9.140625" style="45"/>
-    <col min="5870" max="5870" width="4.140625" style="45" customWidth="1"/>
-    <col min="5871" max="5871" width="15.5703125" style="45" customWidth="1"/>
-    <col min="5872" max="5872" width="7.28515625" style="45" customWidth="1"/>
-    <col min="5873" max="5873" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5874" max="5874" width="4.42578125" style="45" customWidth="1"/>
-    <col min="5875" max="5880" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5881" max="5881" width="9" style="45" customWidth="1"/>
-    <col min="5882" max="5882" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5883" max="5884" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5885" max="5886" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5887" max="5887" width="6.140625" style="45" customWidth="1"/>
-    <col min="5888" max="5888" width="6.42578125" style="45" customWidth="1"/>
-    <col min="5889" max="5889" width="4.85546875" style="45" customWidth="1"/>
-    <col min="5890" max="5890" width="7.5703125" style="45" customWidth="1"/>
-    <col min="5891" max="5891" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5892" max="5892" width="7.140625" style="45" customWidth="1"/>
-    <col min="5893" max="5893" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5894" max="5894" width="6.85546875" style="45" customWidth="1"/>
-    <col min="5895" max="5895" width="9.28515625" style="45" customWidth="1"/>
-    <col min="5896" max="5896" width="5.85546875" style="45" customWidth="1"/>
-    <col min="5897" max="5897" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5898" max="5898" width="10" style="45" customWidth="1"/>
-    <col min="5899" max="5904" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="5905" max="6125" width="9.140625" style="45"/>
-    <col min="6126" max="6126" width="4.140625" style="45" customWidth="1"/>
-    <col min="6127" max="6127" width="15.5703125" style="45" customWidth="1"/>
-    <col min="6128" max="6128" width="7.28515625" style="45" customWidth="1"/>
-    <col min="6129" max="6129" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6130" max="6130" width="4.42578125" style="45" customWidth="1"/>
-    <col min="6131" max="6136" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6137" max="6137" width="9" style="45" customWidth="1"/>
-    <col min="6138" max="6138" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6139" max="6140" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6141" max="6142" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6143" max="6143" width="6.140625" style="45" customWidth="1"/>
-    <col min="6144" max="6144" width="6.42578125" style="45" customWidth="1"/>
-    <col min="6145" max="6145" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6146" max="6146" width="7.5703125" style="45" customWidth="1"/>
-    <col min="6147" max="6147" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6148" max="6148" width="7.140625" style="45" customWidth="1"/>
-    <col min="6149" max="6149" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6150" max="6150" width="6.85546875" style="45" customWidth="1"/>
-    <col min="6151" max="6151" width="9.28515625" style="45" customWidth="1"/>
-    <col min="6152" max="6152" width="5.85546875" style="45" customWidth="1"/>
-    <col min="6153" max="6153" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6154" max="6154" width="10" style="45" customWidth="1"/>
-    <col min="6155" max="6160" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6161" max="6381" width="9.140625" style="45"/>
-    <col min="6382" max="6382" width="4.140625" style="45" customWidth="1"/>
-    <col min="6383" max="6383" width="15.5703125" style="45" customWidth="1"/>
-    <col min="6384" max="6384" width="7.28515625" style="45" customWidth="1"/>
-    <col min="6385" max="6385" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6386" max="6386" width="4.42578125" style="45" customWidth="1"/>
-    <col min="6387" max="6392" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6393" max="6393" width="9" style="45" customWidth="1"/>
-    <col min="6394" max="6394" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6395" max="6396" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6397" max="6398" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6399" max="6399" width="6.140625" style="45" customWidth="1"/>
-    <col min="6400" max="6400" width="6.42578125" style="45" customWidth="1"/>
-    <col min="6401" max="6401" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6402" max="6402" width="7.5703125" style="45" customWidth="1"/>
-    <col min="6403" max="6403" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6404" max="6404" width="7.140625" style="45" customWidth="1"/>
-    <col min="6405" max="6405" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6406" max="6406" width="6.85546875" style="45" customWidth="1"/>
-    <col min="6407" max="6407" width="9.28515625" style="45" customWidth="1"/>
-    <col min="6408" max="6408" width="5.85546875" style="45" customWidth="1"/>
-    <col min="6409" max="6409" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6410" max="6410" width="10" style="45" customWidth="1"/>
-    <col min="6411" max="6416" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6417" max="6637" width="9.140625" style="45"/>
-    <col min="6638" max="6638" width="4.140625" style="45" customWidth="1"/>
-    <col min="6639" max="6639" width="15.5703125" style="45" customWidth="1"/>
-    <col min="6640" max="6640" width="7.28515625" style="45" customWidth="1"/>
-    <col min="6641" max="6641" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6642" max="6642" width="4.42578125" style="45" customWidth="1"/>
-    <col min="6643" max="6648" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6649" max="6649" width="9" style="45" customWidth="1"/>
-    <col min="6650" max="6650" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6651" max="6652" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6653" max="6654" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6655" max="6655" width="6.140625" style="45" customWidth="1"/>
-    <col min="6656" max="6656" width="6.42578125" style="45" customWidth="1"/>
-    <col min="6657" max="6657" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6658" max="6658" width="7.5703125" style="45" customWidth="1"/>
-    <col min="6659" max="6659" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6660" max="6660" width="7.140625" style="45" customWidth="1"/>
-    <col min="6661" max="6661" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6662" max="6662" width="6.85546875" style="45" customWidth="1"/>
-    <col min="6663" max="6663" width="9.28515625" style="45" customWidth="1"/>
-    <col min="6664" max="6664" width="5.85546875" style="45" customWidth="1"/>
-    <col min="6665" max="6665" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6666" max="6666" width="10" style="45" customWidth="1"/>
-    <col min="6667" max="6672" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6673" max="6893" width="9.140625" style="45"/>
-    <col min="6894" max="6894" width="4.140625" style="45" customWidth="1"/>
-    <col min="6895" max="6895" width="15.5703125" style="45" customWidth="1"/>
-    <col min="6896" max="6896" width="7.28515625" style="45" customWidth="1"/>
-    <col min="6897" max="6897" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6898" max="6898" width="4.42578125" style="45" customWidth="1"/>
-    <col min="6899" max="6904" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6905" max="6905" width="9" style="45" customWidth="1"/>
-    <col min="6906" max="6906" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6907" max="6908" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6909" max="6910" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6911" max="6911" width="6.140625" style="45" customWidth="1"/>
-    <col min="6912" max="6912" width="6.42578125" style="45" customWidth="1"/>
-    <col min="6913" max="6913" width="4.85546875" style="45" customWidth="1"/>
-    <col min="6914" max="6914" width="7.5703125" style="45" customWidth="1"/>
-    <col min="6915" max="6915" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6916" max="6916" width="7.140625" style="45" customWidth="1"/>
-    <col min="6917" max="6917" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6918" max="6918" width="6.85546875" style="45" customWidth="1"/>
-    <col min="6919" max="6919" width="9.28515625" style="45" customWidth="1"/>
-    <col min="6920" max="6920" width="5.85546875" style="45" customWidth="1"/>
-    <col min="6921" max="6921" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6922" max="6922" width="10" style="45" customWidth="1"/>
-    <col min="6923" max="6928" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="6929" max="7149" width="9.140625" style="45"/>
-    <col min="7150" max="7150" width="4.140625" style="45" customWidth="1"/>
-    <col min="7151" max="7151" width="15.5703125" style="45" customWidth="1"/>
-    <col min="7152" max="7152" width="7.28515625" style="45" customWidth="1"/>
-    <col min="7153" max="7153" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7154" max="7154" width="4.42578125" style="45" customWidth="1"/>
-    <col min="7155" max="7160" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7161" max="7161" width="9" style="45" customWidth="1"/>
-    <col min="7162" max="7162" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7163" max="7164" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7165" max="7166" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7167" max="7167" width="6.140625" style="45" customWidth="1"/>
-    <col min="7168" max="7168" width="6.42578125" style="45" customWidth="1"/>
-    <col min="7169" max="7169" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7170" max="7170" width="7.5703125" style="45" customWidth="1"/>
-    <col min="7171" max="7171" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7172" max="7172" width="7.140625" style="45" customWidth="1"/>
-    <col min="7173" max="7173" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7174" max="7174" width="6.85546875" style="45" customWidth="1"/>
-    <col min="7175" max="7175" width="9.28515625" style="45" customWidth="1"/>
-    <col min="7176" max="7176" width="5.85546875" style="45" customWidth="1"/>
-    <col min="7177" max="7177" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7178" max="7178" width="10" style="45" customWidth="1"/>
-    <col min="7179" max="7184" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7185" max="7405" width="9.140625" style="45"/>
-    <col min="7406" max="7406" width="4.140625" style="45" customWidth="1"/>
-    <col min="7407" max="7407" width="15.5703125" style="45" customWidth="1"/>
-    <col min="7408" max="7408" width="7.28515625" style="45" customWidth="1"/>
-    <col min="7409" max="7409" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7410" max="7410" width="4.42578125" style="45" customWidth="1"/>
-    <col min="7411" max="7416" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7417" max="7417" width="9" style="45" customWidth="1"/>
-    <col min="7418" max="7418" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7419" max="7420" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7421" max="7422" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7423" max="7423" width="6.140625" style="45" customWidth="1"/>
-    <col min="7424" max="7424" width="6.42578125" style="45" customWidth="1"/>
-    <col min="7425" max="7425" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7426" max="7426" width="7.5703125" style="45" customWidth="1"/>
-    <col min="7427" max="7427" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7428" max="7428" width="7.140625" style="45" customWidth="1"/>
-    <col min="7429" max="7429" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7430" max="7430" width="6.85546875" style="45" customWidth="1"/>
-    <col min="7431" max="7431" width="9.28515625" style="45" customWidth="1"/>
-    <col min="7432" max="7432" width="5.85546875" style="45" customWidth="1"/>
-    <col min="7433" max="7433" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7434" max="7434" width="10" style="45" customWidth="1"/>
-    <col min="7435" max="7440" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7441" max="7661" width="9.140625" style="45"/>
-    <col min="7662" max="7662" width="4.140625" style="45" customWidth="1"/>
-    <col min="7663" max="7663" width="15.5703125" style="45" customWidth="1"/>
-    <col min="7664" max="7664" width="7.28515625" style="45" customWidth="1"/>
-    <col min="7665" max="7665" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7666" max="7666" width="4.42578125" style="45" customWidth="1"/>
-    <col min="7667" max="7672" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7673" max="7673" width="9" style="45" customWidth="1"/>
-    <col min="7674" max="7674" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7675" max="7676" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7677" max="7678" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7679" max="7679" width="6.140625" style="45" customWidth="1"/>
-    <col min="7680" max="7680" width="6.42578125" style="45" customWidth="1"/>
-    <col min="7681" max="7681" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7682" max="7682" width="7.5703125" style="45" customWidth="1"/>
-    <col min="7683" max="7683" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7684" max="7684" width="7.140625" style="45" customWidth="1"/>
-    <col min="7685" max="7685" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7686" max="7686" width="6.85546875" style="45" customWidth="1"/>
-    <col min="7687" max="7687" width="9.28515625" style="45" customWidth="1"/>
-    <col min="7688" max="7688" width="5.85546875" style="45" customWidth="1"/>
-    <col min="7689" max="7689" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7690" max="7690" width="10" style="45" customWidth="1"/>
-    <col min="7691" max="7696" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7697" max="7917" width="9.140625" style="45"/>
-    <col min="7918" max="7918" width="4.140625" style="45" customWidth="1"/>
-    <col min="7919" max="7919" width="15.5703125" style="45" customWidth="1"/>
-    <col min="7920" max="7920" width="7.28515625" style="45" customWidth="1"/>
-    <col min="7921" max="7921" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7922" max="7922" width="4.42578125" style="45" customWidth="1"/>
-    <col min="7923" max="7928" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7929" max="7929" width="9" style="45" customWidth="1"/>
-    <col min="7930" max="7930" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7931" max="7932" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7933" max="7934" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7935" max="7935" width="6.140625" style="45" customWidth="1"/>
-    <col min="7936" max="7936" width="6.42578125" style="45" customWidth="1"/>
-    <col min="7937" max="7937" width="4.85546875" style="45" customWidth="1"/>
-    <col min="7938" max="7938" width="7.5703125" style="45" customWidth="1"/>
-    <col min="7939" max="7939" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7940" max="7940" width="7.140625" style="45" customWidth="1"/>
-    <col min="7941" max="7941" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7942" max="7942" width="6.85546875" style="45" customWidth="1"/>
-    <col min="7943" max="7943" width="9.28515625" style="45" customWidth="1"/>
-    <col min="7944" max="7944" width="5.85546875" style="45" customWidth="1"/>
-    <col min="7945" max="7945" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7946" max="7946" width="10" style="45" customWidth="1"/>
-    <col min="7947" max="7952" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="7953" max="8173" width="9.140625" style="45"/>
-    <col min="8174" max="8174" width="4.140625" style="45" customWidth="1"/>
-    <col min="8175" max="8175" width="15.5703125" style="45" customWidth="1"/>
-    <col min="8176" max="8176" width="7.28515625" style="45" customWidth="1"/>
-    <col min="8177" max="8177" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8178" max="8178" width="4.42578125" style="45" customWidth="1"/>
-    <col min="8179" max="8184" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8185" max="8185" width="9" style="45" customWidth="1"/>
-    <col min="8186" max="8186" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8187" max="8188" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8189" max="8190" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8191" max="8191" width="6.140625" style="45" customWidth="1"/>
-    <col min="8192" max="8192" width="6.42578125" style="45" customWidth="1"/>
-    <col min="8193" max="8193" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8194" max="8194" width="7.5703125" style="45" customWidth="1"/>
-    <col min="8195" max="8195" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8196" max="8196" width="7.140625" style="45" customWidth="1"/>
-    <col min="8197" max="8197" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8198" max="8198" width="6.85546875" style="45" customWidth="1"/>
-    <col min="8199" max="8199" width="9.28515625" style="45" customWidth="1"/>
-    <col min="8200" max="8200" width="5.85546875" style="45" customWidth="1"/>
-    <col min="8201" max="8201" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8202" max="8202" width="10" style="45" customWidth="1"/>
-    <col min="8203" max="8208" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8209" max="8429" width="9.140625" style="45"/>
-    <col min="8430" max="8430" width="4.140625" style="45" customWidth="1"/>
-    <col min="8431" max="8431" width="15.5703125" style="45" customWidth="1"/>
-    <col min="8432" max="8432" width="7.28515625" style="45" customWidth="1"/>
-    <col min="8433" max="8433" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8434" max="8434" width="4.42578125" style="45" customWidth="1"/>
-    <col min="8435" max="8440" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8441" max="8441" width="9" style="45" customWidth="1"/>
-    <col min="8442" max="8442" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8443" max="8444" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8445" max="8446" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8447" max="8447" width="6.140625" style="45" customWidth="1"/>
-    <col min="8448" max="8448" width="6.42578125" style="45" customWidth="1"/>
-    <col min="8449" max="8449" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8450" max="8450" width="7.5703125" style="45" customWidth="1"/>
-    <col min="8451" max="8451" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8452" max="8452" width="7.140625" style="45" customWidth="1"/>
-    <col min="8453" max="8453" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8454" max="8454" width="6.85546875" style="45" customWidth="1"/>
-    <col min="8455" max="8455" width="9.28515625" style="45" customWidth="1"/>
-    <col min="8456" max="8456" width="5.85546875" style="45" customWidth="1"/>
-    <col min="8457" max="8457" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8458" max="8458" width="10" style="45" customWidth="1"/>
-    <col min="8459" max="8464" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8465" max="8685" width="9.140625" style="45"/>
-    <col min="8686" max="8686" width="4.140625" style="45" customWidth="1"/>
-    <col min="8687" max="8687" width="15.5703125" style="45" customWidth="1"/>
-    <col min="8688" max="8688" width="7.28515625" style="45" customWidth="1"/>
-    <col min="8689" max="8689" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8690" max="8690" width="4.42578125" style="45" customWidth="1"/>
-    <col min="8691" max="8696" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8697" max="8697" width="9" style="45" customWidth="1"/>
-    <col min="8698" max="8698" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8699" max="8700" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8701" max="8702" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8703" max="8703" width="6.140625" style="45" customWidth="1"/>
-    <col min="8704" max="8704" width="6.42578125" style="45" customWidth="1"/>
-    <col min="8705" max="8705" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8706" max="8706" width="7.5703125" style="45" customWidth="1"/>
-    <col min="8707" max="8707" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8708" max="8708" width="7.140625" style="45" customWidth="1"/>
-    <col min="8709" max="8709" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8710" max="8710" width="6.85546875" style="45" customWidth="1"/>
-    <col min="8711" max="8711" width="9.28515625" style="45" customWidth="1"/>
-    <col min="8712" max="8712" width="5.85546875" style="45" customWidth="1"/>
-    <col min="8713" max="8713" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8714" max="8714" width="10" style="45" customWidth="1"/>
-    <col min="8715" max="8720" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8721" max="8941" width="9.140625" style="45"/>
-    <col min="8942" max="8942" width="4.140625" style="45" customWidth="1"/>
-    <col min="8943" max="8943" width="15.5703125" style="45" customWidth="1"/>
-    <col min="8944" max="8944" width="7.28515625" style="45" customWidth="1"/>
-    <col min="8945" max="8945" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8946" max="8946" width="4.42578125" style="45" customWidth="1"/>
-    <col min="8947" max="8952" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8953" max="8953" width="9" style="45" customWidth="1"/>
-    <col min="8954" max="8954" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8955" max="8956" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8957" max="8958" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8959" max="8959" width="6.140625" style="45" customWidth="1"/>
-    <col min="8960" max="8960" width="6.42578125" style="45" customWidth="1"/>
-    <col min="8961" max="8961" width="4.85546875" style="45" customWidth="1"/>
-    <col min="8962" max="8962" width="7.5703125" style="45" customWidth="1"/>
-    <col min="8963" max="8963" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8964" max="8964" width="7.140625" style="45" customWidth="1"/>
-    <col min="8965" max="8965" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8966" max="8966" width="6.85546875" style="45" customWidth="1"/>
-    <col min="8967" max="8967" width="9.28515625" style="45" customWidth="1"/>
-    <col min="8968" max="8968" width="5.85546875" style="45" customWidth="1"/>
-    <col min="8969" max="8969" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8970" max="8970" width="10" style="45" customWidth="1"/>
-    <col min="8971" max="8976" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="8977" max="9197" width="9.140625" style="45"/>
-    <col min="9198" max="9198" width="4.140625" style="45" customWidth="1"/>
-    <col min="9199" max="9199" width="15.5703125" style="45" customWidth="1"/>
-    <col min="9200" max="9200" width="7.28515625" style="45" customWidth="1"/>
-    <col min="9201" max="9201" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9202" max="9202" width="4.42578125" style="45" customWidth="1"/>
-    <col min="9203" max="9208" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9209" max="9209" width="9" style="45" customWidth="1"/>
-    <col min="9210" max="9210" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9211" max="9212" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9213" max="9214" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9215" max="9215" width="6.140625" style="45" customWidth="1"/>
-    <col min="9216" max="9216" width="6.42578125" style="45" customWidth="1"/>
-    <col min="9217" max="9217" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9218" max="9218" width="7.5703125" style="45" customWidth="1"/>
-    <col min="9219" max="9219" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9220" max="9220" width="7.140625" style="45" customWidth="1"/>
-    <col min="9221" max="9221" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9222" max="9222" width="6.85546875" style="45" customWidth="1"/>
-    <col min="9223" max="9223" width="9.28515625" style="45" customWidth="1"/>
-    <col min="9224" max="9224" width="5.85546875" style="45" customWidth="1"/>
-    <col min="9225" max="9225" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9226" max="9226" width="10" style="45" customWidth="1"/>
-    <col min="9227" max="9232" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9233" max="9453" width="9.140625" style="45"/>
-    <col min="9454" max="9454" width="4.140625" style="45" customWidth="1"/>
-    <col min="9455" max="9455" width="15.5703125" style="45" customWidth="1"/>
-    <col min="9456" max="9456" width="7.28515625" style="45" customWidth="1"/>
-    <col min="9457" max="9457" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9458" max="9458" width="4.42578125" style="45" customWidth="1"/>
-    <col min="9459" max="9464" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9465" max="9465" width="9" style="45" customWidth="1"/>
-    <col min="9466" max="9466" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9467" max="9468" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9469" max="9470" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9471" max="9471" width="6.140625" style="45" customWidth="1"/>
-    <col min="9472" max="9472" width="6.42578125" style="45" customWidth="1"/>
-    <col min="9473" max="9473" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9474" max="9474" width="7.5703125" style="45" customWidth="1"/>
-    <col min="9475" max="9475" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9476" max="9476" width="7.140625" style="45" customWidth="1"/>
-    <col min="9477" max="9477" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9478" max="9478" width="6.85546875" style="45" customWidth="1"/>
-    <col min="9479" max="9479" width="9.28515625" style="45" customWidth="1"/>
-    <col min="9480" max="9480" width="5.85546875" style="45" customWidth="1"/>
-    <col min="9481" max="9481" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9482" max="9482" width="10" style="45" customWidth="1"/>
-    <col min="9483" max="9488" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9489" max="9709" width="9.140625" style="45"/>
-    <col min="9710" max="9710" width="4.140625" style="45" customWidth="1"/>
-    <col min="9711" max="9711" width="15.5703125" style="45" customWidth="1"/>
-    <col min="9712" max="9712" width="7.28515625" style="45" customWidth="1"/>
-    <col min="9713" max="9713" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9714" max="9714" width="4.42578125" style="45" customWidth="1"/>
-    <col min="9715" max="9720" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9721" max="9721" width="9" style="45" customWidth="1"/>
-    <col min="9722" max="9722" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9723" max="9724" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9725" max="9726" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9727" max="9727" width="6.140625" style="45" customWidth="1"/>
-    <col min="9728" max="9728" width="6.42578125" style="45" customWidth="1"/>
-    <col min="9729" max="9729" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9730" max="9730" width="7.5703125" style="45" customWidth="1"/>
-    <col min="9731" max="9731" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9732" max="9732" width="7.140625" style="45" customWidth="1"/>
-    <col min="9733" max="9733" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9734" max="9734" width="6.85546875" style="45" customWidth="1"/>
-    <col min="9735" max="9735" width="9.28515625" style="45" customWidth="1"/>
-    <col min="9736" max="9736" width="5.85546875" style="45" customWidth="1"/>
-    <col min="9737" max="9737" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9738" max="9738" width="10" style="45" customWidth="1"/>
-    <col min="9739" max="9744" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9745" max="9965" width="9.140625" style="45"/>
-    <col min="9966" max="9966" width="4.140625" style="45" customWidth="1"/>
-    <col min="9967" max="9967" width="15.5703125" style="45" customWidth="1"/>
-    <col min="9968" max="9968" width="7.28515625" style="45" customWidth="1"/>
-    <col min="9969" max="9969" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9970" max="9970" width="4.42578125" style="45" customWidth="1"/>
-    <col min="9971" max="9976" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9977" max="9977" width="9" style="45" customWidth="1"/>
-    <col min="9978" max="9978" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9979" max="9980" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9981" max="9982" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9983" max="9983" width="6.140625" style="45" customWidth="1"/>
-    <col min="9984" max="9984" width="6.42578125" style="45" customWidth="1"/>
-    <col min="9985" max="9985" width="4.85546875" style="45" customWidth="1"/>
-    <col min="9986" max="9986" width="7.5703125" style="45" customWidth="1"/>
-    <col min="9987" max="9987" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9988" max="9988" width="7.140625" style="45" customWidth="1"/>
-    <col min="9989" max="9989" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9990" max="9990" width="6.85546875" style="45" customWidth="1"/>
-    <col min="9991" max="9991" width="9.28515625" style="45" customWidth="1"/>
-    <col min="9992" max="9992" width="5.85546875" style="45" customWidth="1"/>
-    <col min="9993" max="9993" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="9994" max="9994" width="10" style="45" customWidth="1"/>
-    <col min="9995" max="10000" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10001" max="10221" width="9.140625" style="45"/>
-    <col min="10222" max="10222" width="4.140625" style="45" customWidth="1"/>
-    <col min="10223" max="10223" width="15.5703125" style="45" customWidth="1"/>
-    <col min="10224" max="10224" width="7.28515625" style="45" customWidth="1"/>
-    <col min="10225" max="10225" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10226" max="10226" width="4.42578125" style="45" customWidth="1"/>
-    <col min="10227" max="10232" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10233" max="10233" width="9" style="45" customWidth="1"/>
-    <col min="10234" max="10234" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10235" max="10236" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10237" max="10238" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10239" max="10239" width="6.140625" style="45" customWidth="1"/>
-    <col min="10240" max="10240" width="6.42578125" style="45" customWidth="1"/>
-    <col min="10241" max="10241" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10242" max="10242" width="7.5703125" style="45" customWidth="1"/>
-    <col min="10243" max="10243" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10244" max="10244" width="7.140625" style="45" customWidth="1"/>
-    <col min="10245" max="10245" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10246" max="10246" width="6.85546875" style="45" customWidth="1"/>
-    <col min="10247" max="10247" width="9.28515625" style="45" customWidth="1"/>
-    <col min="10248" max="10248" width="5.85546875" style="45" customWidth="1"/>
-    <col min="10249" max="10249" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10250" max="10250" width="10" style="45" customWidth="1"/>
-    <col min="10251" max="10256" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10257" max="10477" width="9.140625" style="45"/>
-    <col min="10478" max="10478" width="4.140625" style="45" customWidth="1"/>
-    <col min="10479" max="10479" width="15.5703125" style="45" customWidth="1"/>
-    <col min="10480" max="10480" width="7.28515625" style="45" customWidth="1"/>
-    <col min="10481" max="10481" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10482" max="10482" width="4.42578125" style="45" customWidth="1"/>
-    <col min="10483" max="10488" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10489" max="10489" width="9" style="45" customWidth="1"/>
-    <col min="10490" max="10490" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10491" max="10492" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10493" max="10494" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10495" max="10495" width="6.140625" style="45" customWidth="1"/>
-    <col min="10496" max="10496" width="6.42578125" style="45" customWidth="1"/>
-    <col min="10497" max="10497" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10498" max="10498" width="7.5703125" style="45" customWidth="1"/>
-    <col min="10499" max="10499" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10500" max="10500" width="7.140625" style="45" customWidth="1"/>
-    <col min="10501" max="10501" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10502" max="10502" width="6.85546875" style="45" customWidth="1"/>
-    <col min="10503" max="10503" width="9.28515625" style="45" customWidth="1"/>
-    <col min="10504" max="10504" width="5.85546875" style="45" customWidth="1"/>
-    <col min="10505" max="10505" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10506" max="10506" width="10" style="45" customWidth="1"/>
-    <col min="10507" max="10512" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10513" max="10733" width="9.140625" style="45"/>
-    <col min="10734" max="10734" width="4.140625" style="45" customWidth="1"/>
-    <col min="10735" max="10735" width="15.5703125" style="45" customWidth="1"/>
-    <col min="10736" max="10736" width="7.28515625" style="45" customWidth="1"/>
-    <col min="10737" max="10737" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10738" max="10738" width="4.42578125" style="45" customWidth="1"/>
-    <col min="10739" max="10744" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10745" max="10745" width="9" style="45" customWidth="1"/>
-    <col min="10746" max="10746" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10747" max="10748" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10749" max="10750" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10751" max="10751" width="6.140625" style="45" customWidth="1"/>
-    <col min="10752" max="10752" width="6.42578125" style="45" customWidth="1"/>
-    <col min="10753" max="10753" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10754" max="10754" width="7.5703125" style="45" customWidth="1"/>
-    <col min="10755" max="10755" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10756" max="10756" width="7.140625" style="45" customWidth="1"/>
-    <col min="10757" max="10757" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10758" max="10758" width="6.85546875" style="45" customWidth="1"/>
-    <col min="10759" max="10759" width="9.28515625" style="45" customWidth="1"/>
-    <col min="10760" max="10760" width="5.85546875" style="45" customWidth="1"/>
-    <col min="10761" max="10761" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10762" max="10762" width="10" style="45" customWidth="1"/>
-    <col min="10763" max="10768" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="10769" max="10989" width="9.140625" style="45"/>
-    <col min="10990" max="10990" width="4.140625" style="45" customWidth="1"/>
-    <col min="10991" max="10991" width="15.5703125" style="45" customWidth="1"/>
-    <col min="10992" max="10992" width="7.28515625" style="45" customWidth="1"/>
-    <col min="10993" max="10993" width="4.85546875" style="45" customWidth="1"/>
-    <col min="10994" max="10994" width="4.42578125" style="45" customWidth="1"/>
-    <col min="10995" max="11000" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11001" max="11001" width="9" style="45" customWidth="1"/>
-    <col min="11002" max="11002" width="4.85546875" style="45" customWidth="1"/>
-    <col min="11003" max="11004" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11005" max="11006" width="4.85546875" style="45" customWidth="1"/>
-    <col min="11007" max="11007" width="6.140625" style="45" customWidth="1"/>
-    <col min="11008" max="11008" width="6.42578125" style="45" customWidth="1"/>
-    <col min="11009" max="11009" width="4.85546875" style="45" customWidth="1"/>
-    <col min="11010" max="11010" width="7.5703125" style="45" customWidth="1"/>
-    <col min="11011" max="11011" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11012" max="11012" width="7.140625" style="45" customWidth="1"/>
-    <col min="11013" max="11013" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11014" max="11014" width="6.85546875" style="45" customWidth="1"/>
-    <col min="11015" max="11015" width="9.28515625" style="45" customWidth="1"/>
-    <col min="11016" max="11016" width="5.85546875" style="45" customWidth="1"/>
-    <col min="11017" max="11017" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11018" max="11018" width="10" style="45" customWidth="1"/>
-    <col min="11019" max="11024" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11025" max="11245" width="9.140625" style="45"/>
-    <col min="11246" max="11246" width="4.140625" style="45" customWidth="1"/>
-    <col min="11247" max="11247" width="15.5703125" style="45" customWidth="1"/>
-    <col min="11248" max="11248" width="7.28515625" style="45" customWidth="1"/>
-    <col min="11249" max="11249" width="4.85546875" style="45" customWidth="1"/>
-    <col min="11250" max="11250" width="4.42578125" style="45" customWidth="1"/>
-    <col min="11251" max="11256" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11257" max="11257" width="9" style="45" customWidth="1"/>
-    <col min="11258" max="11258" width="4.85546875" style="45" customWidth="1"/>
-    <col min="11259" max="11260" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11261" max="11262" width="4.85546875" style="45" customWidth="1"/>
-    <col min="11263" max="11263" width="6.140625" style="45" customWidth="1"/>
-    <col min="11264" max="11264" width="6.42578125" style="45" customWidth="1"/>
-    <col min="11265" max="11265" width="4.85546875" style="45" customWidth="1"/>
-    <col min="11266" max="11266" width="7.5703125" style="45" customWidth="1"/>
-    <col min="11267" max="11267" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11268" max="11268" width="7.140625" style="45" customWidth="1"/>
-    <col min="11269" max="11269" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11270" max="11270" width="6.85546875" style="45" customWidth="1"/>
-    <col min="11271" max="11271" width="9.28515625" style="45" customWidth="1"/>
-    <col min="11272" max="11272" width="5.85546875" style="45" customWidth="1"/>
-    <col min="11273" max="11273" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11274" max="11274" width="10" style="45" customWidth="1"/>
-    <col min="11275" max="11280" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11281" max="11501" width="9.140625" style="45"/>
-    <col min="11502" max="11502" width="4.140625" style="45" customWidth="1"/>
-    <col min="11503" max="11503" width="15.5703125" style="45" customWidth="1"/>
-    <col min="11504" max="11504" width="7.28515625" style="45" customWidth="1"/>
-    <col min="11505" max="11505" width="4.85546875" style="45" customWidth="1"/>
-    <col min="11506" max="11506" width="4.42578125" style="45" customWidth="1"/>
-    <col min="11507" max="11512" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11513" max="11513" width="9" style="45" customWidth="1"/>
-    <col min="11514" max="11514" width="4.85546875" style="45" customWidth="1"/>
-    <col min="11515" max="11516" width="0" style="45" hidden="1" customWidth="1"/>
-    <col min="11517" max="11517" width="4.85546875" style="45" customWidth="1"/>
-    <col min="11518" max="11518" width="4.85546875" customWidth="1"/>
-    <col min="11519" max="11519" width="6.140625" customWidth="1"/>
-    <col min="11520" max="11520" width="6.42578125" customWidth="1"/>
-    <col min="11521" max="11521" width="4.85546875" customWidth="1"/>
-    <col min="11522" max="11522" width="7.5703125" customWidth="1"/>
-    <col min="11523" max="11523" width="0" hidden="1" customWidth="1"/>
-    <col min="11524" max="11524" width="7.140625" customWidth="1"/>
-    <col min="11525" max="11525" width="0" hidden="1" customWidth="1"/>
-    <col min="11526" max="11526" width="6.85546875" customWidth="1"/>
-    <col min="11527" max="11527" width="9.28515625" customWidth="1"/>
-    <col min="11528" max="11528" width="5.85546875" customWidth="1"/>
-    <col min="11529" max="11529" width="0" hidden="1" customWidth="1"/>
-    <col min="11530" max="11530" width="10" customWidth="1"/>
-    <col min="11531" max="11536" width="0" hidden="1" customWidth="1"/>
-    <col min="11758" max="11758" width="4.140625" customWidth="1"/>
-    <col min="11759" max="11759" width="15.5703125" customWidth="1"/>
-    <col min="11760" max="11760" width="7.28515625" customWidth="1"/>
-    <col min="11761" max="11761" width="4.85546875" customWidth="1"/>
-    <col min="11762" max="11762" width="4.42578125" customWidth="1"/>
-    <col min="11763" max="11768" width="0" hidden="1" customWidth="1"/>
-    <col min="11769" max="11769" width="9" customWidth="1"/>
-    <col min="11770" max="11770" width="4.85546875" customWidth="1"/>
-    <col min="11771" max="11772" width="0" hidden="1" customWidth="1"/>
-    <col min="11773" max="11774" width="4.85546875" customWidth="1"/>
-    <col min="11775" max="11775" width="6.140625" customWidth="1"/>
-    <col min="11776" max="11776" width="6.42578125" customWidth="1"/>
-    <col min="11777" max="11777" width="4.85546875" customWidth="1"/>
-    <col min="11778" max="11778" width="7.5703125" customWidth="1"/>
-    <col min="11779" max="11779" width="0" hidden="1" customWidth="1"/>
-    <col min="11780" max="11780" width="7.140625" customWidth="1"/>
-    <col min="11781" max="11781" width="0" hidden="1" customWidth="1"/>
-    <col min="11782" max="11782" width="6.85546875" customWidth="1"/>
-    <col min="11783" max="11783" width="9.28515625" customWidth="1"/>
-    <col min="11784" max="11784" width="5.85546875" customWidth="1"/>
-    <col min="11785" max="11785" width="0" hidden="1" customWidth="1"/>
-    <col min="11786" max="11786" width="10" customWidth="1"/>
-    <col min="11787" max="11792" width="0" hidden="1" customWidth="1"/>
-    <col min="12014" max="12014" width="4.140625" customWidth="1"/>
-    <col min="12015" max="12015" width="15.5703125" customWidth="1"/>
-    <col min="12016" max="12016" width="7.28515625" customWidth="1"/>
-    <col min="12017" max="12017" width="4.85546875" customWidth="1"/>
-    <col min="12018" max="12018" width="4.42578125" customWidth="1"/>
-    <col min="12019" max="12024" width="0" hidden="1" customWidth="1"/>
-    <col min="12025" max="12025" width="9" customWidth="1"/>
-    <col min="12026" max="12026" width="4.85546875" customWidth="1"/>
-    <col min="12027" max="12028" width="0" hidden="1" customWidth="1"/>
-    <col min="12029" max="12030" width="4.85546875" customWidth="1"/>
-    <col min="12031" max="12031" width="6.140625" customWidth="1"/>
-    <col min="12032" max="12032" width="6.42578125" customWidth="1"/>
-    <col min="12033" max="12033" width="4.85546875" customWidth="1"/>
-    <col min="12034" max="12034" width="7.5703125" customWidth="1"/>
-    <col min="12035" max="12035" width="0" hidden="1" customWidth="1"/>
-    <col min="12036" max="12036" width="7.140625" customWidth="1"/>
-    <col min="12037" max="12037" width="0" hidden="1" customWidth="1"/>
-    <col min="12038" max="12038" width="6.85546875" customWidth="1"/>
-    <col min="12039" max="12039" width="9.28515625" customWidth="1"/>
-    <col min="12040" max="12040" width="5.85546875" customWidth="1"/>
-    <col min="12041" max="12041" width="0" hidden="1" customWidth="1"/>
-    <col min="12042" max="12042" width="10" customWidth="1"/>
-    <col min="12043" max="12048" width="0" hidden="1" customWidth="1"/>
-    <col min="12270" max="12270" width="4.140625" customWidth="1"/>
-    <col min="12271" max="12271" width="15.5703125" customWidth="1"/>
-    <col min="12272" max="12272" width="7.28515625" customWidth="1"/>
-    <col min="12273" max="12273" width="4.85546875" customWidth="1"/>
-    <col min="12274" max="12274" width="4.42578125" customWidth="1"/>
-    <col min="12275" max="12280" width="0" hidden="1" customWidth="1"/>
-    <col min="12281" max="12281" width="9" customWidth="1"/>
-    <col min="12282" max="12282" width="4.85546875" customWidth="1"/>
-    <col min="12283" max="12284" width="0" hidden="1" customWidth="1"/>
-    <col min="12285" max="12286" width="4.85546875" customWidth="1"/>
-    <col min="12287" max="12287" width="6.140625" customWidth="1"/>
-    <col min="12288" max="12288" width="6.42578125" customWidth="1"/>
-    <col min="12289" max="12289" width="4.85546875" customWidth="1"/>
-    <col min="12290" max="12290" width="7.5703125" customWidth="1"/>
-    <col min="12291" max="12291" width="0" hidden="1" customWidth="1"/>
-    <col min="12292" max="12292" width="7.140625" customWidth="1"/>
-    <col min="12293" max="12293" width="0" hidden="1" customWidth="1"/>
-    <col min="12294" max="12294" width="6.85546875" customWidth="1"/>
-    <col min="12295" max="12295" width="9.28515625" customWidth="1"/>
-    <col min="12296" max="12296" width="5.85546875" customWidth="1"/>
-    <col min="12297" max="12297" width="0" hidden="1" customWidth="1"/>
-    <col min="12298" max="12298" width="10" customWidth="1"/>
-    <col min="12299" max="12304" width="0" hidden="1" customWidth="1"/>
-    <col min="12526" max="12526" width="4.140625" customWidth="1"/>
-    <col min="12527" max="12527" width="15.5703125" customWidth="1"/>
-    <col min="12528" max="12528" width="7.28515625" customWidth="1"/>
-    <col min="12529" max="12529" width="4.85546875" customWidth="1"/>
-    <col min="12530" max="12530" width="4.42578125" customWidth="1"/>
-    <col min="12531" max="12536" width="0" hidden="1" customWidth="1"/>
-    <col min="12537" max="12537" width="9" customWidth="1"/>
-    <col min="12538" max="12538" width="4.85546875" customWidth="1"/>
-    <col min="12539" max="12540" width="0" hidden="1" customWidth="1"/>
-    <col min="12541" max="12542" width="4.85546875" customWidth="1"/>
-    <col min="12543" max="12543" width="6.140625" customWidth="1"/>
-    <col min="12544" max="12544" width="6.42578125" customWidth="1"/>
-    <col min="12545" max="12545" width="4.85546875" customWidth="1"/>
-    <col min="12546" max="12546" width="7.5703125" customWidth="1"/>
-    <col min="12547" max="12547" width="0" hidden="1" customWidth="1"/>
-    <col min="12548" max="12548" width="7.140625" customWidth="1"/>
-    <col min="12549" max="12549" width="0" hidden="1" customWidth="1"/>
-    <col min="12550" max="12550" width="6.85546875" customWidth="1"/>
-    <col min="12551" max="12551" width="9.28515625" customWidth="1"/>
-    <col min="12552" max="12552" width="5.85546875" customWidth="1"/>
-    <col min="12553" max="12553" width="0" hidden="1" customWidth="1"/>
-    <col min="12554" max="12554" width="10" customWidth="1"/>
-    <col min="12555" max="12560" width="0" hidden="1" customWidth="1"/>
-    <col min="12782" max="12782" width="4.140625" customWidth="1"/>
-    <col min="12783" max="12783" width="15.5703125" customWidth="1"/>
-    <col min="12784" max="12784" width="7.28515625" customWidth="1"/>
-    <col min="12785" max="12785" width="4.85546875" customWidth="1"/>
-    <col min="12786" max="12786" width="4.42578125" customWidth="1"/>
-    <col min="12787" max="12792" width="0" hidden="1" customWidth="1"/>
-    <col min="12793" max="12793" width="9" customWidth="1"/>
-    <col min="12794" max="12794" width="4.85546875" customWidth="1"/>
-    <col min="12795" max="12796" width="0" hidden="1" customWidth="1"/>
-    <col min="12797" max="12798" width="4.85546875" customWidth="1"/>
-    <col min="12799" max="12799" width="6.140625" customWidth="1"/>
-    <col min="12800" max="12800" width="6.42578125" customWidth="1"/>
-    <col min="12801" max="12801" width="4.85546875" customWidth="1"/>
-    <col min="12802" max="12802" width="7.5703125" customWidth="1"/>
-    <col min="12803" max="12803" width="0" hidden="1" customWidth="1"/>
-    <col min="12804" max="12804" width="7.140625" customWidth="1"/>
-    <col min="12805" max="12805" width="0" hidden="1" customWidth="1"/>
-    <col min="12806" max="12806" width="6.85546875" customWidth="1"/>
-    <col min="12807" max="12807" width="9.28515625" customWidth="1"/>
-    <col min="12808" max="12808" width="5.85546875" customWidth="1"/>
-    <col min="12809" max="12809" width="0" hidden="1" customWidth="1"/>
-    <col min="12810" max="12810" width="10" customWidth="1"/>
-    <col min="12811" max="12816" width="0" hidden="1" customWidth="1"/>
-    <col min="13038" max="13038" width="4.140625" customWidth="1"/>
-    <col min="13039" max="13039" width="15.5703125" customWidth="1"/>
-    <col min="13040" max="13040" width="7.28515625" customWidth="1"/>
-    <col min="13041" max="13041" width="4.85546875" customWidth="1"/>
-    <col min="13042" max="13042" width="4.42578125" customWidth="1"/>
-    <col min="13043" max="13048" width="0" hidden="1" customWidth="1"/>
-    <col min="13049" max="13049" width="9" customWidth="1"/>
-    <col min="13050" max="13050" width="4.85546875" customWidth="1"/>
-    <col min="13051" max="13052" width="0" hidden="1" customWidth="1"/>
-    <col min="13053" max="13054" width="4.85546875" customWidth="1"/>
-    <col min="13055" max="13055" width="6.140625" customWidth="1"/>
-    <col min="13056" max="13056" width="6.42578125" customWidth="1"/>
-    <col min="13057" max="13057" width="4.85546875" customWidth="1"/>
-    <col min="13058" max="13058" width="7.5703125" customWidth="1"/>
-    <col min="13059" max="13059" width="0" hidden="1" customWidth="1"/>
-    <col min="13060" max="13060" width="7.140625" customWidth="1"/>
-    <col min="13061" max="13061" width="0" hidden="1" customWidth="1"/>
-    <col min="13062" max="13062" width="6.85546875" customWidth="1"/>
-    <col min="13063" max="13063" width="9.28515625" customWidth="1"/>
-    <col min="13064" max="13064" width="5.85546875" customWidth="1"/>
-    <col min="13065" max="13065" width="0" hidden="1" customWidth="1"/>
-    <col min="13066" max="13066" width="10" customWidth="1"/>
-    <col min="13067" max="13072" width="0" hidden="1" customWidth="1"/>
-    <col min="13294" max="13294" width="4.140625" customWidth="1"/>
-    <col min="13295" max="13295" width="15.5703125" customWidth="1"/>
-    <col min="13296" max="13296" width="7.28515625" customWidth="1"/>
-    <col min="13297" max="13297" width="4.85546875" customWidth="1"/>
-    <col min="13298" max="13298" width="4.42578125" customWidth="1"/>
-    <col min="13299" max="13304" width="0" hidden="1" customWidth="1"/>
-    <col min="13305" max="13305" width="9" customWidth="1"/>
-    <col min="13306" max="13306" width="4.85546875" customWidth="1"/>
-    <col min="13307" max="13308" width="0" hidden="1" customWidth="1"/>
-    <col min="13309" max="13310" width="4.85546875" customWidth="1"/>
-    <col min="13311" max="13311" width="6.140625" customWidth="1"/>
-    <col min="13312" max="13312" width="6.42578125" customWidth="1"/>
-    <col min="13313" max="13313" width="4.85546875" customWidth="1"/>
-    <col min="13314" max="13314" width="7.5703125" customWidth="1"/>
-    <col min="13315" max="13315" width="0" hidden="1" customWidth="1"/>
-    <col min="13316" max="13316" width="7.140625" customWidth="1"/>
-    <col min="13317" max="13317" width="0" hidden="1" customWidth="1"/>
-    <col min="13318" max="13318" width="6.85546875" customWidth="1"/>
-    <col min="13319" max="13319" width="9.28515625" customWidth="1"/>
-    <col min="13320" max="13320" width="5.85546875" customWidth="1"/>
-    <col min="13321" max="13321" width="0" hidden="1" customWidth="1"/>
-    <col min="13322" max="13322" width="10" customWidth="1"/>
-    <col min="13323" max="13328" width="0" hidden="1" customWidth="1"/>
-    <col min="13550" max="13550" width="4.140625" customWidth="1"/>
-    <col min="13551" max="13551" width="15.5703125" customWidth="1"/>
-    <col min="13552" max="13552" width="7.28515625" customWidth="1"/>
-    <col min="13553" max="13553" width="4.85546875" customWidth="1"/>
-    <col min="13554" max="13554" width="4.42578125" customWidth="1"/>
-    <col min="13555" max="13560" width="0" hidden="1" customWidth="1"/>
-    <col min="13561" max="13561" width="9" customWidth="1"/>
-    <col min="13562" max="13562" width="4.85546875" customWidth="1"/>
-    <col min="13563" max="13564" width="0" hidden="1" customWidth="1"/>
-    <col min="13565" max="13566" width="4.85546875" customWidth="1"/>
-    <col min="13567" max="13567" width="6.140625" customWidth="1"/>
-    <col min="13568" max="13568" width="6.42578125" customWidth="1"/>
-    <col min="13569" max="13569" width="4.85546875" customWidth="1"/>
-    <col min="13570" max="13570" width="7.5703125" customWidth="1"/>
-    <col min="13571" max="13571" width="0" hidden="1" customWidth="1"/>
-    <col min="13572" max="13572" width="7.140625" customWidth="1"/>
-    <col min="13573" max="13573" width="0" hidden="1" customWidth="1"/>
-    <col min="13574" max="13574" width="6.85546875" customWidth="1"/>
-    <col min="13575" max="13575" width="9.28515625" customWidth="1"/>
-    <col min="13576" max="13576" width="5.85546875" customWidth="1"/>
-    <col min="13577" max="13577" width="0" hidden="1" customWidth="1"/>
-    <col min="13578" max="13578" width="10" customWidth="1"/>
-    <col min="13579" max="13584" width="0" hidden="1" customWidth="1"/>
-    <col min="13806" max="13806" width="4.140625" customWidth="1"/>
-    <col min="13807" max="13807" width="15.5703125" customWidth="1"/>
-    <col min="13808" max="13808" width="7.28515625" customWidth="1"/>
-    <col min="13809" max="13809" width="4.85546875" customWidth="1"/>
-    <col min="13810" max="13810" width="4.42578125" customWidth="1"/>
-    <col min="13811" max="13816" width="0" hidden="1" customWidth="1"/>
-    <col min="13817" max="13817" width="9" customWidth="1"/>
-    <col min="13818" max="13818" width="4.85546875" customWidth="1"/>
-    <col min="13819" max="13820" width="0" hidden="1" customWidth="1"/>
-    <col min="13821" max="13822" width="4.85546875" customWidth="1"/>
-    <col min="13823" max="13823" width="6.140625" customWidth="1"/>
-    <col min="13824" max="13824" width="6.42578125" customWidth="1"/>
-    <col min="13825" max="13825" width="4.85546875" customWidth="1"/>
-    <col min="13826" max="13826" width="7.5703125" customWidth="1"/>
-    <col min="13827" max="13827" width="0" hidden="1" customWidth="1"/>
-    <col min="13828" max="13828" width="7.140625" customWidth="1"/>
-    <col min="13829" max="13829" width="0" hidden="1" customWidth="1"/>
-    <col min="13830" max="13830" width="6.85546875" customWidth="1"/>
-    <col min="13831" max="13831" width="9.28515625" customWidth="1"/>
-    <col min="13832" max="13832" width="5.85546875" customWidth="1"/>
-    <col min="13833" max="13833" width="0" hidden="1" customWidth="1"/>
-    <col min="13834" max="13834" width="10" customWidth="1"/>
-    <col min="13835" max="13840" width="0" hidden="1" customWidth="1"/>
-    <col min="14062" max="14062" width="4.140625" customWidth="1"/>
-    <col min="14063" max="14063" width="15.5703125" customWidth="1"/>
-    <col min="14064" max="14064" width="7.28515625" customWidth="1"/>
-    <col min="14065" max="14065" width="4.85546875" customWidth="1"/>
-    <col min="14066" max="14066" width="4.42578125" customWidth="1"/>
-    <col min="14067" max="14072" width="0" hidden="1" customWidth="1"/>
-    <col min="14073" max="14073" width="9" customWidth="1"/>
-    <col min="14074" max="14074" width="4.85546875" customWidth="1"/>
-    <col min="14075" max="14076" width="0" hidden="1" customWidth="1"/>
-    <col min="14077" max="14078" width="4.85546875" customWidth="1"/>
-    <col min="14079" max="14079" width="6.140625" customWidth="1"/>
-    <col min="14080" max="14080" width="6.42578125" customWidth="1"/>
-    <col min="14081" max="14081" width="4.85546875" customWidth="1"/>
-    <col min="14082" max="14082" width="7.5703125" customWidth="1"/>
-    <col min="14083" max="14083" width="0" hidden="1" customWidth="1"/>
-    <col min="14084" max="14084" width="7.140625" customWidth="1"/>
-    <col min="14085" max="14085" width="0" hidden="1" customWidth="1"/>
-    <col min="14086" max="14086" width="6.85546875" customWidth="1"/>
-    <col min="14087" max="14087" width="9.28515625" customWidth="1"/>
-    <col min="14088" max="14088" width="5.85546875" customWidth="1"/>
-    <col min="14089" max="14089" width="0" hidden="1" customWidth="1"/>
-    <col min="14090" max="14090" width="10" customWidth="1"/>
-    <col min="14091" max="14096" width="0" hidden="1" customWidth="1"/>
-    <col min="14318" max="14318" width="4.140625" customWidth="1"/>
-    <col min="14319" max="14319" width="15.5703125" customWidth="1"/>
-    <col min="14320" max="14320" width="7.28515625" customWidth="1"/>
-    <col min="14321" max="14321" width="4.85546875" customWidth="1"/>
-    <col min="14322" max="14322" width="4.42578125" customWidth="1"/>
-    <col min="14323" max="14328" width="0" hidden="1" customWidth="1"/>
-    <col min="14329" max="14329" width="9" customWidth="1"/>
-    <col min="14330" max="14330" width="4.85546875" customWidth="1"/>
-    <col min="14331" max="14332" width="0" hidden="1" customWidth="1"/>
-    <col min="14333" max="14334" width="4.85546875" customWidth="1"/>
-    <col min="14335" max="14335" width="6.140625" customWidth="1"/>
-    <col min="14336" max="14336" width="6.42578125" customWidth="1"/>
-    <col min="14337" max="14337" width="4.85546875" customWidth="1"/>
-    <col min="14338" max="14338" width="7.5703125" customWidth="1"/>
-    <col min="14339" max="14339" width="0" hidden="1" customWidth="1"/>
-    <col min="14340" max="14340" width="7.140625" customWidth="1"/>
-    <col min="14341" max="14341" width="0" hidden="1" customWidth="1"/>
-    <col min="14342" max="14342" width="6.85546875" customWidth="1"/>
-    <col min="14343" max="14343" width="9.28515625" customWidth="1"/>
-    <col min="14344" max="14344" width="5.85546875" customWidth="1"/>
-    <col min="14345" max="14345" width="0" hidden="1" customWidth="1"/>
-    <col min="14346" max="14346" width="10" customWidth="1"/>
-    <col min="14347" max="14352" width="0" hidden="1" customWidth="1"/>
-    <col min="14574" max="14574" width="4.140625" customWidth="1"/>
-    <col min="14575" max="14575" width="15.5703125" customWidth="1"/>
-    <col min="14576" max="14576" width="7.28515625" customWidth="1"/>
-    <col min="14577" max="14577" width="4.85546875" customWidth="1"/>
-    <col min="14578" max="14578" width="4.42578125" customWidth="1"/>
-    <col min="14579" max="14584" width="0" hidden="1" customWidth="1"/>
-    <col min="14585" max="14585" width="9" customWidth="1"/>
-    <col min="14586" max="14586" width="4.85546875" customWidth="1"/>
-    <col min="14587" max="14588" width="0" hidden="1" customWidth="1"/>
-    <col min="14589" max="14590" width="4.85546875" customWidth="1"/>
-    <col min="14591" max="14591" width="6.140625" customWidth="1"/>
-    <col min="14592" max="14592" width="6.42578125" customWidth="1"/>
-    <col min="14593" max="14593" width="4.85546875" customWidth="1"/>
-    <col min="14594" max="14594" width="7.5703125" customWidth="1"/>
-    <col min="14595" max="14595" width="0" hidden="1" customWidth="1"/>
-    <col min="14596" max="14596" width="7.140625" customWidth="1"/>
-    <col min="14597" max="14597" width="0" hidden="1" customWidth="1"/>
-    <col min="14598" max="14598" width="6.85546875" customWidth="1"/>
-    <col min="14599" max="14599" width="9.28515625" customWidth="1"/>
-    <col min="14600" max="14600" width="5.85546875" customWidth="1"/>
-    <col min="14601" max="14601" width="0" hidden="1" customWidth="1"/>
-    <col min="14602" max="14602" width="10" customWidth="1"/>
-    <col min="14603" max="14608" width="0" hidden="1" customWidth="1"/>
-    <col min="14830" max="14830" width="4.140625" customWidth="1"/>
-    <col min="14831" max="14831" width="15.5703125" customWidth="1"/>
-    <col min="14832" max="14832" width="7.28515625" customWidth="1"/>
-    <col min="14833" max="14833" width="4.85546875" customWidth="1"/>
-    <col min="14834" max="14834" width="4.42578125" customWidth="1"/>
-    <col min="14835" max="14840" width="0" hidden="1" customWidth="1"/>
-    <col min="14841" max="14841" width="9" customWidth="1"/>
-    <col min="14842" max="14842" width="4.85546875" customWidth="1"/>
-    <col min="14843" max="14844" width="0" hidden="1" customWidth="1"/>
-    <col min="14845" max="14846" width="4.85546875" customWidth="1"/>
-    <col min="14847" max="14847" width="6.140625" customWidth="1"/>
-    <col min="14848" max="14848" width="6.42578125" customWidth="1"/>
-    <col min="14849" max="14849" width="4.85546875" customWidth="1"/>
-    <col min="14850" max="14850" width="7.5703125" customWidth="1"/>
-    <col min="14851" max="14851" width="0" hidden="1" customWidth="1"/>
-    <col min="14852" max="14852" width="7.140625" customWidth="1"/>
-    <col min="14853" max="14853" width="0" hidden="1" customWidth="1"/>
-    <col min="14854" max="14854" width="6.85546875" customWidth="1"/>
-    <col min="14855" max="14855" width="9.28515625" customWidth="1"/>
-    <col min="14856" max="14856" width="5.85546875" customWidth="1"/>
-    <col min="14857" max="14857" width="0" hidden="1" customWidth="1"/>
-    <col min="14858" max="14858" width="10" customWidth="1"/>
-    <col min="14859" max="14864" width="0" hidden="1" customWidth="1"/>
-    <col min="15086" max="15086" width="4.140625" customWidth="1"/>
-    <col min="15087" max="15087" width="15.5703125" customWidth="1"/>
-    <col min="15088" max="15088" width="7.28515625" customWidth="1"/>
-    <col min="15089" max="15089" width="4.85546875" customWidth="1"/>
-    <col min="15090" max="15090" width="4.42578125" customWidth="1"/>
-    <col min="15091" max="15096" width="0" hidden="1" customWidth="1"/>
-    <col min="15097" max="15097" width="9" customWidth="1"/>
-    <col min="15098" max="15098" width="4.85546875" customWidth="1"/>
-    <col min="15099" max="15100" width="0" hidden="1" customWidth="1"/>
-    <col min="15101" max="15102" width="4.85546875" customWidth="1"/>
-    <col min="15103" max="15103" width="6.140625" customWidth="1"/>
-    <col min="15104" max="15104" width="6.42578125" customWidth="1"/>
-    <col min="15105" max="15105" width="4.85546875" customWidth="1"/>
-    <col min="15106" max="15106" width="7.5703125" customWidth="1"/>
-    <col min="15107" max="15107" width="0" hidden="1" customWidth="1"/>
-    <col min="15108" max="15108" width="7.140625" customWidth="1"/>
-    <col min="15109" max="15109" width="0" hidden="1" customWidth="1"/>
-    <col min="15110" max="15110" width="6.85546875" customWidth="1"/>
-    <col min="15111" max="15111" width="9.28515625" customWidth="1"/>
-    <col min="15112" max="15112" width="5.85546875" customWidth="1"/>
-    <col min="15113" max="15113" width="0" hidden="1" customWidth="1"/>
-    <col min="15114" max="15114" width="10" customWidth="1"/>
-    <col min="15115" max="15120" width="0" hidden="1" customWidth="1"/>
-    <col min="15342" max="15342" width="4.140625" customWidth="1"/>
-    <col min="15343" max="15343" width="15.5703125" customWidth="1"/>
-    <col min="15344" max="15344" width="7.28515625" customWidth="1"/>
-    <col min="15345" max="15345" width="4.85546875" customWidth="1"/>
-    <col min="15346" max="15346" width="4.42578125" customWidth="1"/>
-    <col min="15347" max="15352" width="0" hidden="1" customWidth="1"/>
-    <col min="15353" max="15353" width="9" customWidth="1"/>
-    <col min="15354" max="15354" width="4.85546875" customWidth="1"/>
-    <col min="15355" max="15356" width="0" hidden="1" customWidth="1"/>
-    <col min="15357" max="15358" width="4.85546875" customWidth="1"/>
-    <col min="15359" max="15359" width="6.140625" customWidth="1"/>
-    <col min="15360" max="15360" width="6.42578125" customWidth="1"/>
-    <col min="15361" max="15361" width="4.85546875" customWidth="1"/>
-    <col min="15362" max="15362" width="7.5703125" customWidth="1"/>
-    <col min="15363" max="15363" width="0" hidden="1" customWidth="1"/>
-    <col min="15364" max="15364" width="7.140625" customWidth="1"/>
-    <col min="15365" max="15365" width="0" hidden="1" customWidth="1"/>
-    <col min="15366" max="15366" width="6.85546875" customWidth="1"/>
-    <col min="15367" max="15367" width="9.28515625" customWidth="1"/>
-    <col min="15368" max="15368" width="5.85546875" customWidth="1"/>
-    <col min="15369" max="15369" width="0" hidden="1" customWidth="1"/>
-    <col min="15370" max="15370" width="10" customWidth="1"/>
-    <col min="15371" max="15376" width="0" hidden="1" customWidth="1"/>
-    <col min="15598" max="15598" width="4.140625" customWidth="1"/>
-    <col min="15599" max="15599" width="15.5703125" customWidth="1"/>
-    <col min="15600" max="15600" width="7.28515625" customWidth="1"/>
-    <col min="15601" max="15601" width="4.85546875" customWidth="1"/>
-    <col min="15602" max="15602" width="4.42578125" customWidth="1"/>
-    <col min="15603" max="15608" width="0" hidden="1" customWidth="1"/>
-    <col min="15609" max="15609" width="9" customWidth="1"/>
-    <col min="15610" max="15610" width="4.85546875" customWidth="1"/>
-    <col min="15611" max="15612" width="0" hidden="1" customWidth="1"/>
-    <col min="15613" max="15614" width="4.85546875" customWidth="1"/>
-    <col min="15615" max="15615" width="6.140625" customWidth="1"/>
-    <col min="15616" max="15616" width="6.42578125" customWidth="1"/>
-    <col min="15617" max="15617" width="4.85546875" customWidth="1"/>
-    <col min="15618" max="15618" width="7.5703125" customWidth="1"/>
-    <col min="15619" max="15619" width="0" hidden="1" customWidth="1"/>
-    <col min="15620" max="15620" width="7.140625" customWidth="1"/>
-    <col min="15621" max="15621" width="0" hidden="1" customWidth="1"/>
-    <col min="15622" max="15622" width="6.85546875" customWidth="1"/>
-    <col min="15623" max="15623" width="9.28515625" customWidth="1"/>
-    <col min="15624" max="15624" width="5.85546875" customWidth="1"/>
-    <col min="15625" max="15625" width="0" hidden="1" customWidth="1"/>
-    <col min="15626" max="15626" width="10" customWidth="1"/>
-    <col min="15627" max="15632" width="0" hidden="1" customWidth="1"/>
-    <col min="15854" max="15854" width="4.140625" customWidth="1"/>
-    <col min="15855" max="15855" width="15.5703125" customWidth="1"/>
-    <col min="15856" max="15856" width="7.28515625" customWidth="1"/>
-    <col min="15857" max="15857" width="4.85546875" customWidth="1"/>
-    <col min="15858" max="15858" width="4.42578125" customWidth="1"/>
-    <col min="15859" max="15864" width="0" hidden="1" customWidth="1"/>
-    <col min="15865" max="15865" width="9" customWidth="1"/>
-    <col min="15866" max="15866" width="4.85546875" customWidth="1"/>
-    <col min="15867" max="15868" width="0" hidden="1" customWidth="1"/>
-    <col min="15869" max="15870" width="4.85546875" customWidth="1"/>
-    <col min="15871" max="15871" width="6.140625" customWidth="1"/>
-    <col min="15872" max="15872" width="6.42578125" customWidth="1"/>
-    <col min="15873" max="15873" width="4.85546875" customWidth="1"/>
-    <col min="15874" max="15874" width="7.5703125" customWidth="1"/>
-    <col min="15875" max="15875" width="0" hidden="1" customWidth="1"/>
-    <col min="15876" max="15876" width="7.140625" customWidth="1"/>
-    <col min="15877" max="15877" width="0" hidden="1" customWidth="1"/>
-    <col min="15878" max="15878" width="6.85546875" customWidth="1"/>
-    <col min="15879" max="15879" width="9.28515625" customWidth="1"/>
-    <col min="15880" max="15880" width="5.85546875" customWidth="1"/>
-    <col min="15881" max="15881" width="0" hidden="1" customWidth="1"/>
-    <col min="15882" max="15882" width="10" customWidth="1"/>
-    <col min="15883" max="15888" width="0" hidden="1" customWidth="1"/>
-    <col min="16110" max="16110" width="4.140625" customWidth="1"/>
-    <col min="16111" max="16111" width="15.5703125" customWidth="1"/>
-    <col min="16112" max="16112" width="7.28515625" customWidth="1"/>
-    <col min="16113" max="16113" width="4.85546875" customWidth="1"/>
-    <col min="16114" max="16114" width="4.42578125" customWidth="1"/>
-    <col min="16115" max="16120" width="0" hidden="1" customWidth="1"/>
-    <col min="16121" max="16121" width="9" customWidth="1"/>
-    <col min="16122" max="16122" width="4.85546875" customWidth="1"/>
-    <col min="16123" max="16124" width="0" hidden="1" customWidth="1"/>
-    <col min="16125" max="16126" width="4.85546875" customWidth="1"/>
-    <col min="16127" max="16127" width="6.140625" customWidth="1"/>
-    <col min="16128" max="16128" width="6.42578125" customWidth="1"/>
-    <col min="16129" max="16129" width="4.85546875" customWidth="1"/>
-    <col min="16130" max="16130" width="7.5703125" customWidth="1"/>
-    <col min="16131" max="16131" width="0" hidden="1" customWidth="1"/>
-    <col min="16132" max="16132" width="7.140625" customWidth="1"/>
-    <col min="16133" max="16133" width="0" hidden="1" customWidth="1"/>
-    <col min="16134" max="16134" width="6.85546875" customWidth="1"/>
-    <col min="16135" max="16135" width="9.28515625" customWidth="1"/>
-    <col min="16136" max="16136" width="5.85546875" customWidth="1"/>
-    <col min="16137" max="16137" width="0" hidden="1" customWidth="1"/>
-    <col min="16138" max="16138" width="10" customWidth="1"/>
-    <col min="16139" max="16144" width="0" hidden="1" customWidth="1"/>
-    <col min="16377" max="16384" width="9.140625" customWidth="1"/>
+    <col min="12" max="13" width="8" style="45" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="45" customWidth="1"/>
+    <col min="15" max="15" width="7.42578125" style="45" customWidth="1"/>
+    <col min="16" max="16" width="6.140625" style="45" customWidth="1"/>
+    <col min="17" max="17" width="7" style="50" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" style="45" customWidth="1"/>
+    <col min="19" max="20" width="8.5703125" style="54" customWidth="1"/>
+    <col min="21" max="21" width="8.42578125" style="54" customWidth="1"/>
+    <col min="22" max="22" width="7.42578125" style="54" customWidth="1"/>
+    <col min="23" max="23" width="7.28515625" style="54" customWidth="1"/>
+    <col min="24" max="24" width="9.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.140625" style="57" customWidth="1"/>
+    <col min="26" max="26" width="11.140625" style="45" customWidth="1"/>
+    <col min="27" max="28" width="11.140625" style="45" bestFit="1" customWidth="1"/>
+    <col min="29" max="238" width="9.140625" style="45"/>
+    <col min="239" max="239" width="4.140625" style="45" customWidth="1"/>
+    <col min="240" max="240" width="15.5703125" style="45" customWidth="1"/>
+    <col min="241" max="241" width="7.28515625" style="45" customWidth="1"/>
+    <col min="242" max="242" width="4.85546875" style="45" customWidth="1"/>
+    <col min="243" max="243" width="4.42578125" style="45" customWidth="1"/>
+    <col min="244" max="249" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="250" max="250" width="9" style="45" customWidth="1"/>
+    <col min="251" max="251" width="4.85546875" style="45" customWidth="1"/>
+    <col min="252" max="253" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="254" max="255" width="4.85546875" style="45" customWidth="1"/>
+    <col min="256" max="256" width="6.140625" style="45" customWidth="1"/>
+    <col min="257" max="257" width="6.42578125" style="45" customWidth="1"/>
+    <col min="258" max="258" width="4.85546875" style="45" customWidth="1"/>
+    <col min="259" max="259" width="7.5703125" style="45" customWidth="1"/>
+    <col min="260" max="260" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="261" max="261" width="7.140625" style="45" customWidth="1"/>
+    <col min="262" max="262" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="263" max="263" width="6.85546875" style="45" customWidth="1"/>
+    <col min="264" max="264" width="9.28515625" style="45" customWidth="1"/>
+    <col min="265" max="265" width="5.85546875" style="45" customWidth="1"/>
+    <col min="266" max="266" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="267" max="267" width="10" style="45" customWidth="1"/>
+    <col min="268" max="273" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="274" max="494" width="9.140625" style="45"/>
+    <col min="495" max="495" width="4.140625" style="45" customWidth="1"/>
+    <col min="496" max="496" width="15.5703125" style="45" customWidth="1"/>
+    <col min="497" max="497" width="7.28515625" style="45" customWidth="1"/>
+    <col min="498" max="498" width="4.85546875" style="45" customWidth="1"/>
+    <col min="499" max="499" width="4.42578125" style="45" customWidth="1"/>
+    <col min="500" max="505" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="506" max="506" width="9" style="45" customWidth="1"/>
+    <col min="507" max="507" width="4.85546875" style="45" customWidth="1"/>
+    <col min="508" max="509" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="510" max="511" width="4.85546875" style="45" customWidth="1"/>
+    <col min="512" max="512" width="6.140625" style="45" customWidth="1"/>
+    <col min="513" max="513" width="6.42578125" style="45" customWidth="1"/>
+    <col min="514" max="514" width="4.85546875" style="45" customWidth="1"/>
+    <col min="515" max="515" width="7.5703125" style="45" customWidth="1"/>
+    <col min="516" max="516" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="517" max="517" width="7.140625" style="45" customWidth="1"/>
+    <col min="518" max="518" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="519" max="519" width="6.85546875" style="45" customWidth="1"/>
+    <col min="520" max="520" width="9.28515625" style="45" customWidth="1"/>
+    <col min="521" max="521" width="5.85546875" style="45" customWidth="1"/>
+    <col min="522" max="522" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="523" max="523" width="10" style="45" customWidth="1"/>
+    <col min="524" max="529" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="530" max="750" width="9.140625" style="45"/>
+    <col min="751" max="751" width="4.140625" style="45" customWidth="1"/>
+    <col min="752" max="752" width="15.5703125" style="45" customWidth="1"/>
+    <col min="753" max="753" width="7.28515625" style="45" customWidth="1"/>
+    <col min="754" max="754" width="4.85546875" style="45" customWidth="1"/>
+    <col min="755" max="755" width="4.42578125" style="45" customWidth="1"/>
+    <col min="756" max="761" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="762" max="762" width="9" style="45" customWidth="1"/>
+    <col min="763" max="763" width="4.85546875" style="45" customWidth="1"/>
+    <col min="764" max="765" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="766" max="767" width="4.85546875" style="45" customWidth="1"/>
+    <col min="768" max="768" width="6.140625" style="45" customWidth="1"/>
+    <col min="769" max="769" width="6.42578125" style="45" customWidth="1"/>
+    <col min="770" max="770" width="4.85546875" style="45" customWidth="1"/>
+    <col min="771" max="771" width="7.5703125" style="45" customWidth="1"/>
+    <col min="772" max="772" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="773" max="773" width="7.140625" style="45" customWidth="1"/>
+    <col min="774" max="774" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="775" max="775" width="6.85546875" style="45" customWidth="1"/>
+    <col min="776" max="776" width="9.28515625" style="45" customWidth="1"/>
+    <col min="777" max="777" width="5.85546875" style="45" customWidth="1"/>
+    <col min="778" max="778" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="779" max="779" width="10" style="45" customWidth="1"/>
+    <col min="780" max="785" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="786" max="1006" width="9.140625" style="45"/>
+    <col min="1007" max="1007" width="4.140625" style="45" customWidth="1"/>
+    <col min="1008" max="1008" width="15.5703125" style="45" customWidth="1"/>
+    <col min="1009" max="1009" width="7.28515625" style="45" customWidth="1"/>
+    <col min="1010" max="1010" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1011" max="1011" width="4.42578125" style="45" customWidth="1"/>
+    <col min="1012" max="1017" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1018" max="1018" width="9" style="45" customWidth="1"/>
+    <col min="1019" max="1019" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1020" max="1021" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1022" max="1023" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1024" max="1024" width="6.140625" style="45" customWidth="1"/>
+    <col min="1025" max="1025" width="6.42578125" style="45" customWidth="1"/>
+    <col min="1026" max="1026" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1027" max="1027" width="7.5703125" style="45" customWidth="1"/>
+    <col min="1028" max="1028" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1029" max="1029" width="7.140625" style="45" customWidth="1"/>
+    <col min="1030" max="1030" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1031" max="1031" width="6.85546875" style="45" customWidth="1"/>
+    <col min="1032" max="1032" width="9.28515625" style="45" customWidth="1"/>
+    <col min="1033" max="1033" width="5.85546875" style="45" customWidth="1"/>
+    <col min="1034" max="1034" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1035" max="1035" width="10" style="45" customWidth="1"/>
+    <col min="1036" max="1041" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1042" max="1262" width="9.140625" style="45"/>
+    <col min="1263" max="1263" width="4.140625" style="45" customWidth="1"/>
+    <col min="1264" max="1264" width="15.5703125" style="45" customWidth="1"/>
+    <col min="1265" max="1265" width="7.28515625" style="45" customWidth="1"/>
+    <col min="1266" max="1266" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1267" max="1267" width="4.42578125" style="45" customWidth="1"/>
+    <col min="1268" max="1273" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1274" max="1274" width="9" style="45" customWidth="1"/>
+    <col min="1275" max="1275" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1276" max="1277" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1278" max="1279" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1280" max="1280" width="6.140625" style="45" customWidth="1"/>
+    <col min="1281" max="1281" width="6.42578125" style="45" customWidth="1"/>
+    <col min="1282" max="1282" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1283" max="1283" width="7.5703125" style="45" customWidth="1"/>
+    <col min="1284" max="1284" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1285" max="1285" width="7.140625" style="45" customWidth="1"/>
+    <col min="1286" max="1286" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1287" max="1287" width="6.85546875" style="45" customWidth="1"/>
+    <col min="1288" max="1288" width="9.28515625" style="45" customWidth="1"/>
+    <col min="1289" max="1289" width="5.85546875" style="45" customWidth="1"/>
+    <col min="1290" max="1290" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1291" max="1291" width="10" style="45" customWidth="1"/>
+    <col min="1292" max="1297" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1298" max="1518" width="9.140625" style="45"/>
+    <col min="1519" max="1519" width="4.140625" style="45" customWidth="1"/>
+    <col min="1520" max="1520" width="15.5703125" style="45" customWidth="1"/>
+    <col min="1521" max="1521" width="7.28515625" style="45" customWidth="1"/>
+    <col min="1522" max="1522" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1523" max="1523" width="4.42578125" style="45" customWidth="1"/>
+    <col min="1524" max="1529" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1530" max="1530" width="9" style="45" customWidth="1"/>
+    <col min="1531" max="1531" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1532" max="1533" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1534" max="1535" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1536" max="1536" width="6.140625" style="45" customWidth="1"/>
+    <col min="1537" max="1537" width="6.42578125" style="45" customWidth="1"/>
+    <col min="1538" max="1538" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1539" max="1539" width="7.5703125" style="45" customWidth="1"/>
+    <col min="1540" max="1540" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1541" max="1541" width="7.140625" style="45" customWidth="1"/>
+    <col min="1542" max="1542" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1543" max="1543" width="6.85546875" style="45" customWidth="1"/>
+    <col min="1544" max="1544" width="9.28515625" style="45" customWidth="1"/>
+    <col min="1545" max="1545" width="5.85546875" style="45" customWidth="1"/>
+    <col min="1546" max="1546" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1547" max="1547" width="10" style="45" customWidth="1"/>
+    <col min="1548" max="1553" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1554" max="1774" width="9.140625" style="45"/>
+    <col min="1775" max="1775" width="4.140625" style="45" customWidth="1"/>
+    <col min="1776" max="1776" width="15.5703125" style="45" customWidth="1"/>
+    <col min="1777" max="1777" width="7.28515625" style="45" customWidth="1"/>
+    <col min="1778" max="1778" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1779" max="1779" width="4.42578125" style="45" customWidth="1"/>
+    <col min="1780" max="1785" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1786" max="1786" width="9" style="45" customWidth="1"/>
+    <col min="1787" max="1787" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1788" max="1789" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1790" max="1791" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1792" max="1792" width="6.140625" style="45" customWidth="1"/>
+    <col min="1793" max="1793" width="6.42578125" style="45" customWidth="1"/>
+    <col min="1794" max="1794" width="4.85546875" style="45" customWidth="1"/>
+    <col min="1795" max="1795" width="7.5703125" style="45" customWidth="1"/>
+    <col min="1796" max="1796" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1797" max="1797" width="7.140625" style="45" customWidth="1"/>
+    <col min="1798" max="1798" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1799" max="1799" width="6.85546875" style="45" customWidth="1"/>
+    <col min="1800" max="1800" width="9.28515625" style="45" customWidth="1"/>
+    <col min="1801" max="1801" width="5.85546875" style="45" customWidth="1"/>
+    <col min="1802" max="1802" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1803" max="1803" width="10" style="45" customWidth="1"/>
+    <col min="1804" max="1809" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="1810" max="2030" width="9.140625" style="45"/>
+    <col min="2031" max="2031" width="4.140625" style="45" customWidth="1"/>
+    <col min="2032" max="2032" width="15.5703125" style="45" customWidth="1"/>
+    <col min="2033" max="2033" width="7.28515625" style="45" customWidth="1"/>
+    <col min="2034" max="2034" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2035" max="2035" width="4.42578125" style="45" customWidth="1"/>
+    <col min="2036" max="2041" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2042" max="2042" width="9" style="45" customWidth="1"/>
+    <col min="2043" max="2043" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2044" max="2045" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2046" max="2047" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2048" max="2048" width="6.140625" style="45" customWidth="1"/>
+    <col min="2049" max="2049" width="6.42578125" style="45" customWidth="1"/>
+    <col min="2050" max="2050" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2051" max="2051" width="7.5703125" style="45" customWidth="1"/>
+    <col min="2052" max="2052" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2053" max="2053" width="7.140625" style="45" customWidth="1"/>
+    <col min="2054" max="2054" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2055" max="2055" width="6.85546875" style="45" customWidth="1"/>
+    <col min="2056" max="2056" width="9.28515625" style="45" customWidth="1"/>
+    <col min="2057" max="2057" width="5.85546875" style="45" customWidth="1"/>
+    <col min="2058" max="2058" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2059" max="2059" width="10" style="45" customWidth="1"/>
+    <col min="2060" max="2065" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2066" max="2286" width="9.140625" style="45"/>
+    <col min="2287" max="2287" width="4.140625" style="45" customWidth="1"/>
+    <col min="2288" max="2288" width="15.5703125" style="45" customWidth="1"/>
+    <col min="2289" max="2289" width="7.28515625" style="45" customWidth="1"/>
+    <col min="2290" max="2290" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2291" max="2291" width="4.42578125" style="45" customWidth="1"/>
+    <col min="2292" max="2297" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2298" max="2298" width="9" style="45" customWidth="1"/>
+    <col min="2299" max="2299" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2300" max="2301" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2302" max="2303" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2304" max="2304" width="6.140625" style="45" customWidth="1"/>
+    <col min="2305" max="2305" width="6.42578125" style="45" customWidth="1"/>
+    <col min="2306" max="2306" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2307" max="2307" width="7.5703125" style="45" customWidth="1"/>
+    <col min="2308" max="2308" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2309" max="2309" width="7.140625" style="45" customWidth="1"/>
+    <col min="2310" max="2310" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2311" max="2311" width="6.85546875" style="45" customWidth="1"/>
+    <col min="2312" max="2312" width="9.28515625" style="45" customWidth="1"/>
+    <col min="2313" max="2313" width="5.85546875" style="45" customWidth="1"/>
+    <col min="2314" max="2314" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2315" max="2315" width="10" style="45" customWidth="1"/>
+    <col min="2316" max="2321" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2322" max="2542" width="9.140625" style="45"/>
+    <col min="2543" max="2543" width="4.140625" style="45" customWidth="1"/>
+    <col min="2544" max="2544" width="15.5703125" style="45" customWidth="1"/>
+    <col min="2545" max="2545" width="7.28515625" style="45" customWidth="1"/>
+    <col min="2546" max="2546" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2547" max="2547" width="4.42578125" style="45" customWidth="1"/>
+    <col min="2548" max="2553" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2554" max="2554" width="9" style="45" customWidth="1"/>
+    <col min="2555" max="2555" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2556" max="2557" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2558" max="2559" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2560" max="2560" width="6.140625" style="45" customWidth="1"/>
+    <col min="2561" max="2561" width="6.42578125" style="45" customWidth="1"/>
+    <col min="2562" max="2562" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2563" max="2563" width="7.5703125" style="45" customWidth="1"/>
+    <col min="2564" max="2564" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2565" max="2565" width="7.140625" style="45" customWidth="1"/>
+    <col min="2566" max="2566" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2567" max="2567" width="6.85546875" style="45" customWidth="1"/>
+    <col min="2568" max="2568" width="9.28515625" style="45" customWidth="1"/>
+    <col min="2569" max="2569" width="5.85546875" style="45" customWidth="1"/>
+    <col min="2570" max="2570" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2571" max="2571" width="10" style="45" customWidth="1"/>
+    <col min="2572" max="2577" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2578" max="2798" width="9.140625" style="45"/>
+    <col min="2799" max="2799" width="4.140625" style="45" customWidth="1"/>
+    <col min="2800" max="2800" width="15.5703125" style="45" customWidth="1"/>
+    <col min="2801" max="2801" width="7.28515625" style="45" customWidth="1"/>
+    <col min="2802" max="2802" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2803" max="2803" width="4.42578125" style="45" customWidth="1"/>
+    <col min="2804" max="2809" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2810" max="2810" width="9" style="45" customWidth="1"/>
+    <col min="2811" max="2811" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2812" max="2813" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2814" max="2815" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2816" max="2816" width="6.140625" style="45" customWidth="1"/>
+    <col min="2817" max="2817" width="6.42578125" style="45" customWidth="1"/>
+    <col min="2818" max="2818" width="4.85546875" style="45" customWidth="1"/>
+    <col min="2819" max="2819" width="7.5703125" style="45" customWidth="1"/>
+    <col min="2820" max="2820" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2821" max="2821" width="7.140625" style="45" customWidth="1"/>
+    <col min="2822" max="2822" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2823" max="2823" width="6.85546875" style="45" customWidth="1"/>
+    <col min="2824" max="2824" width="9.28515625" style="45" customWidth="1"/>
+    <col min="2825" max="2825" width="5.85546875" style="45" customWidth="1"/>
+    <col min="2826" max="2826" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2827" max="2827" width="10" style="45" customWidth="1"/>
+    <col min="2828" max="2833" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="2834" max="3054" width="9.140625" style="45"/>
+    <col min="3055" max="3055" width="4.140625" style="45" customWidth="1"/>
+    <col min="3056" max="3056" width="15.5703125" style="45" customWidth="1"/>
+    <col min="3057" max="3057" width="7.28515625" style="45" customWidth="1"/>
+    <col min="3058" max="3058" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3059" max="3059" width="4.42578125" style="45" customWidth="1"/>
+    <col min="3060" max="3065" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3066" max="3066" width="9" style="45" customWidth="1"/>
+    <col min="3067" max="3067" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3068" max="3069" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3070" max="3071" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3072" max="3072" width="6.140625" style="45" customWidth="1"/>
+    <col min="3073" max="3073" width="6.42578125" style="45" customWidth="1"/>
+    <col min="3074" max="3074" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3075" max="3075" width="7.5703125" style="45" customWidth="1"/>
+    <col min="3076" max="3076" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3077" max="3077" width="7.140625" style="45" customWidth="1"/>
+    <col min="3078" max="3078" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3079" max="3079" width="6.85546875" style="45" customWidth="1"/>
+    <col min="3080" max="3080" width="9.28515625" style="45" customWidth="1"/>
+    <col min="3081" max="3081" width="5.85546875" style="45" customWidth="1"/>
+    <col min="3082" max="3082" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3083" max="3083" width="10" style="45" customWidth="1"/>
+    <col min="3084" max="3089" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3090" max="3310" width="9.140625" style="45"/>
+    <col min="3311" max="3311" width="4.140625" style="45" customWidth="1"/>
+    <col min="3312" max="3312" width="15.5703125" style="45" customWidth="1"/>
+    <col min="3313" max="3313" width="7.28515625" style="45" customWidth="1"/>
+    <col min="3314" max="3314" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3315" max="3315" width="4.42578125" style="45" customWidth="1"/>
+    <col min="3316" max="3321" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3322" max="3322" width="9" style="45" customWidth="1"/>
+    <col min="3323" max="3323" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3324" max="3325" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3326" max="3327" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3328" max="3328" width="6.140625" style="45" customWidth="1"/>
+    <col min="3329" max="3329" width="6.42578125" style="45" customWidth="1"/>
+    <col min="3330" max="3330" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3331" max="3331" width="7.5703125" style="45" customWidth="1"/>
+    <col min="3332" max="3332" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3333" max="3333" width="7.140625" style="45" customWidth="1"/>
+    <col min="3334" max="3334" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3335" max="3335" width="6.85546875" style="45" customWidth="1"/>
+    <col min="3336" max="3336" width="9.28515625" style="45" customWidth="1"/>
+    <col min="3337" max="3337" width="5.85546875" style="45" customWidth="1"/>
+    <col min="3338" max="3338" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3339" max="3339" width="10" style="45" customWidth="1"/>
+    <col min="3340" max="3345" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3346" max="3566" width="9.140625" style="45"/>
+    <col min="3567" max="3567" width="4.140625" style="45" customWidth="1"/>
+    <col min="3568" max="3568" width="15.5703125" style="45" customWidth="1"/>
+    <col min="3569" max="3569" width="7.28515625" style="45" customWidth="1"/>
+    <col min="3570" max="3570" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3571" max="3571" width="4.42578125" style="45" customWidth="1"/>
+    <col min="3572" max="3577" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3578" max="3578" width="9" style="45" customWidth="1"/>
+    <col min="3579" max="3579" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3580" max="3581" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3582" max="3583" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3584" max="3584" width="6.140625" style="45" customWidth="1"/>
+    <col min="3585" max="3585" width="6.42578125" style="45" customWidth="1"/>
+    <col min="3586" max="3586" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3587" max="3587" width="7.5703125" style="45" customWidth="1"/>
+    <col min="3588" max="3588" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3589" max="3589" width="7.140625" style="45" customWidth="1"/>
+    <col min="3590" max="3590" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3591" max="3591" width="6.85546875" style="45" customWidth="1"/>
+    <col min="3592" max="3592" width="9.28515625" style="45" customWidth="1"/>
+    <col min="3593" max="3593" width="5.85546875" style="45" customWidth="1"/>
+    <col min="3594" max="3594" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3595" max="3595" width="10" style="45" customWidth="1"/>
+    <col min="3596" max="3601" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3602" max="3822" width="9.140625" style="45"/>
+    <col min="3823" max="3823" width="4.140625" style="45" customWidth="1"/>
+    <col min="3824" max="3824" width="15.5703125" style="45" customWidth="1"/>
+    <col min="3825" max="3825" width="7.28515625" style="45" customWidth="1"/>
+    <col min="3826" max="3826" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3827" max="3827" width="4.42578125" style="45" customWidth="1"/>
+    <col min="3828" max="3833" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3834" max="3834" width="9" style="45" customWidth="1"/>
+    <col min="3835" max="3835" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3836" max="3837" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3838" max="3839" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3840" max="3840" width="6.140625" style="45" customWidth="1"/>
+    <col min="3841" max="3841" width="6.42578125" style="45" customWidth="1"/>
+    <col min="3842" max="3842" width="4.85546875" style="45" customWidth="1"/>
+    <col min="3843" max="3843" width="7.5703125" style="45" customWidth="1"/>
+    <col min="3844" max="3844" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3845" max="3845" width="7.140625" style="45" customWidth="1"/>
+    <col min="3846" max="3846" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3847" max="3847" width="6.85546875" style="45" customWidth="1"/>
+    <col min="3848" max="3848" width="9.28515625" style="45" customWidth="1"/>
+    <col min="3849" max="3849" width="5.85546875" style="45" customWidth="1"/>
+    <col min="3850" max="3850" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3851" max="3851" width="10" style="45" customWidth="1"/>
+    <col min="3852" max="3857" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="3858" max="4078" width="9.140625" style="45"/>
+    <col min="4079" max="4079" width="4.140625" style="45" customWidth="1"/>
+    <col min="4080" max="4080" width="15.5703125" style="45" customWidth="1"/>
+    <col min="4081" max="4081" width="7.28515625" style="45" customWidth="1"/>
+    <col min="4082" max="4082" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4083" max="4083" width="4.42578125" style="45" customWidth="1"/>
+    <col min="4084" max="4089" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4090" max="4090" width="9" style="45" customWidth="1"/>
+    <col min="4091" max="4091" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4092" max="4093" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4094" max="4095" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4096" max="4096" width="6.140625" style="45" customWidth="1"/>
+    <col min="4097" max="4097" width="6.42578125" style="45" customWidth="1"/>
+    <col min="4098" max="4098" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4099" max="4099" width="7.5703125" style="45" customWidth="1"/>
+    <col min="4100" max="4100" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4101" max="4101" width="7.140625" style="45" customWidth="1"/>
+    <col min="4102" max="4102" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4103" max="4103" width="6.85546875" style="45" customWidth="1"/>
+    <col min="4104" max="4104" width="9.28515625" style="45" customWidth="1"/>
+    <col min="4105" max="4105" width="5.85546875" style="45" customWidth="1"/>
+    <col min="4106" max="4106" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4107" max="4107" width="10" style="45" customWidth="1"/>
+    <col min="4108" max="4113" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4114" max="4334" width="9.140625" style="45"/>
+    <col min="4335" max="4335" width="4.140625" style="45" customWidth="1"/>
+    <col min="4336" max="4336" width="15.5703125" style="45" customWidth="1"/>
+    <col min="4337" max="4337" width="7.28515625" style="45" customWidth="1"/>
+    <col min="4338" max="4338" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4339" max="4339" width="4.42578125" style="45" customWidth="1"/>
+    <col min="4340" max="4345" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4346" max="4346" width="9" style="45" customWidth="1"/>
+    <col min="4347" max="4347" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4348" max="4349" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4350" max="4351" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4352" max="4352" width="6.140625" style="45" customWidth="1"/>
+    <col min="4353" max="4353" width="6.42578125" style="45" customWidth="1"/>
+    <col min="4354" max="4354" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4355" max="4355" width="7.5703125" style="45" customWidth="1"/>
+    <col min="4356" max="4356" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4357" max="4357" width="7.140625" style="45" customWidth="1"/>
+    <col min="4358" max="4358" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4359" max="4359" width="6.85546875" style="45" customWidth="1"/>
+    <col min="4360" max="4360" width="9.28515625" style="45" customWidth="1"/>
+    <col min="4361" max="4361" width="5.85546875" style="45" customWidth="1"/>
+    <col min="4362" max="4362" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4363" max="4363" width="10" style="45" customWidth="1"/>
+    <col min="4364" max="4369" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4370" max="4590" width="9.140625" style="45"/>
+    <col min="4591" max="4591" width="4.140625" style="45" customWidth="1"/>
+    <col min="4592" max="4592" width="15.5703125" style="45" customWidth="1"/>
+    <col min="4593" max="4593" width="7.28515625" style="45" customWidth="1"/>
+    <col min="4594" max="4594" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4595" max="4595" width="4.42578125" style="45" customWidth="1"/>
+    <col min="4596" max="4601" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4602" max="4602" width="9" style="45" customWidth="1"/>
+    <col min="4603" max="4603" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4604" max="4605" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4606" max="4607" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4608" max="4608" width="6.140625" style="45" customWidth="1"/>
+    <col min="4609" max="4609" width="6.42578125" style="45" customWidth="1"/>
+    <col min="4610" max="4610" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4611" max="4611" width="7.5703125" style="45" customWidth="1"/>
+    <col min="4612" max="4612" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4613" max="4613" width="7.140625" style="45" customWidth="1"/>
+    <col min="4614" max="4614" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4615" max="4615" width="6.85546875" style="45" customWidth="1"/>
+    <col min="4616" max="4616" width="9.28515625" style="45" customWidth="1"/>
+    <col min="4617" max="4617" width="5.85546875" style="45" customWidth="1"/>
+    <col min="4618" max="4618" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4619" max="4619" width="10" style="45" customWidth="1"/>
+    <col min="4620" max="4625" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4626" max="4846" width="9.140625" style="45"/>
+    <col min="4847" max="4847" width="4.140625" style="45" customWidth="1"/>
+    <col min="4848" max="4848" width="15.5703125" style="45" customWidth="1"/>
+    <col min="4849" max="4849" width="7.28515625" style="45" customWidth="1"/>
+    <col min="4850" max="4850" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4851" max="4851" width="4.42578125" style="45" customWidth="1"/>
+    <col min="4852" max="4857" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4858" max="4858" width="9" style="45" customWidth="1"/>
+    <col min="4859" max="4859" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4860" max="4861" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4862" max="4863" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4864" max="4864" width="6.140625" style="45" customWidth="1"/>
+    <col min="4865" max="4865" width="6.42578125" style="45" customWidth="1"/>
+    <col min="4866" max="4866" width="4.85546875" style="45" customWidth="1"/>
+    <col min="4867" max="4867" width="7.5703125" style="45" customWidth="1"/>
+    <col min="4868" max="4868" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4869" max="4869" width="7.140625" style="45" customWidth="1"/>
+    <col min="4870" max="4870" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4871" max="4871" width="6.85546875" style="45" customWidth="1"/>
+    <col min="4872" max="4872" width="9.28515625" style="45" customWidth="1"/>
+    <col min="4873" max="4873" width="5.85546875" style="45" customWidth="1"/>
+    <col min="4874" max="4874" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4875" max="4875" width="10" style="45" customWidth="1"/>
+    <col min="4876" max="4881" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="4882" max="5102" width="9.140625" style="45"/>
+    <col min="5103" max="5103" width="4.140625" style="45" customWidth="1"/>
+    <col min="5104" max="5104" width="15.5703125" style="45" customWidth="1"/>
+    <col min="5105" max="5105" width="7.28515625" style="45" customWidth="1"/>
+    <col min="5106" max="5106" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5107" max="5107" width="4.42578125" style="45" customWidth="1"/>
+    <col min="5108" max="5113" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5114" max="5114" width="9" style="45" customWidth="1"/>
+    <col min="5115" max="5115" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5116" max="5117" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5118" max="5119" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5120" max="5120" width="6.140625" style="45" customWidth="1"/>
+    <col min="5121" max="5121" width="6.42578125" style="45" customWidth="1"/>
+    <col min="5122" max="5122" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5123" max="5123" width="7.5703125" style="45" customWidth="1"/>
+    <col min="5124" max="5124" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5125" max="5125" width="7.140625" style="45" customWidth="1"/>
+    <col min="5126" max="5126" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5127" max="5127" width="6.85546875" style="45" customWidth="1"/>
+    <col min="5128" max="5128" width="9.28515625" style="45" customWidth="1"/>
+    <col min="5129" max="5129" width="5.85546875" style="45" customWidth="1"/>
+    <col min="5130" max="5130" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5131" max="5131" width="10" style="45" customWidth="1"/>
+    <col min="5132" max="5137" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5138" max="5358" width="9.140625" style="45"/>
+    <col min="5359" max="5359" width="4.140625" style="45" customWidth="1"/>
+    <col min="5360" max="5360" width="15.5703125" style="45" customWidth="1"/>
+    <col min="5361" max="5361" width="7.28515625" style="45" customWidth="1"/>
+    <col min="5362" max="5362" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5363" max="5363" width="4.42578125" style="45" customWidth="1"/>
+    <col min="5364" max="5369" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5370" max="5370" width="9" style="45" customWidth="1"/>
+    <col min="5371" max="5371" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5372" max="5373" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5374" max="5375" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5376" max="5376" width="6.140625" style="45" customWidth="1"/>
+    <col min="5377" max="5377" width="6.42578125" style="45" customWidth="1"/>
+    <col min="5378" max="5378" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5379" max="5379" width="7.5703125" style="45" customWidth="1"/>
+    <col min="5380" max="5380" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5381" max="5381" width="7.140625" style="45" customWidth="1"/>
+    <col min="5382" max="5382" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5383" max="5383" width="6.85546875" style="45" customWidth="1"/>
+    <col min="5384" max="5384" width="9.28515625" style="45" customWidth="1"/>
+    <col min="5385" max="5385" width="5.85546875" style="45" customWidth="1"/>
+    <col min="5386" max="5386" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5387" max="5387" width="10" style="45" customWidth="1"/>
+    <col min="5388" max="5393" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5394" max="5614" width="9.140625" style="45"/>
+    <col min="5615" max="5615" width="4.140625" style="45" customWidth="1"/>
+    <col min="5616" max="5616" width="15.5703125" style="45" customWidth="1"/>
+    <col min="5617" max="5617" width="7.28515625" style="45" customWidth="1"/>
+    <col min="5618" max="5618" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5619" max="5619" width="4.42578125" style="45" customWidth="1"/>
+    <col min="5620" max="5625" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5626" max="5626" width="9" style="45" customWidth="1"/>
+    <col min="5627" max="5627" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5628" max="5629" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5630" max="5631" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5632" max="5632" width="6.140625" style="45" customWidth="1"/>
+    <col min="5633" max="5633" width="6.42578125" style="45" customWidth="1"/>
+    <col min="5634" max="5634" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5635" max="5635" width="7.5703125" style="45" customWidth="1"/>
+    <col min="5636" max="5636" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5637" max="5637" width="7.140625" style="45" customWidth="1"/>
+    <col min="5638" max="5638" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5639" max="5639" width="6.85546875" style="45" customWidth="1"/>
+    <col min="5640" max="5640" width="9.28515625" style="45" customWidth="1"/>
+    <col min="5641" max="5641" width="5.85546875" style="45" customWidth="1"/>
+    <col min="5642" max="5642" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5643" max="5643" width="10" style="45" customWidth="1"/>
+    <col min="5644" max="5649" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5650" max="5870" width="9.140625" style="45"/>
+    <col min="5871" max="5871" width="4.140625" style="45" customWidth="1"/>
+    <col min="5872" max="5872" width="15.5703125" style="45" customWidth="1"/>
+    <col min="5873" max="5873" width="7.28515625" style="45" customWidth="1"/>
+    <col min="5874" max="5874" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5875" max="5875" width="4.42578125" style="45" customWidth="1"/>
+    <col min="5876" max="5881" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5882" max="5882" width="9" style="45" customWidth="1"/>
+    <col min="5883" max="5883" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5884" max="5885" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5886" max="5887" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5888" max="5888" width="6.140625" style="45" customWidth="1"/>
+    <col min="5889" max="5889" width="6.42578125" style="45" customWidth="1"/>
+    <col min="5890" max="5890" width="4.85546875" style="45" customWidth="1"/>
+    <col min="5891" max="5891" width="7.5703125" style="45" customWidth="1"/>
+    <col min="5892" max="5892" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5893" max="5893" width="7.140625" style="45" customWidth="1"/>
+    <col min="5894" max="5894" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5895" max="5895" width="6.85546875" style="45" customWidth="1"/>
+    <col min="5896" max="5896" width="9.28515625" style="45" customWidth="1"/>
+    <col min="5897" max="5897" width="5.85546875" style="45" customWidth="1"/>
+    <col min="5898" max="5898" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5899" max="5899" width="10" style="45" customWidth="1"/>
+    <col min="5900" max="5905" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="5906" max="6126" width="9.140625" style="45"/>
+    <col min="6127" max="6127" width="4.140625" style="45" customWidth="1"/>
+    <col min="6128" max="6128" width="15.5703125" style="45" customWidth="1"/>
+    <col min="6129" max="6129" width="7.28515625" style="45" customWidth="1"/>
+    <col min="6130" max="6130" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6131" max="6131" width="4.42578125" style="45" customWidth="1"/>
+    <col min="6132" max="6137" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6138" max="6138" width="9" style="45" customWidth="1"/>
+    <col min="6139" max="6139" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6140" max="6141" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6142" max="6143" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6144" max="6144" width="6.140625" style="45" customWidth="1"/>
+    <col min="6145" max="6145" width="6.42578125" style="45" customWidth="1"/>
+    <col min="6146" max="6146" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6147" max="6147" width="7.5703125" style="45" customWidth="1"/>
+    <col min="6148" max="6148" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6149" max="6149" width="7.140625" style="45" customWidth="1"/>
+    <col min="6150" max="6150" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6151" max="6151" width="6.85546875" style="45" customWidth="1"/>
+    <col min="6152" max="6152" width="9.28515625" style="45" customWidth="1"/>
+    <col min="6153" max="6153" width="5.85546875" style="45" customWidth="1"/>
+    <col min="6154" max="6154" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6155" max="6155" width="10" style="45" customWidth="1"/>
+    <col min="6156" max="6161" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6162" max="6382" width="9.140625" style="45"/>
+    <col min="6383" max="6383" width="4.140625" style="45" customWidth="1"/>
+    <col min="6384" max="6384" width="15.5703125" style="45" customWidth="1"/>
+    <col min="6385" max="6385" width="7.28515625" style="45" customWidth="1"/>
+    <col min="6386" max="6386" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6387" max="6387" width="4.42578125" style="45" customWidth="1"/>
+    <col min="6388" max="6393" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6394" max="6394" width="9" style="45" customWidth="1"/>
+    <col min="6395" max="6395" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6396" max="6397" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6398" max="6399" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6400" max="6400" width="6.140625" style="45" customWidth="1"/>
+    <col min="6401" max="6401" width="6.42578125" style="45" customWidth="1"/>
+    <col min="6402" max="6402" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6403" max="6403" width="7.5703125" style="45" customWidth="1"/>
+    <col min="6404" max="6404" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6405" max="6405" width="7.140625" style="45" customWidth="1"/>
+    <col min="6406" max="6406" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6407" max="6407" width="6.85546875" style="45" customWidth="1"/>
+    <col min="6408" max="6408" width="9.28515625" style="45" customWidth="1"/>
+    <col min="6409" max="6409" width="5.85546875" style="45" customWidth="1"/>
+    <col min="6410" max="6410" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6411" max="6411" width="10" style="45" customWidth="1"/>
+    <col min="6412" max="6417" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6418" max="6638" width="9.140625" style="45"/>
+    <col min="6639" max="6639" width="4.140625" style="45" customWidth="1"/>
+    <col min="6640" max="6640" width="15.5703125" style="45" customWidth="1"/>
+    <col min="6641" max="6641" width="7.28515625" style="45" customWidth="1"/>
+    <col min="6642" max="6642" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6643" max="6643" width="4.42578125" style="45" customWidth="1"/>
+    <col min="6644" max="6649" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6650" max="6650" width="9" style="45" customWidth="1"/>
+    <col min="6651" max="6651" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6652" max="6653" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6654" max="6655" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6656" max="6656" width="6.140625" style="45" customWidth="1"/>
+    <col min="6657" max="6657" width="6.42578125" style="45" customWidth="1"/>
+    <col min="6658" max="6658" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6659" max="6659" width="7.5703125" style="45" customWidth="1"/>
+    <col min="6660" max="6660" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6661" max="6661" width="7.140625" style="45" customWidth="1"/>
+    <col min="6662" max="6662" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6663" max="6663" width="6.85546875" style="45" customWidth="1"/>
+    <col min="6664" max="6664" width="9.28515625" style="45" customWidth="1"/>
+    <col min="6665" max="6665" width="5.85546875" style="45" customWidth="1"/>
+    <col min="6666" max="6666" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6667" max="6667" width="10" style="45" customWidth="1"/>
+    <col min="6668" max="6673" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6674" max="6894" width="9.140625" style="45"/>
+    <col min="6895" max="6895" width="4.140625" style="45" customWidth="1"/>
+    <col min="6896" max="6896" width="15.5703125" style="45" customWidth="1"/>
+    <col min="6897" max="6897" width="7.28515625" style="45" customWidth="1"/>
+    <col min="6898" max="6898" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6899" max="6899" width="4.42578125" style="45" customWidth="1"/>
+    <col min="6900" max="6905" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6906" max="6906" width="9" style="45" customWidth="1"/>
+    <col min="6907" max="6907" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6908" max="6909" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6910" max="6911" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6912" max="6912" width="6.140625" style="45" customWidth="1"/>
+    <col min="6913" max="6913" width="6.42578125" style="45" customWidth="1"/>
+    <col min="6914" max="6914" width="4.85546875" style="45" customWidth="1"/>
+    <col min="6915" max="6915" width="7.5703125" style="45" customWidth="1"/>
+    <col min="6916" max="6916" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6917" max="6917" width="7.140625" style="45" customWidth="1"/>
+    <col min="6918" max="6918" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6919" max="6919" width="6.85546875" style="45" customWidth="1"/>
+    <col min="6920" max="6920" width="9.28515625" style="45" customWidth="1"/>
+    <col min="6921" max="6921" width="5.85546875" style="45" customWidth="1"/>
+    <col min="6922" max="6922" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6923" max="6923" width="10" style="45" customWidth="1"/>
+    <col min="6924" max="6929" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="6930" max="7150" width="9.140625" style="45"/>
+    <col min="7151" max="7151" width="4.140625" style="45" customWidth="1"/>
+    <col min="7152" max="7152" width="15.5703125" style="45" customWidth="1"/>
+    <col min="7153" max="7153" width="7.28515625" style="45" customWidth="1"/>
+    <col min="7154" max="7154" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7155" max="7155" width="4.42578125" style="45" customWidth="1"/>
+    <col min="7156" max="7161" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7162" max="7162" width="9" style="45" customWidth="1"/>
+    <col min="7163" max="7163" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7164" max="7165" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7166" max="7167" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7168" max="7168" width="6.140625" style="45" customWidth="1"/>
+    <col min="7169" max="7169" width="6.42578125" style="45" customWidth="1"/>
+    <col min="7170" max="7170" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7171" max="7171" width="7.5703125" style="45" customWidth="1"/>
+    <col min="7172" max="7172" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7173" max="7173" width="7.140625" style="45" customWidth="1"/>
+    <col min="7174" max="7174" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7175" max="7175" width="6.85546875" style="45" customWidth="1"/>
+    <col min="7176" max="7176" width="9.28515625" style="45" customWidth="1"/>
+    <col min="7177" max="7177" width="5.85546875" style="45" customWidth="1"/>
+    <col min="7178" max="7178" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7179" max="7179" width="10" style="45" customWidth="1"/>
+    <col min="7180" max="7185" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7186" max="7406" width="9.140625" style="45"/>
+    <col min="7407" max="7407" width="4.140625" style="45" customWidth="1"/>
+    <col min="7408" max="7408" width="15.5703125" style="45" customWidth="1"/>
+    <col min="7409" max="7409" width="7.28515625" style="45" customWidth="1"/>
+    <col min="7410" max="7410" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7411" max="7411" width="4.42578125" style="45" customWidth="1"/>
+    <col min="7412" max="7417" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7418" max="7418" width="9" style="45" customWidth="1"/>
+    <col min="7419" max="7419" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7420" max="7421" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7422" max="7423" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7424" max="7424" width="6.140625" style="45" customWidth="1"/>
+    <col min="7425" max="7425" width="6.42578125" style="45" customWidth="1"/>
+    <col min="7426" max="7426" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7427" max="7427" width="7.5703125" style="45" customWidth="1"/>
+    <col min="7428" max="7428" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7429" max="7429" width="7.140625" style="45" customWidth="1"/>
+    <col min="7430" max="7430" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7431" max="7431" width="6.85546875" style="45" customWidth="1"/>
+    <col min="7432" max="7432" width="9.28515625" style="45" customWidth="1"/>
+    <col min="7433" max="7433" width="5.85546875" style="45" customWidth="1"/>
+    <col min="7434" max="7434" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7435" max="7435" width="10" style="45" customWidth="1"/>
+    <col min="7436" max="7441" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7442" max="7662" width="9.140625" style="45"/>
+    <col min="7663" max="7663" width="4.140625" style="45" customWidth="1"/>
+    <col min="7664" max="7664" width="15.5703125" style="45" customWidth="1"/>
+    <col min="7665" max="7665" width="7.28515625" style="45" customWidth="1"/>
+    <col min="7666" max="7666" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7667" max="7667" width="4.42578125" style="45" customWidth="1"/>
+    <col min="7668" max="7673" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7674" max="7674" width="9" style="45" customWidth="1"/>
+    <col min="7675" max="7675" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7676" max="7677" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7678" max="7679" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7680" max="7680" width="6.140625" style="45" customWidth="1"/>
+    <col min="7681" max="7681" width="6.42578125" style="45" customWidth="1"/>
+    <col min="7682" max="7682" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7683" max="7683" width="7.5703125" style="45" customWidth="1"/>
+    <col min="7684" max="7684" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7685" max="7685" width="7.140625" style="45" customWidth="1"/>
+    <col min="7686" max="7686" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7687" max="7687" width="6.85546875" style="45" customWidth="1"/>
+    <col min="7688" max="7688" width="9.28515625" style="45" customWidth="1"/>
+    <col min="7689" max="7689" width="5.85546875" style="45" customWidth="1"/>
+    <col min="7690" max="7690" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7691" max="7691" width="10" style="45" customWidth="1"/>
+    <col min="7692" max="7697" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7698" max="7918" width="9.140625" style="45"/>
+    <col min="7919" max="7919" width="4.140625" style="45" customWidth="1"/>
+    <col min="7920" max="7920" width="15.5703125" style="45" customWidth="1"/>
+    <col min="7921" max="7921" width="7.28515625" style="45" customWidth="1"/>
+    <col min="7922" max="7922" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7923" max="7923" width="4.42578125" style="45" customWidth="1"/>
+    <col min="7924" max="7929" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7930" max="7930" width="9" style="45" customWidth="1"/>
+    <col min="7931" max="7931" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7932" max="7933" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7934" max="7935" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7936" max="7936" width="6.140625" style="45" customWidth="1"/>
+    <col min="7937" max="7937" width="6.42578125" style="45" customWidth="1"/>
+    <col min="7938" max="7938" width="4.85546875" style="45" customWidth="1"/>
+    <col min="7939" max="7939" width="7.5703125" style="45" customWidth="1"/>
+    <col min="7940" max="7940" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7941" max="7941" width="7.140625" style="45" customWidth="1"/>
+    <col min="7942" max="7942" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7943" max="7943" width="6.85546875" style="45" customWidth="1"/>
+    <col min="7944" max="7944" width="9.28515625" style="45" customWidth="1"/>
+    <col min="7945" max="7945" width="5.85546875" style="45" customWidth="1"/>
+    <col min="7946" max="7946" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7947" max="7947" width="10" style="45" customWidth="1"/>
+    <col min="7948" max="7953" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="7954" max="8174" width="9.140625" style="45"/>
+    <col min="8175" max="8175" width="4.140625" style="45" customWidth="1"/>
+    <col min="8176" max="8176" width="15.5703125" style="45" customWidth="1"/>
+    <col min="8177" max="8177" width="7.28515625" style="45" customWidth="1"/>
+    <col min="8178" max="8178" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8179" max="8179" width="4.42578125" style="45" customWidth="1"/>
+    <col min="8180" max="8185" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8186" max="8186" width="9" style="45" customWidth="1"/>
+    <col min="8187" max="8187" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8188" max="8189" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8190" max="8191" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8192" max="8192" width="6.140625" style="45" customWidth="1"/>
+    <col min="8193" max="8193" width="6.42578125" style="45" customWidth="1"/>
+    <col min="8194" max="8194" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8195" max="8195" width="7.5703125" style="45" customWidth="1"/>
+    <col min="8196" max="8196" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8197" max="8197" width="7.140625" style="45" customWidth="1"/>
+    <col min="8198" max="8198" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8199" max="8199" width="6.85546875" style="45" customWidth="1"/>
+    <col min="8200" max="8200" width="9.28515625" style="45" customWidth="1"/>
+    <col min="8201" max="8201" width="5.85546875" style="45" customWidth="1"/>
+    <col min="8202" max="8202" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8203" max="8203" width="10" style="45" customWidth="1"/>
+    <col min="8204" max="8209" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8210" max="8430" width="9.140625" style="45"/>
+    <col min="8431" max="8431" width="4.140625" style="45" customWidth="1"/>
+    <col min="8432" max="8432" width="15.5703125" style="45" customWidth="1"/>
+    <col min="8433" max="8433" width="7.28515625" style="45" customWidth="1"/>
+    <col min="8434" max="8434" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8435" max="8435" width="4.42578125" style="45" customWidth="1"/>
+    <col min="8436" max="8441" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8442" max="8442" width="9" style="45" customWidth="1"/>
+    <col min="8443" max="8443" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8444" max="8445" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8446" max="8447" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8448" max="8448" width="6.140625" style="45" customWidth="1"/>
+    <col min="8449" max="8449" width="6.42578125" style="45" customWidth="1"/>
+    <col min="8450" max="8450" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8451" max="8451" width="7.5703125" style="45" customWidth="1"/>
+    <col min="8452" max="8452" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8453" max="8453" width="7.140625" style="45" customWidth="1"/>
+    <col min="8454" max="8454" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8455" max="8455" width="6.85546875" style="45" customWidth="1"/>
+    <col min="8456" max="8456" width="9.28515625" style="45" customWidth="1"/>
+    <col min="8457" max="8457" width="5.85546875" style="45" customWidth="1"/>
+    <col min="8458" max="8458" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8459" max="8459" width="10" style="45" customWidth="1"/>
+    <col min="8460" max="8465" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8466" max="8686" width="9.140625" style="45"/>
+    <col min="8687" max="8687" width="4.140625" style="45" customWidth="1"/>
+    <col min="8688" max="8688" width="15.5703125" style="45" customWidth="1"/>
+    <col min="8689" max="8689" width="7.28515625" style="45" customWidth="1"/>
+    <col min="8690" max="8690" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8691" max="8691" width="4.42578125" style="45" customWidth="1"/>
+    <col min="8692" max="8697" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8698" max="8698" width="9" style="45" customWidth="1"/>
+    <col min="8699" max="8699" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8700" max="8701" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8702" max="8703" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8704" max="8704" width="6.140625" style="45" customWidth="1"/>
+    <col min="8705" max="8705" width="6.42578125" style="45" customWidth="1"/>
+    <col min="8706" max="8706" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8707" max="8707" width="7.5703125" style="45" customWidth="1"/>
+    <col min="8708" max="8708" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8709" max="8709" width="7.140625" style="45" customWidth="1"/>
+    <col min="8710" max="8710" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8711" max="8711" width="6.85546875" style="45" customWidth="1"/>
+    <col min="8712" max="8712" width="9.28515625" style="45" customWidth="1"/>
+    <col min="8713" max="8713" width="5.85546875" style="45" customWidth="1"/>
+    <col min="8714" max="8714" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8715" max="8715" width="10" style="45" customWidth="1"/>
+    <col min="8716" max="8721" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8722" max="8942" width="9.140625" style="45"/>
+    <col min="8943" max="8943" width="4.140625" style="45" customWidth="1"/>
+    <col min="8944" max="8944" width="15.5703125" style="45" customWidth="1"/>
+    <col min="8945" max="8945" width="7.28515625" style="45" customWidth="1"/>
+    <col min="8946" max="8946" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8947" max="8947" width="4.42578125" style="45" customWidth="1"/>
+    <col min="8948" max="8953" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8954" max="8954" width="9" style="45" customWidth="1"/>
+    <col min="8955" max="8955" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8956" max="8957" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8958" max="8959" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8960" max="8960" width="6.140625" style="45" customWidth="1"/>
+    <col min="8961" max="8961" width="6.42578125" style="45" customWidth="1"/>
+    <col min="8962" max="8962" width="4.85546875" style="45" customWidth="1"/>
+    <col min="8963" max="8963" width="7.5703125" style="45" customWidth="1"/>
+    <col min="8964" max="8964" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8965" max="8965" width="7.140625" style="45" customWidth="1"/>
+    <col min="8966" max="8966" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8967" max="8967" width="6.85546875" style="45" customWidth="1"/>
+    <col min="8968" max="8968" width="9.28515625" style="45" customWidth="1"/>
+    <col min="8969" max="8969" width="5.85546875" style="45" customWidth="1"/>
+    <col min="8970" max="8970" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8971" max="8971" width="10" style="45" customWidth="1"/>
+    <col min="8972" max="8977" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="8978" max="9198" width="9.140625" style="45"/>
+    <col min="9199" max="9199" width="4.140625" style="45" customWidth="1"/>
+    <col min="9200" max="9200" width="15.5703125" style="45" customWidth="1"/>
+    <col min="9201" max="9201" width="7.28515625" style="45" customWidth="1"/>
+    <col min="9202" max="9202" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9203" max="9203" width="4.42578125" style="45" customWidth="1"/>
+    <col min="9204" max="9209" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9210" max="9210" width="9" style="45" customWidth="1"/>
+    <col min="9211" max="9211" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9212" max="9213" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9214" max="9215" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9216" max="9216" width="6.140625" style="45" customWidth="1"/>
+    <col min="9217" max="9217" width="6.42578125" style="45" customWidth="1"/>
+    <col min="9218" max="9218" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9219" max="9219" width="7.5703125" style="45" customWidth="1"/>
+    <col min="9220" max="9220" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9221" max="9221" width="7.140625" style="45" customWidth="1"/>
+    <col min="9222" max="9222" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9223" max="9223" width="6.85546875" style="45" customWidth="1"/>
+    <col min="9224" max="9224" width="9.28515625" style="45" customWidth="1"/>
+    <col min="9225" max="9225" width="5.85546875" style="45" customWidth="1"/>
+    <col min="9226" max="9226" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9227" max="9227" width="10" style="45" customWidth="1"/>
+    <col min="9228" max="9233" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9234" max="9454" width="9.140625" style="45"/>
+    <col min="9455" max="9455" width="4.140625" style="45" customWidth="1"/>
+    <col min="9456" max="9456" width="15.5703125" style="45" customWidth="1"/>
+    <col min="9457" max="9457" width="7.28515625" style="45" customWidth="1"/>
+    <col min="9458" max="9458" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9459" max="9459" width="4.42578125" style="45" customWidth="1"/>
+    <col min="9460" max="9465" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9466" max="9466" width="9" style="45" customWidth="1"/>
+    <col min="9467" max="9467" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9468" max="9469" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9470" max="9471" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9472" max="9472" width="6.140625" style="45" customWidth="1"/>
+    <col min="9473" max="9473" width="6.42578125" style="45" customWidth="1"/>
+    <col min="9474" max="9474" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9475" max="9475" width="7.5703125" style="45" customWidth="1"/>
+    <col min="9476" max="9476" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9477" max="9477" width="7.140625" style="45" customWidth="1"/>
+    <col min="9478" max="9478" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9479" max="9479" width="6.85546875" style="45" customWidth="1"/>
+    <col min="9480" max="9480" width="9.28515625" style="45" customWidth="1"/>
+    <col min="9481" max="9481" width="5.85546875" style="45" customWidth="1"/>
+    <col min="9482" max="9482" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9483" max="9483" width="10" style="45" customWidth="1"/>
+    <col min="9484" max="9489" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9490" max="9710" width="9.140625" style="45"/>
+    <col min="9711" max="9711" width="4.140625" style="45" customWidth="1"/>
+    <col min="9712" max="9712" width="15.5703125" style="45" customWidth="1"/>
+    <col min="9713" max="9713" width="7.28515625" style="45" customWidth="1"/>
+    <col min="9714" max="9714" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9715" max="9715" width="4.42578125" style="45" customWidth="1"/>
+    <col min="9716" max="9721" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9722" max="9722" width="9" style="45" customWidth="1"/>
+    <col min="9723" max="9723" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9724" max="9725" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9726" max="9727" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9728" max="9728" width="6.140625" style="45" customWidth="1"/>
+    <col min="9729" max="9729" width="6.42578125" style="45" customWidth="1"/>
+    <col min="9730" max="9730" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9731" max="9731" width="7.5703125" style="45" customWidth="1"/>
+    <col min="9732" max="9732" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9733" max="9733" width="7.140625" style="45" customWidth="1"/>
+    <col min="9734" max="9734" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9735" max="9735" width="6.85546875" style="45" customWidth="1"/>
+    <col min="9736" max="9736" width="9.28515625" style="45" customWidth="1"/>
+    <col min="9737" max="9737" width="5.85546875" style="45" customWidth="1"/>
+    <col min="9738" max="9738" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9739" max="9739" width="10" style="45" customWidth="1"/>
+    <col min="9740" max="9745" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9746" max="9966" width="9.140625" style="45"/>
+    <col min="9967" max="9967" width="4.140625" style="45" customWidth="1"/>
+    <col min="9968" max="9968" width="15.5703125" style="45" customWidth="1"/>
+    <col min="9969" max="9969" width="7.28515625" style="45" customWidth="1"/>
+    <col min="9970" max="9970" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9971" max="9971" width="4.42578125" style="45" customWidth="1"/>
+    <col min="9972" max="9977" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9978" max="9978" width="9" style="45" customWidth="1"/>
+    <col min="9979" max="9979" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9980" max="9981" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9982" max="9983" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9984" max="9984" width="6.140625" style="45" customWidth="1"/>
+    <col min="9985" max="9985" width="6.42578125" style="45" customWidth="1"/>
+    <col min="9986" max="9986" width="4.85546875" style="45" customWidth="1"/>
+    <col min="9987" max="9987" width="7.5703125" style="45" customWidth="1"/>
+    <col min="9988" max="9988" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9989" max="9989" width="7.140625" style="45" customWidth="1"/>
+    <col min="9990" max="9990" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9991" max="9991" width="6.85546875" style="45" customWidth="1"/>
+    <col min="9992" max="9992" width="9.28515625" style="45" customWidth="1"/>
+    <col min="9993" max="9993" width="5.85546875" style="45" customWidth="1"/>
+    <col min="9994" max="9994" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="9995" max="9995" width="10" style="45" customWidth="1"/>
+    <col min="9996" max="10001" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10002" max="10222" width="9.140625" style="45"/>
+    <col min="10223" max="10223" width="4.140625" style="45" customWidth="1"/>
+    <col min="10224" max="10224" width="15.5703125" style="45" customWidth="1"/>
+    <col min="10225" max="10225" width="7.28515625" style="45" customWidth="1"/>
+    <col min="10226" max="10226" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10227" max="10227" width="4.42578125" style="45" customWidth="1"/>
+    <col min="10228" max="10233" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10234" max="10234" width="9" style="45" customWidth="1"/>
+    <col min="10235" max="10235" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10236" max="10237" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10238" max="10239" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10240" max="10240" width="6.140625" style="45" customWidth="1"/>
+    <col min="10241" max="10241" width="6.42578125" style="45" customWidth="1"/>
+    <col min="10242" max="10242" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10243" max="10243" width="7.5703125" style="45" customWidth="1"/>
+    <col min="10244" max="10244" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10245" max="10245" width="7.140625" style="45" customWidth="1"/>
+    <col min="10246" max="10246" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10247" max="10247" width="6.85546875" style="45" customWidth="1"/>
+    <col min="10248" max="10248" width="9.28515625" style="45" customWidth="1"/>
+    <col min="10249" max="10249" width="5.85546875" style="45" customWidth="1"/>
+    <col min="10250" max="10250" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10251" max="10251" width="10" style="45" customWidth="1"/>
+    <col min="10252" max="10257" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10258" max="10478" width="9.140625" style="45"/>
+    <col min="10479" max="10479" width="4.140625" style="45" customWidth="1"/>
+    <col min="10480" max="10480" width="15.5703125" style="45" customWidth="1"/>
+    <col min="10481" max="10481" width="7.28515625" style="45" customWidth="1"/>
+    <col min="10482" max="10482" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10483" max="10483" width="4.42578125" style="45" customWidth="1"/>
+    <col min="10484" max="10489" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10490" max="10490" width="9" style="45" customWidth="1"/>
+    <col min="10491" max="10491" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10492" max="10493" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10494" max="10495" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10496" max="10496" width="6.140625" style="45" customWidth="1"/>
+    <col min="10497" max="10497" width="6.42578125" style="45" customWidth="1"/>
+    <col min="10498" max="10498" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10499" max="10499" width="7.5703125" style="45" customWidth="1"/>
+    <col min="10500" max="10500" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10501" max="10501" width="7.140625" style="45" customWidth="1"/>
+    <col min="10502" max="10502" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10503" max="10503" width="6.85546875" style="45" customWidth="1"/>
+    <col min="10504" max="10504" width="9.28515625" style="45" customWidth="1"/>
+    <col min="10505" max="10505" width="5.85546875" style="45" customWidth="1"/>
+    <col min="10506" max="10506" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10507" max="10507" width="10" style="45" customWidth="1"/>
+    <col min="10508" max="10513" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10514" max="10734" width="9.140625" style="45"/>
+    <col min="10735" max="10735" width="4.140625" style="45" customWidth="1"/>
+    <col min="10736" max="10736" width="15.5703125" style="45" customWidth="1"/>
+    <col min="10737" max="10737" width="7.28515625" style="45" customWidth="1"/>
+    <col min="10738" max="10738" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10739" max="10739" width="4.42578125" style="45" customWidth="1"/>
+    <col min="10740" max="10745" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10746" max="10746" width="9" style="45" customWidth="1"/>
+    <col min="10747" max="10747" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10748" max="10749" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10750" max="10751" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10752" max="10752" width="6.140625" style="45" customWidth="1"/>
+    <col min="10753" max="10753" width="6.42578125" style="45" customWidth="1"/>
+    <col min="10754" max="10754" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10755" max="10755" width="7.5703125" style="45" customWidth="1"/>
+    <col min="10756" max="10756" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10757" max="10757" width="7.140625" style="45" customWidth="1"/>
+    <col min="10758" max="10758" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10759" max="10759" width="6.85546875" style="45" customWidth="1"/>
+    <col min="10760" max="10760" width="9.28515625" style="45" customWidth="1"/>
+    <col min="10761" max="10761" width="5.85546875" style="45" customWidth="1"/>
+    <col min="10762" max="10762" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10763" max="10763" width="10" style="45" customWidth="1"/>
+    <col min="10764" max="10769" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="10770" max="10990" width="9.140625" style="45"/>
+    <col min="10991" max="10991" width="4.140625" style="45" customWidth="1"/>
+    <col min="10992" max="10992" width="15.5703125" style="45" customWidth="1"/>
+    <col min="10993" max="10993" width="7.28515625" style="45" customWidth="1"/>
+    <col min="10994" max="10994" width="4.85546875" style="45" customWidth="1"/>
+    <col min="10995" max="10995" width="4.42578125" style="45" customWidth="1"/>
+    <col min="10996" max="11001" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11002" max="11002" width="9" style="45" customWidth="1"/>
+    <col min="11003" max="11003" width="4.85546875" style="45" customWidth="1"/>
+    <col min="11004" max="11005" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11006" max="11007" width="4.85546875" style="45" customWidth="1"/>
+    <col min="11008" max="11008" width="6.140625" style="45" customWidth="1"/>
+    <col min="11009" max="11009" width="6.42578125" style="45" customWidth="1"/>
+    <col min="11010" max="11010" width="4.85546875" style="45" customWidth="1"/>
+    <col min="11011" max="11011" width="7.5703125" style="45" customWidth="1"/>
+    <col min="11012" max="11012" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11013" max="11013" width="7.140625" style="45" customWidth="1"/>
+    <col min="11014" max="11014" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11015" max="11015" width="6.85546875" style="45" customWidth="1"/>
+    <col min="11016" max="11016" width="9.28515625" style="45" customWidth="1"/>
+    <col min="11017" max="11017" width="5.85546875" style="45" customWidth="1"/>
+    <col min="11018" max="11018" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11019" max="11019" width="10" style="45" customWidth="1"/>
+    <col min="11020" max="11025" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11026" max="11246" width="9.140625" style="45"/>
+    <col min="11247" max="11247" width="4.140625" style="45" customWidth="1"/>
+    <col min="11248" max="11248" width="15.5703125" style="45" customWidth="1"/>
+    <col min="11249" max="11249" width="7.28515625" style="45" customWidth="1"/>
+    <col min="11250" max="11250" width="4.85546875" style="45" customWidth="1"/>
+    <col min="11251" max="11251" width="4.42578125" style="45" customWidth="1"/>
+    <col min="11252" max="11257" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11258" max="11258" width="9" style="45" customWidth="1"/>
+    <col min="11259" max="11259" width="4.85546875" style="45" customWidth="1"/>
+    <col min="11260" max="11261" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11262" max="11263" width="4.85546875" style="45" customWidth="1"/>
+    <col min="11264" max="11264" width="6.140625" style="45" customWidth="1"/>
+    <col min="11265" max="11265" width="6.42578125" style="45" customWidth="1"/>
+    <col min="11266" max="11266" width="4.85546875" style="45" customWidth="1"/>
+    <col min="11267" max="11267" width="7.5703125" style="45" customWidth="1"/>
+    <col min="11268" max="11268" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11269" max="11269" width="7.140625" style="45" customWidth="1"/>
+    <col min="11270" max="11270" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11271" max="11271" width="6.85546875" style="45" customWidth="1"/>
+    <col min="11272" max="11272" width="9.28515625" style="45" customWidth="1"/>
+    <col min="11273" max="11273" width="5.85546875" style="45" customWidth="1"/>
+    <col min="11274" max="11274" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11275" max="11275" width="10" style="45" customWidth="1"/>
+    <col min="11276" max="11281" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11282" max="11502" width="9.140625" style="45"/>
+    <col min="11503" max="11503" width="4.140625" style="45" customWidth="1"/>
+    <col min="11504" max="11504" width="15.5703125" style="45" customWidth="1"/>
+    <col min="11505" max="11505" width="7.28515625" style="45" customWidth="1"/>
+    <col min="11506" max="11506" width="4.85546875" style="45" customWidth="1"/>
+    <col min="11507" max="11507" width="4.42578125" style="45" customWidth="1"/>
+    <col min="11508" max="11513" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11514" max="11514" width="9" style="45" customWidth="1"/>
+    <col min="11515" max="11515" width="4.85546875" style="45" customWidth="1"/>
+    <col min="11516" max="11517" width="0" style="45" hidden="1" customWidth="1"/>
+    <col min="11518" max="11518" width="4.85546875" style="45" customWidth="1"/>
+    <col min="11519" max="11519" width="4.85546875" customWidth="1"/>
+    <col min="11520" max="11520" width="6.140625" customWidth="1"/>
+    <col min="11521" max="11521" width="6.42578125" customWidth="1"/>
+    <col min="11522" max="11522" width="4.85546875" customWidth="1"/>
+    <col min="11523" max="11523" width="7.5703125" customWidth="1"/>
+    <col min="11524" max="11524" width="0" hidden="1" customWidth="1"/>
+    <col min="11525" max="11525" width="7.140625" customWidth="1"/>
+    <col min="11526" max="11526" width="0" hidden="1" customWidth="1"/>
+    <col min="11527" max="11527" width="6.85546875" customWidth="1"/>
+    <col min="11528" max="11528" width="9.28515625" customWidth="1"/>
+    <col min="11529" max="11529" width="5.85546875" customWidth="1"/>
+    <col min="11530" max="11530" width="0" hidden="1" customWidth="1"/>
+    <col min="11531" max="11531" width="10" customWidth="1"/>
+    <col min="11532" max="11537" width="0" hidden="1" customWidth="1"/>
+    <col min="11759" max="11759" width="4.140625" customWidth="1"/>
+    <col min="11760" max="11760" width="15.5703125" customWidth="1"/>
+    <col min="11761" max="11761" width="7.28515625" customWidth="1"/>
+    <col min="11762" max="11762" width="4.85546875" customWidth="1"/>
+    <col min="11763" max="11763" width="4.42578125" customWidth="1"/>
+    <col min="11764" max="11769" width="0" hidden="1" customWidth="1"/>
+    <col min="11770" max="11770" width="9" customWidth="1"/>
+    <col min="11771" max="11771" width="4.85546875" customWidth="1"/>
+    <col min="11772" max="11773" width="0" hidden="1" customWidth="1"/>
+    <col min="11774" max="11775" width="4.85546875" customWidth="1"/>
+    <col min="11776" max="11776" width="6.140625" customWidth="1"/>
+    <col min="11777" max="11777" width="6.42578125" customWidth="1"/>
+    <col min="11778" max="11778" width="4.85546875" customWidth="1"/>
+    <col min="11779" max="11779" width="7.5703125" customWidth="1"/>
+    <col min="11780" max="11780" width="0" hidden="1" customWidth="1"/>
+    <col min="11781" max="11781" width="7.140625" customWidth="1"/>
+    <col min="11782" max="11782" width="0" hidden="1" customWidth="1"/>
+    <col min="11783" max="11783" width="6.85546875" customWidth="1"/>
+    <col min="11784" max="11784" width="9.28515625" customWidth="1"/>
+    <col min="11785" max="11785" width="5.85546875" customWidth="1"/>
+    <col min="11786" max="11786" width="0" hidden="1" customWidth="1"/>
+    <col min="11787" max="11787" width="10" customWidth="1"/>
+    <col min="11788" max="11793" width="0" hidden="1" customWidth="1"/>
+    <col min="12015" max="12015" width="4.140625" customWidth="1"/>
+    <col min="12016" max="12016" width="15.5703125" customWidth="1"/>
+    <col min="12017" max="12017" width="7.28515625" customWidth="1"/>
+    <col min="12018" max="12018" width="4.85546875" customWidth="1"/>
+    <col min="12019" max="12019" width="4.42578125" customWidth="1"/>
+    <col min="12020" max="12025" width="0" hidden="1" customWidth="1"/>
+    <col min="12026" max="12026" width="9" customWidth="1"/>
+    <col min="12027" max="12027" width="4.85546875" customWidth="1"/>
+    <col min="12028" max="12029" width="0" hidden="1" customWidth="1"/>
+    <col min="12030" max="12031" width="4.85546875" customWidth="1"/>
+    <col min="12032" max="12032" width="6.140625" customWidth="1"/>
+    <col min="12033" max="12033" width="6.42578125" customWidth="1"/>
+    <col min="12034" max="12034" width="4.85546875" customWidth="1"/>
+    <col min="12035" max="12035" width="7.5703125" customWidth="1"/>
+    <col min="12036" max="12036" width="0" hidden="1" customWidth="1"/>
+    <col min="12037" max="12037" width="7.140625" customWidth="1"/>
+    <col min="12038" max="12038" width="0" hidden="1" customWidth="1"/>
+    <col min="12039" max="12039" width="6.85546875" customWidth="1"/>
+    <col min="12040" max="12040" width="9.28515625" customWidth="1"/>
+    <col min="12041" max="12041" width="5.85546875" customWidth="1"/>
+    <col min="12042" max="12042" width="0" hidden="1" customWidth="1"/>
+    <col min="12043" max="12043" width="10" customWidth="1"/>
+    <col min="12044" max="12049" width="0" hidden="1" customWidth="1"/>
+    <col min="12271" max="12271" width="4.140625" customWidth="1"/>
+    <col min="12272" max="12272" width="15.5703125" customWidth="1"/>
+    <col min="12273" max="12273" width="7.28515625" customWidth="1"/>
+    <col min="12274" max="12274" width="4.85546875" customWidth="1"/>
+    <col min="12275" max="12275" width="4.42578125" customWidth="1"/>
+    <col min="12276" max="12281" width="0" hidden="1" customWidth="1"/>
+    <col min="12282" max="12282" width="9" customWidth="1"/>
+    <col min="12283" max="12283" width="4.85546875" customWidth="1"/>
+    <col min="12284" max="12285" width="0" hidden="1" customWidth="1"/>
+    <col min="12286" max="12287" width="4.85546875" customWidth="1"/>
+    <col min="12288" max="12288" width="6.140625" customWidth="1"/>
+    <col min="12289" max="12289" width="6.42578125" customWidth="1"/>
+    <col min="12290" max="12290" width="4.85546875" customWidth="1"/>
+    <col min="12291" max="12291" width="7.5703125" customWidth="1"/>
+    <col min="12292" max="12292" width="0" hidden="1" customWidth="1"/>
+    <col min="12293" max="12293" width="7.140625" customWidth="1"/>
+    <col min="12294" max="12294" width="0" hidden="1" customWidth="1"/>
+    <col min="12295" max="12295" width="6.85546875" customWidth="1"/>
+    <col min="12296" max="12296" width="9.28515625" customWidth="1"/>
+    <col min="12297" max="12297" width="5.85546875" customWidth="1"/>
+    <col min="12298" max="12298" width="0" hidden="1" customWidth="1"/>
+    <col min="12299" max="12299" width="10" customWidth="1"/>
+    <col min="12300" max="12305" width="0" hidden="1" customWidth="1"/>
+    <col min="12527" max="12527" width="4.140625" customWidth="1"/>
+    <col min="12528" max="12528" width="15.5703125" customWidth="1"/>
+    <col min="12529" max="12529" width="7.28515625" customWidth="1"/>
+    <col min="12530" max="12530" width="4.85546875" customWidth="1"/>
+    <col min="12531" max="12531" width="4.42578125" customWidth="1"/>
+    <col min="12532" max="12537" width="0" hidden="1" customWidth="1"/>
+    <col min="12538" max="12538" width="9" customWidth="1"/>
+    <col min="12539" max="12539" width="4.85546875" customWidth="1"/>
+    <col min="12540" max="12541" width="0" hidden="1" customWidth="1"/>
+    <col min="12542" max="12543" width="4.85546875" customWidth="1"/>
+    <col min="12544" max="12544" width="6.140625" customWidth="1"/>
+    <col min="12545" max="12545" width="6.42578125" customWidth="1"/>
+    <col min="12546" max="12546" width="4.85546875" customWidth="1"/>
+    <col min="12547" max="12547" width="7.5703125" customWidth="1"/>
+    <col min="12548" max="12548" width="0" hidden="1" customWidth="1"/>
+    <col min="12549" max="12549" width="7.140625" customWidth="1"/>
+    <col min="12550" max="12550" width="0" hidden="1" customWidth="1"/>
+    <col min="12551" max="12551" width="6.85546875" customWidth="1"/>
+    <col min="12552" max="12552" width="9.28515625" customWidth="1"/>
+    <col min="12553" max="12553" width="5.85546875" customWidth="1"/>
+    <col min="12554" max="12554" width="0" hidden="1" customWidth="1"/>
+    <col min="12555" max="12555" width="10" customWidth="1"/>
+    <col min="12556" max="12561" width="0" hidden="1" customWidth="1"/>
+    <col min="12783" max="12783" width="4.140625" customWidth="1"/>
+    <col min="12784" max="12784" width="15.5703125" customWidth="1"/>
+    <col min="12785" max="12785" width="7.28515625" customWidth="1"/>
+    <col min="12786" max="12786" width="4.85546875" customWidth="1"/>
+    <col min="12787" max="12787" width="4.42578125" customWidth="1"/>
+    <col min="12788" max="12793" width="0" hidden="1" customWidth="1"/>
+    <col min="12794" max="12794" width="9" customWidth="1"/>
+    <col min="12795" max="12795" width="4.85546875" customWidth="1"/>
+    <col min="12796" max="12797" width="0" hidden="1" customWidth="1"/>
+    <col min="12798" max="12799" width="4.85546875" customWidth="1"/>
+    <col min="12800" max="12800" width="6.140625" customWidth="1"/>
+    <col min="12801" max="12801" width="6.42578125" customWidth="1"/>
+    <col min="12802" max="12802" width="4.85546875" customWidth="1"/>
+    <col min="12803" max="12803" width="7.5703125" customWidth="1"/>
+    <col min="12804" max="12804" width="0" hidden="1" customWidth="1"/>
+    <col min="12805" max="12805" width="7.140625" customWidth="1"/>
+    <col min="12806" max="12806" width="0" hidden="1" customWidth="1"/>
+    <col min="12807" max="12807" width="6.85546875" customWidth="1"/>
+    <col min="12808" max="12808" width="9.28515625" customWidth="1"/>
+    <col min="12809" max="12809" width="5.85546875" customWidth="1"/>
+    <col min="12810" max="12810" width="0" hidden="1" customWidth="1"/>
+    <col min="12811" max="12811" width="10" customWidth="1"/>
+    <col min="12812" max="12817" width="0" hidden="1" customWidth="1"/>
+    <col min="13039" max="13039" width="4.140625" customWidth="1"/>
+    <col min="13040" max="13040" width="15.5703125" customWidth="1"/>
+    <col min="13041" max="13041" width="7.28515625" customWidth="1"/>
+    <col min="13042" max="13042" width="4.85546875" customWidth="1"/>
+    <col min="13043" max="13043" width="4.42578125" customWidth="1"/>
+    <col min="13044" max="13049" width="0" hidden="1" customWidth="1"/>
+    <col min="13050" max="13050" width="9" customWidth="1"/>
+    <col min="13051" max="13051" width="4.85546875" customWidth="1"/>
+    <col min="13052" max="13053" width="0" hidden="1" customWidth="1"/>
+    <col min="13054" max="13055" width="4.85546875" customWidth="1"/>
+    <col min="13056" max="13056" width="6.140625" customWidth="1"/>
+    <col min="13057" max="13057" width="6.42578125" customWidth="1"/>
+    <col min="13058" max="13058" width="4.85546875" customWidth="1"/>
+    <col min="13059" max="13059" width="7.5703125" customWidth="1"/>
+    <col min="13060" max="13060" width="0" hidden="1" customWidth="1"/>
+    <col min="13061" max="13061" width="7.140625" customWidth="1"/>
+    <col min="13062" max="13062" width="0" hidden="1" customWidth="1"/>
+    <col min="13063" max="13063" width="6.85546875" customWidth="1"/>
+    <col min="13064" max="13064" width="9.28515625" customWidth="1"/>
+    <col min="13065" max="13065" width="5.85546875" customWidth="1"/>
+    <col min="13066" max="13066" width="0" hidden="1" customWidth="1"/>
+    <col min="13067" max="13067" width="10" customWidth="1"/>
+    <col min="13068" max="13073" width="0" hidden="1" customWidth="1"/>
+    <col min="13295" max="13295" width="4.140625" customWidth="1"/>
+    <col min="13296" max="13296" width="15.5703125" customWidth="1"/>
+    <col min="13297" max="13297" width="7.28515625" customWidth="1"/>
+    <col min="13298" max="13298" width="4.85546875" customWidth="1"/>
+    <col min="13299" max="13299" width="4.42578125" customWidth="1"/>
+    <col min="13300" max="13305" width="0" hidden="1" customWidth="1"/>
+    <col min="13306" max="13306" width="9" customWidth="1"/>
+    <col min="13307" max="13307" width="4.85546875" customWidth="1"/>
+    <col min="13308" max="13309" width="0" hidden="1" customWidth="1"/>
+    <col min="13310" max="13311" width="4.85546875" customWidth="1"/>
+    <col min="13312" max="13312" width="6.140625" customWidth="1"/>
+    <col min="13313" max="13313" width="6.42578125" customWidth="1"/>
+    <col min="13314" max="13314" width="4.85546875" customWidth="1"/>
+    <col min="13315" max="13315" width="7.5703125" customWidth="1"/>
+    <col min="13316" max="13316" width="0" hidden="1" customWidth="1"/>
+    <col min="13317" max="13317" width="7.140625" customWidth="1"/>
+    <col min="13318" max="13318" width="0" hidden="1" customWidth="1"/>
+    <col min="13319" max="13319" width="6.85546875" customWidth="1"/>
+    <col min="13320" max="13320" width="9.28515625" customWidth="1"/>
+    <col min="13321" max="13321" width="5.85546875" customWidth="1"/>
+    <col min="13322" max="13322" width="0" hidden="1" customWidth="1"/>
+    <col min="13323" max="13323" width="10" customWidth="1"/>
+    <col min="13324" max="13329" width="0" hidden="1" customWidth="1"/>
+    <col min="13551" max="13551" width="4.140625" customWidth="1"/>
+    <col min="13552" max="13552" width="15.5703125" customWidth="1"/>
+    <col min="13553" max="13553" width="7.28515625" customWidth="1"/>
+    <col min="13554" max="13554" width="4.85546875" customWidth="1"/>
+    <col min="13555" max="13555" width="4.42578125" customWidth="1"/>
+    <col min="13556" max="13561" width="0" hidden="1" customWidth="1"/>
+    <col min="13562" max="13562" width="9" customWidth="1"/>
+    <col min="13563" max="13563" width="4.85546875" customWidth="1"/>
+    <col min="13564" max="13565" width="0" hidden="1" customWidth="1"/>
+    <col min="13566" max="13567" width="4.85546875" customWidth="1"/>
+    <col min="13568" max="13568" width="6.140625" customWidth="1"/>
+    <col min="13569" max="13569" width="6.42578125" customWidth="1"/>
+    <col min="13570" max="13570" width="4.85546875" customWidth="1"/>
+    <col min="13571" max="13571" width="7.5703125" customWidth="1"/>
+    <col min="13572" max="13572" width="0" hidden="1" customWidth="1"/>
+    <col min="13573" max="13573" width="7.140625" customWidth="1"/>
+    <col min="13574" max="13574" width="0" hidden="1" customWidth="1"/>
+    <col min="13575" max="13575" width="6.85546875" customWidth="1"/>
+    <col min="13576" max="13576" width="9.28515625" customWidth="1"/>
+    <col min="13577" max="13577" width="5.85546875" customWidth="1"/>
+    <col min="13578" max="13578" width="0" hidden="1" customWidth="1"/>
+    <col min="13579" max="13579" width="10" customWidth="1"/>
+    <col min="13580" max="13585" width="0" hidden="1" customWidth="1"/>
+    <col min="13807" max="13807" width="4.140625" customWidth="1"/>
+    <col min="13808" max="13808" width="15.5703125" customWidth="1"/>
+    <col min="13809" max="13809" width="7.28515625" customWidth="1"/>
+    <col min="13810" max="13810" width="4.85546875" customWidth="1"/>
+    <col min="13811" max="13811" width="4.42578125" customWidth="1"/>
+    <col min="13812" max="13817" width="0" hidden="1" customWidth="1"/>
+    <col min="13818" max="13818" width="9" customWidth="1"/>
+    <col min="13819" max="13819" width="4.85546875" customWidth="1"/>
+    <col min="13820" max="13821" width="0" hidden="1" customWidth="1"/>
+    <col min="13822" max="13823" width="4.85546875" customWidth="1"/>
+    <col min="13824" max="13824" width="6.140625" customWidth="1"/>
+    <col min="13825" max="13825" width="6.42578125" customWidth="1"/>
+    <col min="13826" max="13826" width="4.85546875" customWidth="1"/>
+    <col min="13827" max="13827" width="7.5703125" customWidth="1"/>
+    <col min="13828" max="13828" width="0" hidden="1" customWidth="1"/>
+    <col min="13829" max="13829" width="7.140625" customWidth="1"/>
+    <col min="13830" max="13830" width="0" hidden="1" customWidth="1"/>
+    <col min="13831" max="13831" width="6.85546875" customWidth="1"/>
+    <col min="13832" max="13832" width="9.28515625" customWidth="1"/>
+    <col min="13833" max="13833" width="5.85546875" customWidth="1"/>
+    <col min="13834" max="13834" width="0" hidden="1" customWidth="1"/>
+    <col min="13835" max="13835" width="10" customWidth="1"/>
+    <col min="13836" max="13841" width="0" hidden="1" customWidth="1"/>
+    <col min="14063" max="14063" width="4.140625" customWidth="1"/>
+    <col min="14064" max="14064" width="15.5703125" customWidth="1"/>
+    <col min="14065" max="14065" width="7.28515625" customWidth="1"/>
+    <col min="14066" max="14066" width="4.85546875" customWidth="1"/>
+    <col min="14067" max="14067" width="4.42578125" customWidth="1"/>
+    <col min="14068" max="14073" width="0" hidden="1" customWidth="1"/>
+    <col min="14074" max="14074" width="9" customWidth="1"/>
+    <col min="14075" max="14075" width="4.85546875" customWidth="1"/>
+    <col min="14076" max="14077" width="0" hidden="1" customWidth="1"/>
+    <col min="14078" max="14079" width="4.85546875" customWidth="1"/>
+    <col min="14080" max="14080" width="6.140625" customWidth="1"/>
+    <col min="14081" max="14081" width="6.42578125" customWidth="1"/>
+    <col min="14082" max="14082" width="4.85546875" customWidth="1"/>
+    <col min="14083" max="14083" width="7.5703125" customWidth="1"/>
+    <col min="14084" max="14084" width="0" hidden="1" customWidth="1"/>
+    <col min="14085" max="14085" width="7.140625" customWidth="1"/>
+    <col min="14086" max="14086" width="0" hidden="1" customWidth="1"/>
+    <col min="14087" max="14087" width="6.85546875" customWidth="1"/>
+    <col min="14088" max="14088" width="9.28515625" customWidth="1"/>
+    <col min="14089" max="14089" width="5.85546875" customWidth="1"/>
+    <col min="14090" max="14090" width="0" hidden="1" customWidth="1"/>
+    <col min="14091" max="14091" width="10" customWidth="1"/>
+    <col min="14092" max="14097" width="0" hidden="1" customWidth="1"/>
+    <col min="14319" max="14319" width="4.140625" customWidth="1"/>
+    <col min="14320" max="14320" width="15.5703125" customWidth="1"/>
+    <col min="14321" max="14321" width="7.28515625" customWidth="1"/>
+    <col min="14322" max="14322" width="4.85546875" customWidth="1"/>
+    <col min="14323" max="14323" width="4.42578125" customWidth="1"/>
+    <col min="14324" max="14329" width="0" hidden="1" customWidth="1"/>
+    <col min="14330" max="14330" width="9" customWidth="1"/>
+    <col min="14331" max="14331" width="4.85546875" customWidth="1"/>
+    <col min="14332" max="14333" width="0" hidden="1" customWidth="1"/>
+    <col min="14334" max="14335" width="4.85546875" customWidth="1"/>
+    <col min="14336" max="14336" width="6.140625" customWidth="1"/>
+    <col min="14337" max="14337" width="6.42578125" customWidth="1"/>
+    <col min="14338" max="14338" width="4.85546875" customWidth="1"/>
+    <col min="14339" max="14339" width="7.5703125" customWidth="1"/>
+    <col min="14340" max="14340" width="0" hidden="1" customWidth="1"/>
+    <col min="14341" max="14341" width="7.140625" customWidth="1"/>
+    <col min="14342" max="14342" width="0" hidden="1" customWidth="1"/>
+    <col min="14343" max="14343" width="6.85546875" customWidth="1"/>
+    <col min="14344" max="14344" width="9.28515625" customWidth="1"/>
+    <col min="14345" max="14345" width="5.85546875" customWidth="1"/>
+    <col min="14346" max="14346" width="0" hidden="1" customWidth="1"/>
+    <col min="14347" max="14347" width="10" customWidth="1"/>
+    <col min="14348" max="14353" width="0" hidden="1" customWidth="1"/>
+    <col min="14575" max="14575" width="4.140625" customWidth="1"/>
+    <col min="14576" max="14576" width="15.5703125" customWidth="1"/>
+    <col min="14577" max="14577" width="7.28515625" customWidth="1"/>
+    <col min="14578" max="14578" width="4.85546875" customWidth="1"/>
+    <col min="14579" max="14579" width="4.42578125" customWidth="1"/>
+    <col min="14580" max="14585" width="0" hidden="1" customWidth="1"/>
+    <col min="14586" max="14586" width="9" customWidth="1"/>
+    <col min="14587" max="14587" width="4.85546875" customWidth="1"/>
+    <col min="14588" max="14589" width="0" hidden="1" customWidth="1"/>
+    <col min="14590" max="14591" width="4.85546875" customWidth="1"/>
+    <col min="14592" max="14592" width="6.140625" customWidth="1"/>
+    <col min="14593" max="14593" width="6.42578125" customWidth="1"/>
+    <col min="14594" max="14594" width="4.85546875" customWidth="1"/>
+    <col min="14595" max="14595" width="7.5703125" customWidth="1"/>
+    <col min="14596" max="14596" width="0" hidden="1" customWidth="1"/>
+    <col min="14597" max="14597" width="7.140625" customWidth="1"/>
+    <col min="14598" max="14598" width="0" hidden="1" customWidth="1"/>
+    <col min="14599" max="14599" width="6.85546875" customWidth="1"/>
+    <col min="14600" max="14600" width="9.28515625" customWidth="1"/>
+    <col min="14601" max="14601" width="5.85546875" customWidth="1"/>
+    <col min="14602" max="14602" width="0" hidden="1" customWidth="1"/>
+    <col min="14603" max="14603" width="10" customWidth="1"/>
+    <col min="14604" max="14609" width="0" hidden="1" customWidth="1"/>
+    <col min="14831" max="14831" width="4.140625" customWidth="1"/>
+    <col min="14832" max="14832" width="15.5703125" customWidth="1"/>
+    <col min="14833" max="14833" width="7.28515625" customWidth="1"/>
+    <col min="14834" max="14834" width="4.85546875" customWidth="1"/>
+    <col min="14835" max="14835" width="4.42578125" customWidth="1"/>
+    <col min="14836" max="14841" width="0" hidden="1" customWidth="1"/>
+    <col min="14842" max="14842" width="9" customWidth="1"/>
+    <col min="14843" max="14843" width="4.85546875" customWidth="1"/>
+    <col min="14844" max="14845" width="0" hidden="1" customWidth="1"/>
+    <col min="14846" max="14847" width="4.85546875" customWidth="1"/>
+    <col min="14848" max="14848" width="6.140625" customWidth="1"/>
+    <col min="14849" max="14849" width="6.42578125" customWidth="1"/>
+    <col min="14850" max="14850" width="4.85546875" customWidth="1"/>
+    <col min="14851" max="14851" width="7.5703125" customWidth="1"/>
+    <col min="14852" max="14852" width="0" hidden="1" customWidth="1"/>
+    <col min="14853" max="14853" width="7.140625" customWidth="1"/>
+    <col min="14854" max="14854" width="0" hidden="1" customWidth="1"/>
+    <col min="14855" max="14855" width="6.85546875" customWidth="1"/>
+    <col min="14856" max="14856" width="9.28515625" customWidth="1"/>
+    <col min="14857" max="14857" width="5.85546875" customWidth="1"/>
+    <col min="14858" max="14858" width="0" hidden="1" customWidth="1"/>
+    <col min="14859" max="14859" width="10" customWidth="1"/>
+    <col min="14860" max="14865" width="0" hidden="1" customWidth="1"/>
+    <col min="15087" max="15087" width="4.140625" customWidth="1"/>
+    <col min="15088" max="15088" width="15.5703125" customWidth="1"/>
+    <col min="15089" max="15089" width="7.28515625" customWidth="1"/>
+    <col min="15090" max="15090" width="4.85546875" customWidth="1"/>
+    <col min="15091" max="15091" width="4.42578125" customWidth="1"/>
+    <col min="15092" max="15097" width="0" hidden="1" customWidth="1"/>
+    <col min="15098" max="15098" width="9" customWidth="1"/>
+    <col min="15099" max="15099" width="4.85546875" customWidth="1"/>
+    <col min="15100" max="15101" width="0" hidden="1" customWidth="1"/>
+    <col min="15102" max="15103" width="4.85546875" customWidth="1"/>
+    <col min="15104" max="15104" width="6.140625" customWidth="1"/>
+    <col min="15105" max="15105" width="6.42578125" customWidth="1"/>
+    <col min="15106" max="15106" width="4.85546875" customWidth="1"/>
+    <col min="15107" max="15107" width="7.5703125" customWidth="1"/>
+    <col min="15108" max="15108" width="0" hidden="1" customWidth="1"/>
+    <col min="15109" max="15109" width="7.140625" customWidth="1"/>
+    <col min="15110" max="15110" width="0" hidden="1" customWidth="1"/>
+    <col min="15111" max="15111" width="6.85546875" customWidth="1"/>
+    <col min="15112" max="15112" width="9.28515625" customWidth="1"/>
+    <col min="15113" max="15113" width="5.85546875" customWidth="1"/>
+    <col min="15114" max="15114" width="0" hidden="1" customWidth="1"/>
+    <col min="15115" max="15115" width="10" customWidth="1"/>
+    <col min="15116" max="15121" width="0" hidden="1" customWidth="1"/>
+    <col min="15343" max="15343" width="4.140625" customWidth="1"/>
+    <col min="15344" max="15344" width="15.5703125" customWidth="1"/>
+    <col min="15345" max="15345" width="7.28515625" customWidth="1"/>
+    <col min="15346" max="15346" width="4.85546875" customWidth="1"/>
+    <col min="15347" max="15347" width="4.42578125" customWidth="1"/>
+    <col min="15348" max="15353" width="0" hidden="1" customWidth="1"/>
+    <col min="15354" max="15354" width="9" customWidth="1"/>
+    <col min="15355" max="15355" width="4.85546875" customWidth="1"/>
+    <col min="15356" max="15357" width="0" hidden="1" customWidth="1"/>
+    <col min="15358" max="15359" width="4.85546875" customWidth="1"/>
+    <col min="15360" max="15360" width="6.140625" customWidth="1"/>
+    <col min="15361" max="15361" width="6.42578125" customWidth="1"/>
+    <col min="15362" max="15362" width="4.85546875" customWidth="1"/>
+    <col min="15363" max="15363" width="7.5703125" customWidth="1"/>
+    <col min="15364" max="15364" width="0" hidden="1" customWidth="1"/>
+    <col min="15365" max="15365" width="7.140625" customWidth="1"/>
+    <col min="15366" max="15366" width="0" hidden="1" customWidth="1"/>
+    <col min="15367" max="15367" width="6.85546875" customWidth="1"/>
+    <col min="15368" max="15368" width="9.28515625" customWidth="1"/>
+    <col min="15369" max="15369" width="5.85546875" customWidth="1"/>
+    <col min="15370" max="15370" width="0" hidden="1" customWidth="1"/>
+    <col min="15371" max="15371" width="10" customWidth="1"/>
+    <col min="15372" max="15377" width="0" hidden="1" customWidth="1"/>
+    <col min="15599" max="15599" width="4.140625" customWidth="1"/>
+    <col min="15600" max="15600" width="15.5703125" customWidth="1"/>
+    <col min="15601" max="15601" width="7.28515625" customWidth="1"/>
+    <col min="15602" max="15602" width="4.85546875" customWidth="1"/>
+    <col min="15603" max="15603" width="4.42578125" customWidth="1"/>
+    <col min="15604" max="15609" width="0" hidden="1" customWidth="1"/>
+    <col min="15610" max="15610" width="9" customWidth="1"/>
+    <col min="15611" max="15611" width="4.85546875" customWidth="1"/>
+    <col min="15612" max="15613" width="0" hidden="1" customWidth="1"/>
+    <col min="15614" max="15615" width="4.85546875" customWidth="1"/>
+    <col min="15616" max="15616" width="6.140625" customWidth="1"/>
+    <col min="15617" max="15617" width="6.42578125" customWidth="1"/>
+    <col min="15618" max="15618" width="4.85546875" customWidth="1"/>
+    <col min="15619" max="15619" width="7.5703125" customWidth="1"/>
+    <col min="15620" max="15620" width="0" hidden="1" customWidth="1"/>
+    <col min="15621" max="15621" width="7.140625" customWidth="1"/>
+    <col min="15622" max="15622" width="0" hidden="1" customWidth="1"/>
+    <col min="15623" max="15623" width="6.85546875" customWidth="1"/>
+    <col min="15624" max="15624" width="9.28515625" customWidth="1"/>
+    <col min="15625" max="15625" width="5.85546875" customWidth="1"/>
+    <col min="15626" max="15626" width="0" hidden="1" customWidth="1"/>
+    <col min="15627" max="15627" width="10" customWidth="1"/>
+    <col min="15628" max="15633" width="0" hidden="1" customWidth="1"/>
+    <col min="15855" max="15855" width="4.140625" customWidth="1"/>
+    <col min="15856" max="15856" width="15.5703125" customWidth="1"/>
+    <col min="15857" max="15857" width="7.28515625" customWidth="1"/>
+    <col min="15858" max="15858" width="4.85546875" customWidth="1"/>
+    <col min="15859" max="15859" width="4.42578125" customWidth="1"/>
+    <col min="15860" max="15865" width="0" hidden="1" customWidth="1"/>
+    <col min="15866" max="15866" width="9" customWidth="1"/>
+    <col min="15867" max="15867" width="4.85546875" customWidth="1"/>
+    <col min="15868" max="15869" width="0" hidden="1" customWidth="1"/>
+    <col min="15870" max="15871" width="4.85546875" customWidth="1"/>
+    <col min="15872" max="15872" width="6.140625" customWidth="1"/>
+    <col min="15873" max="15873" width="6.42578125" customWidth="1"/>
+    <col min="15874" max="15874" width="4.85546875" customWidth="1"/>
+    <col min="15875" max="15875" width="7.5703125" customWidth="1"/>
+    <col min="15876" max="15876" width="0" hidden="1" customWidth="1"/>
+    <col min="15877" max="15877" width="7.140625" customWidth="1"/>
+    <col min="15878" max="15878" width="0" hidden="1" customWidth="1"/>
+    <col min="15879" max="15879" width="6.85546875" customWidth="1"/>
+    <col min="15880" max="15880" width="9.28515625" customWidth="1"/>
+    <col min="15881" max="15881" width="5.85546875" customWidth="1"/>
+    <col min="15882" max="15882" width="0" hidden="1" customWidth="1"/>
+    <col min="15883" max="15883" width="10" customWidth="1"/>
+    <col min="15884" max="15889" width="0" hidden="1" customWidth="1"/>
+    <col min="16111" max="16111" width="4.140625" customWidth="1"/>
+    <col min="16112" max="16112" width="15.5703125" customWidth="1"/>
+    <col min="16113" max="16113" width="7.28515625" customWidth="1"/>
+    <col min="16114" max="16114" width="4.85546875" customWidth="1"/>
+    <col min="16115" max="16115" width="4.42578125" customWidth="1"/>
+    <col min="16116" max="16121" width="0" hidden="1" customWidth="1"/>
+    <col min="16122" max="16122" width="9" customWidth="1"/>
+    <col min="16123" max="16123" width="4.85546875" customWidth="1"/>
+    <col min="16124" max="16125" width="0" hidden="1" customWidth="1"/>
+    <col min="16126" max="16127" width="4.85546875" customWidth="1"/>
+    <col min="16128" max="16128" width="6.140625" customWidth="1"/>
+    <col min="16129" max="16129" width="6.42578125" customWidth="1"/>
+    <col min="16130" max="16130" width="4.85546875" customWidth="1"/>
+    <col min="16131" max="16131" width="7.5703125" customWidth="1"/>
+    <col min="16132" max="16132" width="0" hidden="1" customWidth="1"/>
+    <col min="16133" max="16133" width="7.140625" customWidth="1"/>
+    <col min="16134" max="16134" width="0" hidden="1" customWidth="1"/>
+    <col min="16135" max="16135" width="6.85546875" customWidth="1"/>
+    <col min="16136" max="16136" width="9.28515625" customWidth="1"/>
+    <col min="16137" max="16137" width="5.85546875" customWidth="1"/>
+    <col min="16138" max="16138" width="0" hidden="1" customWidth="1"/>
+    <col min="16139" max="16139" width="10" customWidth="1"/>
+    <col min="16140" max="16145" width="0" hidden="1" customWidth="1"/>
+    <col min="16378" max="16384" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30 11518:16381" s="52" customFormat="1" ht="16.5">
+    <row r="1" spans="1:31 11519:16382" s="52" customFormat="1" ht="16.5">
       <c r="A1" s="116" t="s">
         <v>18</v>
       </c>
@@ -29420,14 +29426,14 @@
       <c r="O1" s="46"/>
       <c r="P1" s="46"/>
       <c r="Q1" s="46"/>
-      <c r="R1" s="48"/>
+      <c r="R1" s="46"/>
       <c r="S1" s="48"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="49"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="50"/>
-      <c r="X1" s="51"/>
-      <c r="PZZ1"/>
+      <c r="T1" s="48"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="50"/>
+      <c r="Y1" s="51"/>
       <c r="QAA1"/>
       <c r="QAB1"/>
       <c r="QAC1"/>
@@ -34291,8 +34297,9 @@
       <c r="XEY1"/>
       <c r="XEZ1"/>
       <c r="XFA1"/>
+      <c r="XFB1"/>
     </row>
-    <row r="2" spans="1:30 11518:16381" s="52" customFormat="1" ht="16.5">
+    <row r="2" spans="1:31 11519:16382" s="52" customFormat="1" ht="16.5">
       <c r="A2" s="113" t="s">
         <v>19</v>
       </c>
@@ -34300,16 +34307,16 @@
       <c r="C2" s="53"/>
       <c r="L2" s="113"/>
       <c r="M2" s="113"/>
-      <c r="N2" s="114" t="s">
+      <c r="N2" s="113"/>
+      <c r="O2" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="113"/>
-      <c r="R2" s="54"/>
+      <c r="P2" s="113"/>
       <c r="S2" s="54"/>
-      <c r="U2" s="55"/>
-      <c r="W2" s="50"/>
-      <c r="X2" s="51"/>
-      <c r="PZZ2"/>
+      <c r="T2" s="54"/>
+      <c r="V2" s="55"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="51"/>
       <c r="QAA2"/>
       <c r="QAB2"/>
       <c r="QAC2"/>
@@ -39173,21 +39180,22 @@
       <c r="XEY2"/>
       <c r="XEZ2"/>
       <c r="XFA2"/>
+      <c r="XFB2"/>
     </row>
-    <row r="3" spans="1:30 11518:16381" s="52" customFormat="1" ht="16.5">
+    <row r="3" spans="1:31 11519:16382" s="52" customFormat="1" ht="16.5">
       <c r="C3" s="53"/>
       <c r="L3" s="113"/>
       <c r="M3" s="113"/>
-      <c r="N3" s="114" t="s">
+      <c r="N3" s="113"/>
+      <c r="O3" s="114" t="s">
         <v>59</v>
       </c>
-      <c r="O3" s="113"/>
-      <c r="R3" s="54"/>
+      <c r="P3" s="113"/>
       <c r="S3" s="54"/>
-      <c r="U3" s="55"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="51"/>
-      <c r="PZZ3"/>
+      <c r="T3" s="54"/>
+      <c r="V3" s="55"/>
+      <c r="X3" s="50"/>
+      <c r="Y3" s="51"/>
       <c r="QAA3"/>
       <c r="QAB3"/>
       <c r="QAC3"/>
@@ -44051,169 +44059,175 @@
       <c r="XEY3"/>
       <c r="XEZ3"/>
       <c r="XFA3"/>
+      <c r="XFB3"/>
     </row>
-    <row r="4" spans="1:30 11518:16381" ht="13.5" customHeight="1"/>
-    <row r="5" spans="1:30 11518:16381" ht="22.5" customHeight="1">
-      <c r="A5" s="151" t="s">
+    <row r="4" spans="1:31 11519:16382" ht="13.5" customHeight="1"/>
+    <row r="5" spans="1:31 11519:16382" ht="22.5" customHeight="1">
+      <c r="A5" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="151" t="s">
+      <c r="B5" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="151" t="s">
+      <c r="C5" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="151" t="s">
+      <c r="D5" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="151"/>
-      <c r="F5" s="153" t="s">
+      <c r="E5" s="127"/>
+      <c r="F5" s="142" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="169" t="s">
+      <c r="G5" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="176"/>
-      <c r="I5" s="176"/>
-      <c r="J5" s="176"/>
-      <c r="K5" s="176"/>
-      <c r="L5" s="170"/>
-      <c r="M5" s="172" t="s">
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="126"/>
+      <c r="N5" s="136" t="s">
         <v>47</v>
       </c>
-      <c r="N5" s="173"/>
-      <c r="O5" s="173"/>
-      <c r="P5" s="173"/>
-      <c r="Q5" s="173"/>
-      <c r="R5" s="173"/>
-      <c r="S5" s="174"/>
-      <c r="T5" s="151" t="s">
+      <c r="O5" s="137"/>
+      <c r="P5" s="137"/>
+      <c r="Q5" s="137"/>
+      <c r="R5" s="137"/>
+      <c r="S5" s="137"/>
+      <c r="T5" s="138"/>
+      <c r="U5" s="127" t="s">
         <v>24</v>
       </c>
-      <c r="U5" s="169" t="s">
+      <c r="V5" s="133" t="s">
         <v>25</v>
       </c>
-      <c r="V5" s="170"/>
-      <c r="W5" s="171" t="s">
+      <c r="W5" s="134"/>
+      <c r="X5" s="135" t="s">
         <v>26</v>
       </c>
-      <c r="X5" s="137" t="s">
+      <c r="Y5" s="165" t="s">
         <v>27</v>
       </c>
-      <c r="Y5" s="165" t="s">
+      <c r="Z5" s="128" t="s">
         <v>60</v>
       </c>
-      <c r="Z5" s="166" t="s">
+      <c r="AA5" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="AA5" s="154" t="s">
+      <c r="AB5" s="158" t="s">
         <v>58</v>
       </c>
-      <c r="AB5" s="157" t="s">
+      <c r="AC5" s="161" t="s">
         <v>62</v>
       </c>
-      <c r="AC5" s="154" t="s">
+      <c r="AD5" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="AD5" s="145" t="s">
+      <c r="AE5" s="154" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:30 11518:16381" ht="34.5" customHeight="1">
-      <c r="A6" s="151"/>
-      <c r="B6" s="151"/>
-      <c r="C6" s="151"/>
-      <c r="D6" s="151"/>
-      <c r="E6" s="151"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="153" t="s">
+    <row r="6" spans="1:31 11519:16382" ht="34.5" customHeight="1">
+      <c r="A6" s="127"/>
+      <c r="B6" s="127"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="143"/>
+      <c r="G6" s="142" t="s">
         <v>46</v>
       </c>
-      <c r="H6" s="153" t="s">
+      <c r="H6" s="142" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="153" t="s">
+      <c r="I6" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="J6" s="153" t="s">
+      <c r="J6" s="142" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="153" t="s">
+      <c r="K6" s="142" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="153" t="s">
+      <c r="L6" s="142" t="s">
         <v>29</v>
       </c>
-      <c r="M6" s="151" t="s">
+      <c r="M6" s="142" t="s">
+        <v>64</v>
+      </c>
+      <c r="N6" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="152" t="s">
+      <c r="O6" s="132" t="s">
         <v>48</v>
       </c>
-      <c r="O6" s="152" t="s">
+      <c r="P6" s="132" t="s">
         <v>54</v>
       </c>
-      <c r="P6" s="167" t="s">
+      <c r="Q6" s="130" t="s">
         <v>10</v>
       </c>
-      <c r="Q6" s="152" t="s">
+      <c r="R6" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="R6" s="177" t="s">
+      <c r="S6" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="S6" s="175" t="s">
+      <c r="T6" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="T6" s="151"/>
-      <c r="U6" s="151" t="s">
+      <c r="U6" s="127"/>
+      <c r="V6" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="V6" s="151" t="s">
+      <c r="W6" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="W6" s="171"/>
-      <c r="X6" s="137"/>
+      <c r="X6" s="135"/>
       <c r="Y6" s="165"/>
-      <c r="Z6" s="166"/>
-      <c r="AA6" s="155"/>
-      <c r="AB6" s="158"/>
-      <c r="AC6" s="155"/>
-      <c r="AD6" s="146"/>
+      <c r="Z6" s="128"/>
+      <c r="AA6" s="129"/>
+      <c r="AB6" s="159"/>
+      <c r="AC6" s="162"/>
+      <c r="AD6" s="159"/>
+      <c r="AE6" s="155"/>
     </row>
-    <row r="7" spans="1:30 11518:16381" ht="34.5" customHeight="1">
-      <c r="A7" s="151"/>
-      <c r="B7" s="151"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="151"/>
-      <c r="E7" s="151"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="152"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="152"/>
-      <c r="L7" s="152"/>
-      <c r="M7" s="151"/>
-      <c r="N7" s="151"/>
-      <c r="O7" s="151"/>
-      <c r="P7" s="168"/>
-      <c r="Q7" s="151"/>
-      <c r="R7" s="167"/>
-      <c r="S7" s="167"/>
-      <c r="T7" s="151"/>
-      <c r="U7" s="151"/>
-      <c r="V7" s="151"/>
-      <c r="W7" s="171"/>
-      <c r="X7" s="137"/>
+    <row r="7" spans="1:31 11519:16382" ht="34.5" customHeight="1">
+      <c r="A7" s="127"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="132"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="132"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="132"/>
+      <c r="M7" s="132"/>
+      <c r="N7" s="127"/>
+      <c r="O7" s="127"/>
+      <c r="P7" s="127"/>
+      <c r="Q7" s="131"/>
+      <c r="R7" s="127"/>
+      <c r="S7" s="130"/>
+      <c r="T7" s="130"/>
+      <c r="U7" s="127"/>
+      <c r="V7" s="127"/>
+      <c r="W7" s="127"/>
+      <c r="X7" s="135"/>
       <c r="Y7" s="165"/>
-      <c r="Z7" s="166"/>
-      <c r="AA7" s="156"/>
-      <c r="AB7" s="159"/>
-      <c r="AC7" s="156"/>
-      <c r="AD7" s="147"/>
+      <c r="Z7" s="128"/>
+      <c r="AA7" s="129"/>
+      <c r="AB7" s="160"/>
+      <c r="AC7" s="163"/>
+      <c r="AD7" s="160"/>
+      <c r="AE7" s="156"/>
     </row>
-    <row r="8" spans="1:30 11518:16381" ht="15.75" customHeight="1">
+    <row r="8" spans="1:31 11519:16382" ht="15.75" customHeight="1">
       <c r="A8" s="58">
         <v>1</v>
       </c>
@@ -44223,10 +44237,10 @@
       <c r="C8" s="58">
         <v>3</v>
       </c>
-      <c r="D8" s="164">
+      <c r="D8" s="150">
         <v>4</v>
       </c>
-      <c r="E8" s="164"/>
+      <c r="E8" s="150"/>
       <c r="F8" s="69"/>
       <c r="G8" s="69">
         <v>5</v>
@@ -44246,75 +44260,76 @@
       <c r="L8" s="69">
         <v>10</v>
       </c>
-      <c r="M8" s="69">
+      <c r="M8" s="69"/>
+      <c r="N8" s="69">
         <v>11</v>
       </c>
-      <c r="N8" s="69">
+      <c r="O8" s="69">
         <v>12</v>
       </c>
-      <c r="O8" s="69">
+      <c r="P8" s="69">
         <v>13</v>
       </c>
-      <c r="P8" s="83">
+      <c r="Q8" s="83">
         <v>14</v>
       </c>
-      <c r="Q8" s="69">
+      <c r="R8" s="69">
         <v>15</v>
       </c>
-      <c r="R8" s="83">
+      <c r="S8" s="83">
         <v>16</v>
       </c>
-      <c r="S8" s="83">
+      <c r="T8" s="83">
         <v>17</v>
       </c>
-      <c r="T8" s="83">
+      <c r="U8" s="83">
         <v>18</v>
       </c>
-      <c r="U8" s="83">
+      <c r="V8" s="83">
         <v>19</v>
       </c>
-      <c r="V8" s="83">
+      <c r="W8" s="83">
         <v>20</v>
       </c>
-      <c r="W8" s="83">
+      <c r="X8" s="83">
         <v>21</v>
       </c>
-      <c r="X8" s="84">
+      <c r="Y8" s="84">
         <v>22</v>
       </c>
-      <c r="Y8" s="102">
+      <c r="Z8" s="102">
         <v>23</v>
       </c>
-      <c r="Z8" s="71">
+      <c r="AA8" s="71">
         <v>24</v>
       </c>
-      <c r="AA8" s="70" t="s">
+      <c r="AB8" s="70" t="s">
         <v>50</v>
       </c>
-      <c r="AB8" s="71" t="s">
+      <c r="AC8" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="AC8" s="94" t="s">
+      <c r="AD8" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="AD8" s="99" t="s">
+      <c r="AE8" s="99" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:30 11518:16381" ht="15.6" customHeight="1">
-      <c r="A9" s="139">
+    <row r="9" spans="1:31 11519:16382" ht="15.6" customHeight="1">
+      <c r="A9" s="144">
         <v>1</v>
       </c>
-      <c r="B9" s="138">
+      <c r="B9" s="145">
         <f>'Bang TH nop'!B9</f>
         <v>0</v>
       </c>
-      <c r="C9" s="163">
+      <c r="C9" s="146">
         <f>'Bang TH nop'!C9</f>
         <v>0</v>
       </c>
-      <c r="D9" s="149"/>
-      <c r="E9" s="150"/>
+      <c r="D9" s="147"/>
+      <c r="E9" s="148"/>
       <c r="F9" s="110"/>
       <c r="G9" s="77">
         <f>'Bang TH nop'!F9</f>
@@ -44343,34 +44358,35 @@
       <c r="M9" s="85"/>
       <c r="N9" s="85"/>
       <c r="O9" s="85"/>
-      <c r="P9" s="86"/>
-      <c r="Q9" s="85"/>
-      <c r="R9" s="86">
+      <c r="P9" s="85"/>
+      <c r="Q9" s="86"/>
+      <c r="R9" s="85"/>
+      <c r="S9" s="86">
         <f>'Bang TH nop'!L9</f>
         <v>0</v>
       </c>
-      <c r="S9" s="86"/>
       <c r="T9" s="86"/>
       <c r="U9" s="86"/>
       <c r="V9" s="86"/>
       <c r="W9" s="86"/>
-      <c r="X9" s="104"/>
-      <c r="Y9" s="103"/>
-      <c r="Z9" s="72"/>
-      <c r="AA9" s="73"/>
-      <c r="AB9" s="74"/>
-      <c r="AC9" s="73"/>
-      <c r="AD9" s="93"/>
+      <c r="X9" s="86"/>
+      <c r="Y9" s="104"/>
+      <c r="Z9" s="103"/>
+      <c r="AA9" s="72"/>
+      <c r="AB9" s="73"/>
+      <c r="AC9" s="74"/>
+      <c r="AD9" s="73"/>
+      <c r="AE9" s="93"/>
     </row>
-    <row r="10" spans="1:30 11518:16381" ht="15.6" customHeight="1">
-      <c r="A10" s="139"/>
-      <c r="B10" s="138"/>
-      <c r="C10" s="163"/>
-      <c r="D10" s="140">
+    <row r="10" spans="1:31 11519:16382" ht="15.6" customHeight="1">
+      <c r="A10" s="144"/>
+      <c r="B10" s="145"/>
+      <c r="C10" s="146"/>
+      <c r="D10" s="149">
         <f>+'Bang TH nop'!D9</f>
         <v>0</v>
       </c>
-      <c r="E10" s="150"/>
+      <c r="E10" s="148"/>
       <c r="F10" s="111">
         <f>+'Bang TH nop'!E9</f>
         <v>0</v>
@@ -44400,86 +44416,90 @@
         <v>0</v>
       </c>
       <c r="M10" s="79">
+        <f>+F10/26*M9*60%</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="79">
         <f>'Bang TH nop'!O9</f>
         <v>0</v>
       </c>
-      <c r="N10" s="76">
+      <c r="O10" s="76">
         <f>'Bang TH nop'!N9</f>
         <v>0</v>
       </c>
-      <c r="O10" s="76">
+      <c r="P10" s="76">
         <f>+'Bang TH nop'!S9</f>
         <v>0</v>
       </c>
-      <c r="P10" s="87">
+      <c r="Q10" s="87">
         <f>'Bang TH nop'!M9</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="87">
+      <c r="R10" s="87">
         <f>+'Bang TH nop'!Q9+'Bang TH nop'!P9</f>
         <v>0</v>
       </c>
-      <c r="R10" s="59">
-        <f>+R9*15000</f>
+      <c r="S10" s="59">
+        <f>+S9*15000</f>
         <v>0</v>
       </c>
-      <c r="S10" s="59"/>
-      <c r="T10" s="59">
-        <f>SUM(G10:R10)</f>
+      <c r="T10" s="59"/>
+      <c r="U10" s="59">
+        <f>SUM(G10:S10)</f>
         <v>0</v>
       </c>
-      <c r="U10" s="76"/>
-      <c r="V10" s="76">
+      <c r="V10" s="76"/>
+      <c r="W10" s="76">
         <f>+ROUND(D10*0.5%,-3)</f>
         <v>0</v>
       </c>
-      <c r="W10" s="59">
-        <f>ROUND(T10-U10-V10,-2)</f>
+      <c r="X10" s="59">
+        <f>ROUND(U10-V10-W10,-2)</f>
         <v>0</v>
       </c>
-      <c r="X10" s="105">
+      <c r="Y10" s="105">
         <f>+'Bang TH nop'!F9+'Bang TH nop'!H9+'Bang TH nop'!R9</f>
         <v>0</v>
       </c>
-      <c r="Y10" s="103">
+      <c r="Z10" s="103">
         <f>+IFERROR(VLOOKUP(C9,'[1]Bản gốc T03'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="75">
+      <c r="AA10" s="75">
         <f>+IFERROR(VLOOKUP(C9,'[1]Bản gốc T03'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="95" t="e">
-        <f>+Z10/Y10</f>
+      <c r="AB10" s="95" t="e">
+        <f>+AA10/Z10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB10" s="95" t="e">
-        <f>AD10/X10</f>
+      <c r="AC10" s="95" t="e">
+        <f>AE10/Y10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC10" s="96" t="e">
-        <f>+AB10/AA10</f>
+      <c r="AD10" s="96" t="e">
+        <f>+AC10/AB10</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD10" s="93">
-        <f>+T10-J10</f>
+      <c r="AE10" s="93">
+        <f>+U10-J10</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:30 11518:16381" ht="15.6" customHeight="1">
-      <c r="A11" s="139">
+    <row r="11" spans="1:31 11519:16382" ht="15.6" customHeight="1">
+      <c r="A11" s="144">
         <v>2</v>
       </c>
-      <c r="B11" s="138">
+      <c r="B11" s="145">
         <f>'Bang TH nop'!B11</f>
         <v>0</v>
       </c>
-      <c r="C11" s="163">
+      <c r="C11" s="146">
         <f>'Bang TH nop'!C11</f>
         <v>0</v>
       </c>
-      <c r="D11" s="149"/>
-      <c r="E11" s="150"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="148"/>
       <c r="F11" s="110"/>
       <c r="G11" s="77">
         <f>'Bang TH nop'!F11</f>
@@ -44508,34 +44528,35 @@
       <c r="M11" s="85"/>
       <c r="N11" s="85"/>
       <c r="O11" s="85"/>
-      <c r="P11" s="86"/>
-      <c r="Q11" s="85"/>
-      <c r="R11" s="86">
+      <c r="P11" s="85"/>
+      <c r="Q11" s="86"/>
+      <c r="R11" s="85"/>
+      <c r="S11" s="86">
         <f>'Bang TH nop'!L11</f>
         <v>0</v>
       </c>
-      <c r="S11" s="86"/>
       <c r="T11" s="86"/>
       <c r="U11" s="86"/>
       <c r="V11" s="86"/>
       <c r="W11" s="86"/>
-      <c r="X11" s="104"/>
-      <c r="Y11" s="103"/>
-      <c r="Z11" s="72"/>
-      <c r="AA11" s="73"/>
-      <c r="AB11" s="74"/>
-      <c r="AC11" s="73"/>
-      <c r="AD11" s="93"/>
+      <c r="X11" s="86"/>
+      <c r="Y11" s="104"/>
+      <c r="Z11" s="103"/>
+      <c r="AA11" s="72"/>
+      <c r="AB11" s="73"/>
+      <c r="AC11" s="74"/>
+      <c r="AD11" s="73"/>
+      <c r="AE11" s="93"/>
     </row>
-    <row r="12" spans="1:30 11518:16381" ht="15.6" customHeight="1">
-      <c r="A12" s="139"/>
-      <c r="B12" s="138"/>
-      <c r="C12" s="163"/>
-      <c r="D12" s="140">
+    <row r="12" spans="1:31 11519:16382" ht="15.6" customHeight="1">
+      <c r="A12" s="144"/>
+      <c r="B12" s="145"/>
+      <c r="C12" s="146"/>
+      <c r="D12" s="149">
         <f>+'Bang TH nop'!D11</f>
         <v>0</v>
       </c>
-      <c r="E12" s="150"/>
+      <c r="E12" s="148"/>
       <c r="F12" s="111">
         <f>+'Bang TH nop'!E11</f>
         <v>0</v>
@@ -44561,90 +44582,94 @@
         <v>0</v>
       </c>
       <c r="L12" s="79">
-        <f t="shared" ref="L12" si="5">F12*L11/(26)*30%</f>
+        <f>F12*L11/(26)*30%</f>
         <v>0</v>
       </c>
       <c r="M12" s="79">
+        <f>+F12/26*M11*60%</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="79">
         <f>'Bang TH nop'!O11</f>
         <v>0</v>
       </c>
-      <c r="N12" s="76">
+      <c r="O12" s="76">
         <f>'Bang TH nop'!N11</f>
         <v>0</v>
       </c>
-      <c r="O12" s="76">
+      <c r="P12" s="76">
         <f>+'Bang TH nop'!S11</f>
         <v>0</v>
       </c>
-      <c r="P12" s="87">
+      <c r="Q12" s="87">
         <f>'Bang TH nop'!M11</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="87">
+      <c r="R12" s="87">
         <f>+'Bang TH nop'!Q11+'Bang TH nop'!P11</f>
         <v>0</v>
       </c>
-      <c r="R12" s="59">
-        <f t="shared" ref="R12" si="6">+R11*15000</f>
+      <c r="S12" s="59">
+        <f t="shared" ref="S12" si="5">+S11*15000</f>
         <v>0</v>
       </c>
-      <c r="S12" s="59"/>
-      <c r="T12" s="59">
-        <f>SUM(G12:R12)</f>
+      <c r="T12" s="59"/>
+      <c r="U12" s="59">
+        <f>SUM(G12:S12)</f>
         <v>0</v>
       </c>
-      <c r="U12" s="76"/>
-      <c r="V12" s="76">
-        <f t="shared" ref="V12" si="7">+ROUND(D12*0.5%,-3)</f>
+      <c r="V12" s="76"/>
+      <c r="W12" s="76">
+        <f>+ROUND(D12*0.5%,-3)</f>
         <v>0</v>
       </c>
-      <c r="W12" s="59">
-        <f t="shared" ref="W12" si="8">ROUND(T12-U12-V12,-2)</f>
+      <c r="X12" s="59">
+        <f t="shared" ref="X12" si="6">ROUND(U12-V12-W12,-2)</f>
         <v>0</v>
       </c>
-      <c r="X12" s="105">
+      <c r="Y12" s="105">
         <f>+'Bang TH nop'!F11+'Bang TH nop'!H11+'Bang TH nop'!R11</f>
         <v>0</v>
       </c>
-      <c r="Y12" s="103">
+      <c r="Z12" s="103">
         <f>+IFERROR(VLOOKUP(C11,'[1]Bản gốc T03'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z12" s="75">
+      <c r="AA12" s="75">
         <f>+IFERROR(VLOOKUP(C11,'[1]Bản gốc T03'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA12" s="95" t="e">
-        <f t="shared" ref="AA12" si="9">+Z12/Y12</f>
+      <c r="AB12" s="95" t="e">
+        <f t="shared" ref="AB12" si="7">+AA12/Z12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB12" s="95" t="e">
-        <f t="shared" ref="AB12" si="10">AD12/X12</f>
+      <c r="AC12" s="95" t="e">
+        <f t="shared" ref="AC12" si="8">AE12/Y12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC12" s="96" t="e">
-        <f t="shared" ref="AC12" si="11">+AB12/AA12</f>
+      <c r="AD12" s="96" t="e">
+        <f t="shared" ref="AD12" si="9">+AC12/AB12</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD12" s="115">
-        <f>+T12-J12</f>
+      <c r="AE12" s="115">
+        <f>+U12-J12</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:30 11518:16381" ht="15.6" customHeight="1">
-      <c r="A13" s="139">
+    <row r="13" spans="1:31 11519:16382" ht="15.6" customHeight="1">
+      <c r="A13" s="144">
         <v>3</v>
       </c>
-      <c r="B13" s="138">
+      <c r="B13" s="145">
         <f>'Bang TH nop'!B13</f>
         <v>0</v>
       </c>
-      <c r="C13" s="163">
+      <c r="C13" s="146">
         <f>'Bang TH nop'!C13</f>
         <v>0</v>
       </c>
-      <c r="D13" s="149"/>
-      <c r="E13" s="150"/>
+      <c r="D13" s="147"/>
+      <c r="E13" s="148"/>
       <c r="F13" s="110"/>
       <c r="G13" s="77">
         <f>'Bang TH nop'!F13</f>
@@ -44673,146 +44698,148 @@
       <c r="M13" s="85"/>
       <c r="N13" s="85"/>
       <c r="O13" s="85"/>
-      <c r="P13" s="86"/>
-      <c r="Q13" s="85"/>
-      <c r="R13" s="86">
+      <c r="P13" s="85"/>
+      <c r="Q13" s="86"/>
+      <c r="R13" s="85"/>
+      <c r="S13" s="86">
         <f>'Bang TH nop'!L13</f>
         <v>0</v>
       </c>
-      <c r="S13" s="86"/>
       <c r="T13" s="86"/>
       <c r="U13" s="86"/>
       <c r="V13" s="86"/>
       <c r="W13" s="86"/>
-      <c r="X13" s="104"/>
-      <c r="Y13" s="103"/>
-      <c r="Z13" s="72"/>
-      <c r="AA13" s="73"/>
-      <c r="AB13" s="74"/>
-      <c r="AC13" s="73"/>
-      <c r="AD13" s="93"/>
+      <c r="X13" s="86"/>
+      <c r="Y13" s="104"/>
+      <c r="Z13" s="103"/>
+      <c r="AA13" s="72"/>
+      <c r="AB13" s="73"/>
+      <c r="AC13" s="74"/>
+      <c r="AD13" s="73"/>
+      <c r="AE13" s="93"/>
     </row>
-    <row r="14" spans="1:30 11518:16381" ht="15.6" customHeight="1">
-      <c r="A14" s="139"/>
-      <c r="B14" s="138"/>
-      <c r="C14" s="163"/>
-      <c r="D14" s="140">
+    <row r="14" spans="1:31 11519:16382" ht="15.6" customHeight="1">
+      <c r="A14" s="144"/>
+      <c r="B14" s="145"/>
+      <c r="C14" s="146"/>
+      <c r="D14" s="149">
         <f>+'Bang TH nop'!D13</f>
         <v>0</v>
       </c>
-      <c r="E14" s="150"/>
+      <c r="E14" s="148"/>
       <c r="F14" s="111">
         <f>+'Bang TH nop'!E13</f>
         <v>0</v>
       </c>
       <c r="G14" s="78">
-        <f t="shared" ref="G14" si="12">F14/26*G13</f>
+        <f t="shared" ref="G14" si="10">F14/26*G13</f>
         <v>0</v>
       </c>
       <c r="H14" s="60">
-        <f t="shared" ref="H14" si="13">+(F14/26/8*150%)*H13</f>
+        <f t="shared" ref="H14" si="11">+(F14/26/8*150%)*H13</f>
         <v>0</v>
       </c>
       <c r="I14" s="81">
-        <f t="shared" ref="I14" si="14">ROUND(D14/26*I13,)</f>
+        <f t="shared" ref="I14" si="12">ROUND(D14/26*I13,)</f>
         <v>0</v>
       </c>
       <c r="J14" s="81">
-        <f t="shared" ref="J14" si="15">ROUND(F14/26*J13,)*4</f>
+        <f t="shared" ref="J14" si="13">ROUND(F14/26*J13,)*4</f>
         <v>0</v>
       </c>
       <c r="K14" s="81">
-        <f t="shared" ref="K14" si="16">+F14/26*K13*2</f>
+        <f t="shared" ref="K14" si="14">+F14/26*K13*2</f>
         <v>0</v>
       </c>
       <c r="L14" s="79">
-        <f t="shared" ref="L14" si="17">F14*L13/(26)*30%</f>
+        <f>F14*L13/(26)*30%</f>
         <v>0</v>
       </c>
       <c r="M14" s="79">
+        <f>+F14/26*M13*60%</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="79">
         <f>'Bang TH nop'!O13</f>
         <v>0</v>
       </c>
-      <c r="N14" s="76">
+      <c r="O14" s="76">
         <f>'Bang TH nop'!N13</f>
         <v>0</v>
       </c>
-      <c r="O14" s="76">
+      <c r="P14" s="76">
         <f>+'Bang TH nop'!S13</f>
         <v>0</v>
       </c>
-      <c r="P14" s="87">
+      <c r="Q14" s="87">
         <f>'Bang TH nop'!M13</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="87">
+      <c r="R14" s="87">
         <f>+'Bang TH nop'!Q13+'Bang TH nop'!P13</f>
         <v>0</v>
       </c>
-      <c r="R14" s="59">
-        <f t="shared" ref="R14" si="18">+R13*15000</f>
+      <c r="S14" s="59">
+        <f t="shared" ref="S14" si="15">+S13*15000</f>
         <v>0</v>
       </c>
-      <c r="S14" s="59"/>
-      <c r="T14" s="59">
-        <f>SUM(G14:R14)</f>
+      <c r="T14" s="59"/>
+      <c r="U14" s="59">
+        <f>SUM(G14:S14)</f>
         <v>0</v>
       </c>
-      <c r="U14" s="76">
-        <f>D10*10.5%</f>
+      <c r="V14" s="76"/>
+      <c r="W14" s="76">
+        <f>+ROUND(D14*0.5%,-3)</f>
         <v>0</v>
       </c>
-      <c r="V14" s="76">
-        <f t="shared" ref="V14" si="19">+ROUND(D14*0.5%,-3)</f>
+      <c r="X14" s="59">
+        <f t="shared" ref="X14" si="16">ROUND(U14-V14-W14,-2)</f>
         <v>0</v>
       </c>
-      <c r="W14" s="59">
-        <f t="shared" ref="W14" si="20">ROUND(T14-U14-V14,-2)</f>
-        <v>0</v>
-      </c>
-      <c r="X14" s="105">
+      <c r="Y14" s="105">
         <f>+'Bang TH nop'!F13+'Bang TH nop'!H13+'Bang TH nop'!R13</f>
         <v>0</v>
       </c>
-      <c r="Y14" s="103">
+      <c r="Z14" s="103">
         <f>+IFERROR(VLOOKUP(C13,'[1]Bản gốc T03'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z14" s="75">
+      <c r="AA14" s="75">
         <f>+IFERROR(VLOOKUP(C13,'[1]Bản gốc T03'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA14" s="95" t="e">
-        <f t="shared" ref="AA14" si="21">+Z14/Y14</f>
+      <c r="AB14" s="95" t="e">
+        <f t="shared" ref="AB14" si="17">+AA14/Z14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB14" s="95" t="e">
-        <f t="shared" ref="AB14" si="22">AD14/X14</f>
+      <c r="AC14" s="95" t="e">
+        <f t="shared" ref="AC14" si="18">AE14/Y14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC14" s="96" t="e">
-        <f t="shared" ref="AC14" si="23">+AB14/AA14</f>
+      <c r="AD14" s="96" t="e">
+        <f t="shared" ref="AD14" si="19">+AC14/AB14</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD14" s="93">
-        <f>+T14-J14</f>
+      <c r="AE14" s="93">
+        <f>+U14-J14</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:30 11518:16381" ht="15.6" customHeight="1">
-      <c r="A15" s="139">
+    <row r="15" spans="1:31 11519:16382" ht="15.6" customHeight="1">
+      <c r="A15" s="144">
         <v>4</v>
       </c>
-      <c r="B15" s="138">
+      <c r="B15" s="145">
         <f>'Bang TH nop'!B15</f>
         <v>0</v>
       </c>
-      <c r="C15" s="163">
+      <c r="C15" s="146">
         <f>'Bang TH nop'!C15</f>
         <v>0</v>
       </c>
-      <c r="D15" s="149"/>
-      <c r="E15" s="150"/>
+      <c r="D15" s="147"/>
+      <c r="E15" s="148"/>
       <c r="F15" s="110"/>
       <c r="G15" s="77">
         <f>'Bang TH nop'!F15</f>
@@ -44841,146 +44868,148 @@
       <c r="M15" s="85"/>
       <c r="N15" s="85"/>
       <c r="O15" s="85"/>
-      <c r="P15" s="86"/>
-      <c r="Q15" s="85"/>
-      <c r="R15" s="86">
+      <c r="P15" s="85"/>
+      <c r="Q15" s="86"/>
+      <c r="R15" s="85"/>
+      <c r="S15" s="86">
         <f>'Bang TH nop'!L15</f>
         <v>0</v>
       </c>
-      <c r="S15" s="86"/>
       <c r="T15" s="86"/>
       <c r="U15" s="86"/>
       <c r="V15" s="86"/>
       <c r="W15" s="86"/>
-      <c r="X15" s="104"/>
-      <c r="Y15" s="103"/>
-      <c r="Z15" s="72"/>
-      <c r="AA15" s="73"/>
-      <c r="AB15" s="74"/>
-      <c r="AC15" s="73"/>
-      <c r="AD15" s="93"/>
+      <c r="X15" s="86"/>
+      <c r="Y15" s="104"/>
+      <c r="Z15" s="103"/>
+      <c r="AA15" s="72"/>
+      <c r="AB15" s="73"/>
+      <c r="AC15" s="74"/>
+      <c r="AD15" s="73"/>
+      <c r="AE15" s="93"/>
     </row>
-    <row r="16" spans="1:30 11518:16381" ht="15.6" customHeight="1">
-      <c r="A16" s="139"/>
-      <c r="B16" s="138"/>
-      <c r="C16" s="163"/>
-      <c r="D16" s="140">
+    <row r="16" spans="1:31 11519:16382" ht="15.6" customHeight="1">
+      <c r="A16" s="144"/>
+      <c r="B16" s="145"/>
+      <c r="C16" s="146"/>
+      <c r="D16" s="149">
         <f>+'Bang TH nop'!D15</f>
         <v>0</v>
       </c>
-      <c r="E16" s="150"/>
+      <c r="E16" s="148"/>
       <c r="F16" s="111">
         <f>+'Bang TH nop'!E15</f>
         <v>0</v>
       </c>
       <c r="G16" s="78">
-        <f t="shared" ref="G16" si="24">F16/26*G15</f>
+        <f t="shared" ref="G16" si="20">F16/26*G15</f>
         <v>0</v>
       </c>
       <c r="H16" s="60">
-        <f t="shared" ref="H16" si="25">+(F16/26/8*150%)*H15</f>
+        <f t="shared" ref="H16" si="21">+(F16/26/8*150%)*H15</f>
         <v>0</v>
       </c>
       <c r="I16" s="81">
-        <f t="shared" ref="I16" si="26">ROUND(D16/26*I15,)</f>
+        <f t="shared" ref="I16" si="22">ROUND(D16/26*I15,)</f>
         <v>0</v>
       </c>
       <c r="J16" s="81">
-        <f t="shared" ref="J16" si="27">ROUND(F16/26*J15,)*4</f>
+        <f t="shared" ref="J16" si="23">ROUND(F16/26*J15,)*4</f>
         <v>0</v>
       </c>
       <c r="K16" s="81">
-        <f t="shared" ref="K16" si="28">+F16/26*K15*2</f>
+        <f t="shared" ref="K16" si="24">+F16/26*K15*2</f>
         <v>0</v>
       </c>
       <c r="L16" s="79">
-        <f t="shared" ref="L16" si="29">F16*L15/(26)*30%</f>
+        <f>F16*L15/(26)*30%</f>
         <v>0</v>
       </c>
       <c r="M16" s="79">
+        <f>+F16/26*M15*60%</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="79">
         <f>'Bang TH nop'!O15</f>
         <v>0</v>
       </c>
-      <c r="N16" s="76">
+      <c r="O16" s="76">
         <f>'Bang TH nop'!N15</f>
         <v>0</v>
       </c>
-      <c r="O16" s="76">
+      <c r="P16" s="76">
         <f>+'Bang TH nop'!S15</f>
         <v>0</v>
       </c>
-      <c r="P16" s="87">
+      <c r="Q16" s="87">
         <f>'Bang TH nop'!M15</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="87">
+      <c r="R16" s="87">
         <f>+'Bang TH nop'!Q15+'Bang TH nop'!P15</f>
         <v>0</v>
       </c>
-      <c r="R16" s="59">
-        <f t="shared" ref="R16" si="30">+R15*15000</f>
+      <c r="S16" s="59">
+        <f t="shared" ref="S16" si="25">+S15*15000</f>
         <v>0</v>
       </c>
-      <c r="S16" s="59"/>
-      <c r="T16" s="59">
-        <f>SUM(G16:R16)</f>
+      <c r="T16" s="59"/>
+      <c r="U16" s="59">
+        <f>SUM(G16:S16)</f>
         <v>0</v>
       </c>
-      <c r="U16" s="76">
-        <f>D12*10.5%</f>
+      <c r="V16" s="76"/>
+      <c r="W16" s="76">
+        <f>+ROUND(D16*0.5%,-3)</f>
         <v>0</v>
       </c>
-      <c r="V16" s="76">
-        <f t="shared" ref="V16" si="31">+ROUND(D16*0.5%,-3)</f>
+      <c r="X16" s="59">
+        <f t="shared" ref="X16" si="26">ROUND(U16-V16-W16,-2)</f>
         <v>0</v>
       </c>
-      <c r="W16" s="59">
-        <f t="shared" ref="W16" si="32">ROUND(T16-U16-V16,-2)</f>
-        <v>0</v>
-      </c>
-      <c r="X16" s="105">
+      <c r="Y16" s="105">
         <f>+'Bang TH nop'!F15+'Bang TH nop'!H15+'Bang TH nop'!R15</f>
         <v>0</v>
       </c>
-      <c r="Y16" s="103">
+      <c r="Z16" s="103">
         <f>+IFERROR(VLOOKUP(C15,'[1]Bản gốc T03'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z16" s="75">
+      <c r="AA16" s="75">
         <f>+IFERROR(VLOOKUP(C15,'[1]Bản gốc T03'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA16" s="95" t="e">
-        <f t="shared" ref="AA16" si="33">+Z16/Y16</f>
+      <c r="AB16" s="95" t="e">
+        <f t="shared" ref="AB16" si="27">+AA16/Z16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB16" s="95" t="e">
-        <f t="shared" ref="AB16" si="34">AD16/X16</f>
+      <c r="AC16" s="95" t="e">
+        <f t="shared" ref="AC16" si="28">AE16/Y16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC16" s="96" t="e">
-        <f t="shared" ref="AC16" si="35">+AB16/AA16</f>
+      <c r="AD16" s="96" t="e">
+        <f t="shared" ref="AD16" si="29">+AC16/AB16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD16" s="93">
-        <f>+T16-J16</f>
+      <c r="AE16" s="93">
+        <f>+U16-J16</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="15.6" customHeight="1">
-      <c r="A17" s="139">
+    <row r="17" spans="1:31" ht="15.6" customHeight="1">
+      <c r="A17" s="144">
         <v>5</v>
       </c>
-      <c r="B17" s="138">
+      <c r="B17" s="145">
         <f>'Bang TH nop'!B17</f>
         <v>0</v>
       </c>
-      <c r="C17" s="163">
+      <c r="C17" s="146">
         <f>'Bang TH nop'!C17</f>
         <v>0</v>
       </c>
-      <c r="D17" s="149"/>
-      <c r="E17" s="150"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="148"/>
       <c r="F17" s="110"/>
       <c r="G17" s="77">
         <f>'Bang TH nop'!F17</f>
@@ -45009,146 +45038,148 @@
       <c r="M17" s="85"/>
       <c r="N17" s="85"/>
       <c r="O17" s="85"/>
-      <c r="P17" s="86"/>
-      <c r="Q17" s="85"/>
-      <c r="R17" s="86">
+      <c r="P17" s="85"/>
+      <c r="Q17" s="86"/>
+      <c r="R17" s="85"/>
+      <c r="S17" s="86">
         <f>'Bang TH nop'!L17</f>
         <v>0</v>
       </c>
-      <c r="S17" s="86"/>
       <c r="T17" s="86"/>
       <c r="U17" s="86"/>
       <c r="V17" s="86"/>
       <c r="W17" s="86"/>
-      <c r="X17" s="104"/>
-      <c r="Y17" s="103"/>
-      <c r="Z17" s="72"/>
-      <c r="AA17" s="73"/>
-      <c r="AB17" s="74"/>
-      <c r="AC17" s="73"/>
-      <c r="AD17" s="93"/>
+      <c r="X17" s="86"/>
+      <c r="Y17" s="104"/>
+      <c r="Z17" s="103"/>
+      <c r="AA17" s="72"/>
+      <c r="AB17" s="73"/>
+      <c r="AC17" s="74"/>
+      <c r="AD17" s="73"/>
+      <c r="AE17" s="93"/>
     </row>
-    <row r="18" spans="1:30" ht="15.6" customHeight="1">
-      <c r="A18" s="139"/>
-      <c r="B18" s="138"/>
-      <c r="C18" s="163"/>
-      <c r="D18" s="140">
+    <row r="18" spans="1:31" ht="15.6" customHeight="1">
+      <c r="A18" s="144"/>
+      <c r="B18" s="145"/>
+      <c r="C18" s="146"/>
+      <c r="D18" s="149">
         <f>+'Bang TH nop'!D17</f>
         <v>0</v>
       </c>
-      <c r="E18" s="150"/>
+      <c r="E18" s="148"/>
       <c r="F18" s="111">
         <f>+'Bang TH nop'!E17</f>
         <v>0</v>
       </c>
       <c r="G18" s="78">
-        <f t="shared" ref="G18" si="36">F18/26*G17</f>
+        <f t="shared" ref="G18" si="30">F18/26*G17</f>
         <v>0</v>
       </c>
       <c r="H18" s="60">
-        <f t="shared" ref="H18" si="37">+(F18/26/8*150%)*H17</f>
+        <f t="shared" ref="H18" si="31">+(F18/26/8*150%)*H17</f>
         <v>0</v>
       </c>
       <c r="I18" s="81">
-        <f t="shared" ref="I18" si="38">ROUND(D18/26*I17,)</f>
+        <f t="shared" ref="I18" si="32">ROUND(D18/26*I17,)</f>
         <v>0</v>
       </c>
       <c r="J18" s="81">
-        <f t="shared" ref="J18" si="39">ROUND(F18/26*J17,)*4</f>
+        <f t="shared" ref="J18" si="33">ROUND(F18/26*J17,)*4</f>
         <v>0</v>
       </c>
       <c r="K18" s="81">
-        <f t="shared" ref="K18" si="40">+F18/26*K17*2</f>
+        <f t="shared" ref="K18" si="34">+F18/26*K17*2</f>
         <v>0</v>
       </c>
       <c r="L18" s="79">
-        <f t="shared" ref="L18" si="41">F18*L17/(26)*30%</f>
+        <f>F18*L17/(26)*30%</f>
         <v>0</v>
       </c>
       <c r="M18" s="79">
+        <f>+F18/26*M17*60%</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="79">
         <f>'Bang TH nop'!O17</f>
         <v>0</v>
       </c>
-      <c r="N18" s="76">
+      <c r="O18" s="76">
         <f>'Bang TH nop'!N17</f>
         <v>0</v>
       </c>
-      <c r="O18" s="76">
+      <c r="P18" s="76">
         <f>+'Bang TH nop'!S17</f>
         <v>0</v>
       </c>
-      <c r="P18" s="87">
+      <c r="Q18" s="87">
         <f>'Bang TH nop'!M17</f>
         <v>0</v>
       </c>
-      <c r="Q18" s="87">
+      <c r="R18" s="87">
         <f>+'Bang TH nop'!Q17+'Bang TH nop'!P17</f>
         <v>0</v>
       </c>
-      <c r="R18" s="59">
-        <f t="shared" ref="R18" si="42">+R17*15000</f>
+      <c r="S18" s="59">
+        <f t="shared" ref="S18" si="35">+S17*15000</f>
         <v>0</v>
       </c>
-      <c r="S18" s="59"/>
-      <c r="T18" s="59">
-        <f>SUM(G18:R18)</f>
+      <c r="T18" s="59"/>
+      <c r="U18" s="59">
+        <f>SUM(G18:S18)</f>
         <v>0</v>
       </c>
-      <c r="U18" s="76">
-        <f>D14*10.5%</f>
+      <c r="V18" s="76"/>
+      <c r="W18" s="76">
+        <f>+ROUND(D18*0.5%,-3)</f>
         <v>0</v>
       </c>
-      <c r="V18" s="76">
-        <f t="shared" ref="V18" si="43">+ROUND(D18*0.5%,-3)</f>
+      <c r="X18" s="59">
+        <f t="shared" ref="X18" si="36">ROUND(U18-V18-W18,-2)</f>
         <v>0</v>
       </c>
-      <c r="W18" s="59">
-        <f t="shared" ref="W18" si="44">ROUND(T18-U18-V18,-2)</f>
-        <v>0</v>
-      </c>
-      <c r="X18" s="105">
+      <c r="Y18" s="105">
         <f>+'Bang TH nop'!F17+'Bang TH nop'!H17+'Bang TH nop'!R17</f>
         <v>0</v>
       </c>
-      <c r="Y18" s="103">
+      <c r="Z18" s="103">
         <f>+IFERROR(VLOOKUP(C17,'[1]Bản gốc T03'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z18" s="75">
+      <c r="AA18" s="75">
         <f>+IFERROR(VLOOKUP(C17,'[1]Bản gốc T03'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA18" s="95" t="e">
-        <f t="shared" ref="AA18" si="45">+Z18/Y18</f>
+      <c r="AB18" s="95" t="e">
+        <f t="shared" ref="AB18" si="37">+AA18/Z18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB18" s="95" t="e">
-        <f t="shared" ref="AB18" si="46">AD18/X18</f>
+      <c r="AC18" s="95" t="e">
+        <f t="shared" ref="AC18" si="38">AE18/Y18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC18" s="96" t="e">
-        <f t="shared" ref="AC18" si="47">+AB18/AA18</f>
+      <c r="AD18" s="96" t="e">
+        <f t="shared" ref="AD18" si="39">+AC18/AB18</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD18" s="93">
-        <f>+T18-J18</f>
+      <c r="AE18" s="93">
+        <f>+U18-J18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="15.6" customHeight="1">
-      <c r="A19" s="139">
+    <row r="19" spans="1:31" ht="15.6" customHeight="1">
+      <c r="A19" s="144">
         <v>6</v>
       </c>
-      <c r="B19" s="138">
+      <c r="B19" s="145">
         <f>'Bang TH nop'!B19</f>
         <v>0</v>
       </c>
-      <c r="C19" s="163">
+      <c r="C19" s="146">
         <f>'Bang TH nop'!C19</f>
         <v>0</v>
       </c>
-      <c r="D19" s="149"/>
-      <c r="E19" s="150"/>
+      <c r="D19" s="147"/>
+      <c r="E19" s="148"/>
       <c r="F19" s="110"/>
       <c r="G19" s="77">
         <f>'Bang TH nop'!F19</f>
@@ -45177,146 +45208,148 @@
       <c r="M19" s="85"/>
       <c r="N19" s="85"/>
       <c r="O19" s="85"/>
-      <c r="P19" s="86"/>
-      <c r="Q19" s="85"/>
-      <c r="R19" s="86">
+      <c r="P19" s="85"/>
+      <c r="Q19" s="86"/>
+      <c r="R19" s="85"/>
+      <c r="S19" s="86">
         <f>'Bang TH nop'!L19</f>
         <v>0</v>
       </c>
-      <c r="S19" s="86"/>
       <c r="T19" s="86"/>
       <c r="U19" s="86"/>
       <c r="V19" s="86"/>
       <c r="W19" s="86"/>
-      <c r="X19" s="104"/>
-      <c r="Y19" s="103"/>
-      <c r="Z19" s="72"/>
-      <c r="AA19" s="73"/>
-      <c r="AB19" s="74"/>
-      <c r="AC19" s="73"/>
-      <c r="AD19" s="93"/>
+      <c r="X19" s="86"/>
+      <c r="Y19" s="104"/>
+      <c r="Z19" s="103"/>
+      <c r="AA19" s="72"/>
+      <c r="AB19" s="73"/>
+      <c r="AC19" s="74"/>
+      <c r="AD19" s="73"/>
+      <c r="AE19" s="93"/>
     </row>
-    <row r="20" spans="1:30" ht="15.6" customHeight="1">
-      <c r="A20" s="139"/>
-      <c r="B20" s="138"/>
-      <c r="C20" s="163"/>
-      <c r="D20" s="140">
+    <row r="20" spans="1:31" ht="15.6" customHeight="1">
+      <c r="A20" s="144"/>
+      <c r="B20" s="145"/>
+      <c r="C20" s="146"/>
+      <c r="D20" s="149">
         <f>+'Bang TH nop'!D19</f>
         <v>0</v>
       </c>
-      <c r="E20" s="150"/>
+      <c r="E20" s="148"/>
       <c r="F20" s="111">
         <f>+'Bang TH nop'!E19</f>
         <v>0</v>
       </c>
       <c r="G20" s="78">
-        <f t="shared" ref="G20" si="48">F20/26*G19</f>
+        <f t="shared" ref="G20" si="40">F20/26*G19</f>
         <v>0</v>
       </c>
       <c r="H20" s="60">
-        <f t="shared" ref="H20" si="49">+(F20/26/8*150%)*H19</f>
+        <f t="shared" ref="H20" si="41">+(F20/26/8*150%)*H19</f>
         <v>0</v>
       </c>
       <c r="I20" s="81">
-        <f t="shared" ref="I20" si="50">ROUND(D20/26*I19,)</f>
+        <f t="shared" ref="I20" si="42">ROUND(D20/26*I19,)</f>
         <v>0</v>
       </c>
       <c r="J20" s="81">
-        <f t="shared" ref="J20" si="51">ROUND(F20/26*J19,)*4</f>
+        <f t="shared" ref="J20" si="43">ROUND(F20/26*J19,)*4</f>
         <v>0</v>
       </c>
       <c r="K20" s="81">
-        <f t="shared" ref="K20" si="52">+F20/26*K19*2</f>
+        <f t="shared" ref="K20" si="44">+F20/26*K19*2</f>
         <v>0</v>
       </c>
       <c r="L20" s="79">
-        <f t="shared" ref="L20" si="53">F20*L19/(26)*30%</f>
+        <f>F20*L19/(26)*30%</f>
         <v>0</v>
       </c>
       <c r="M20" s="79">
+        <f>+F20/26*M19*60%</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="79">
         <f>'Bang TH nop'!O19</f>
         <v>0</v>
       </c>
-      <c r="N20" s="76">
+      <c r="O20" s="76">
         <f>'Bang TH nop'!N19</f>
         <v>0</v>
       </c>
-      <c r="O20" s="76">
+      <c r="P20" s="76">
         <f>+'Bang TH nop'!S19</f>
         <v>0</v>
       </c>
-      <c r="P20" s="87">
+      <c r="Q20" s="87">
         <f>'Bang TH nop'!M19</f>
         <v>0</v>
       </c>
-      <c r="Q20" s="87">
+      <c r="R20" s="87">
         <f>+'Bang TH nop'!Q19+'Bang TH nop'!P19</f>
         <v>0</v>
       </c>
-      <c r="R20" s="59">
-        <f t="shared" ref="R20" si="54">+R19*15000</f>
+      <c r="S20" s="59">
+        <f t="shared" ref="S20" si="45">+S19*15000</f>
         <v>0</v>
       </c>
-      <c r="S20" s="59"/>
-      <c r="T20" s="59">
-        <f>SUM(G20:R20)</f>
+      <c r="T20" s="59"/>
+      <c r="U20" s="59">
+        <f>SUM(G20:S20)</f>
         <v>0</v>
       </c>
-      <c r="U20" s="76">
-        <f>D16*10.5%</f>
+      <c r="V20" s="76"/>
+      <c r="W20" s="76">
+        <f>+ROUND(D20*0.5%,-3)</f>
         <v>0</v>
       </c>
-      <c r="V20" s="76">
-        <f t="shared" ref="V20" si="55">+ROUND(D20*0.5%,-3)</f>
+      <c r="X20" s="59">
+        <f t="shared" ref="X20" si="46">ROUND(U20-V20-W20,-2)</f>
         <v>0</v>
       </c>
-      <c r="W20" s="59">
-        <f t="shared" ref="W20" si="56">ROUND(T20-U20-V20,-2)</f>
-        <v>0</v>
-      </c>
-      <c r="X20" s="105">
+      <c r="Y20" s="105">
         <f>+'Bang TH nop'!F19+'Bang TH nop'!H19+'Bang TH nop'!R19</f>
         <v>0</v>
       </c>
-      <c r="Y20" s="103">
+      <c r="Z20" s="103">
         <f>+IFERROR(VLOOKUP(C19,'[1]Bản gốc T03'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z20" s="75">
+      <c r="AA20" s="75">
         <f>+IFERROR(VLOOKUP(C19,'[1]Bản gốc T03'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA20" s="95" t="e">
-        <f t="shared" ref="AA20" si="57">+Z20/Y20</f>
+      <c r="AB20" s="95" t="e">
+        <f t="shared" ref="AB20" si="47">+AA20/Z20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB20" s="95" t="e">
-        <f t="shared" ref="AB20" si="58">AD20/X20</f>
+      <c r="AC20" s="95" t="e">
+        <f t="shared" ref="AC20" si="48">AE20/Y20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC20" s="96" t="e">
-        <f t="shared" ref="AC20" si="59">+AB20/AA20</f>
+      <c r="AD20" s="96" t="e">
+        <f t="shared" ref="AD20" si="49">+AC20/AB20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD20" s="93">
-        <f>+T20-J20</f>
+      <c r="AE20" s="93">
+        <f>+U20-J20</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="15.6" customHeight="1">
-      <c r="A21" s="139">
+    <row r="21" spans="1:31" ht="15.6" customHeight="1">
+      <c r="A21" s="144">
         <v>7</v>
       </c>
-      <c r="B21" s="138">
+      <c r="B21" s="145">
         <f>'Bang TH nop'!B21</f>
         <v>0</v>
       </c>
-      <c r="C21" s="163">
+      <c r="C21" s="146">
         <f>'Bang TH nop'!C21</f>
         <v>0</v>
       </c>
-      <c r="D21" s="149"/>
-      <c r="E21" s="150"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="148"/>
       <c r="F21" s="110"/>
       <c r="G21" s="77">
         <f>'Bang TH nop'!F21</f>
@@ -45345,138 +45378,140 @@
       <c r="M21" s="85"/>
       <c r="N21" s="85"/>
       <c r="O21" s="85"/>
-      <c r="P21" s="86"/>
-      <c r="Q21" s="85"/>
-      <c r="R21" s="86">
+      <c r="P21" s="85"/>
+      <c r="Q21" s="86"/>
+      <c r="R21" s="85"/>
+      <c r="S21" s="86">
         <f>'Bang TH nop'!L21</f>
         <v>0</v>
       </c>
-      <c r="S21" s="86"/>
       <c r="T21" s="86"/>
       <c r="U21" s="86"/>
       <c r="V21" s="86"/>
       <c r="W21" s="86"/>
-      <c r="X21" s="104"/>
-      <c r="Y21" s="103"/>
-      <c r="Z21" s="72"/>
-      <c r="AA21" s="73"/>
-      <c r="AB21" s="74"/>
-      <c r="AC21" s="73"/>
-      <c r="AD21" s="93"/>
+      <c r="X21" s="86"/>
+      <c r="Y21" s="104"/>
+      <c r="Z21" s="103"/>
+      <c r="AA21" s="72"/>
+      <c r="AB21" s="73"/>
+      <c r="AC21" s="74"/>
+      <c r="AD21" s="73"/>
+      <c r="AE21" s="93"/>
     </row>
-    <row r="22" spans="1:30" ht="15.6" customHeight="1">
-      <c r="A22" s="139"/>
-      <c r="B22" s="138"/>
-      <c r="C22" s="163"/>
-      <c r="D22" s="140">
+    <row r="22" spans="1:31" ht="15.6" customHeight="1">
+      <c r="A22" s="144"/>
+      <c r="B22" s="145"/>
+      <c r="C22" s="146"/>
+      <c r="D22" s="149">
         <f>+'Bang TH nop'!D21</f>
         <v>0</v>
       </c>
-      <c r="E22" s="150"/>
+      <c r="E22" s="148"/>
       <c r="F22" s="111">
         <f>+'Bang TH nop'!E21</f>
         <v>0</v>
       </c>
       <c r="G22" s="78">
-        <f t="shared" ref="G22" si="60">F22/26*G21</f>
+        <f t="shared" ref="G22" si="50">F22/26*G21</f>
         <v>0</v>
       </c>
       <c r="H22" s="60">
-        <f t="shared" ref="H22" si="61">+(F22/26/8*150%)*H21</f>
+        <f t="shared" ref="H22" si="51">+(F22/26/8*150%)*H21</f>
         <v>0</v>
       </c>
       <c r="I22" s="81">
-        <f t="shared" ref="I22" si="62">ROUND(D22/26*I21,)</f>
+        <f t="shared" ref="I22" si="52">ROUND(D22/26*I21,)</f>
         <v>0</v>
       </c>
       <c r="J22" s="81">
-        <f t="shared" ref="J22" si="63">ROUND(F22/26*J21,)*4</f>
+        <f t="shared" ref="J22" si="53">ROUND(F22/26*J21,)*4</f>
         <v>0</v>
       </c>
       <c r="K22" s="81">
-        <f t="shared" ref="K22" si="64">+F22/26*K21*2</f>
+        <f t="shared" ref="K22" si="54">+F22/26*K21*2</f>
         <v>0</v>
       </c>
       <c r="L22" s="79">
-        <f t="shared" ref="L22" si="65">F22*L21/(26)*30%</f>
+        <f>F22*L21/(26)*30%</f>
         <v>0</v>
       </c>
       <c r="M22" s="79">
+        <f>+F22/26*M21*60%</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="79">
         <f>'Bang TH nop'!O21</f>
         <v>0</v>
       </c>
-      <c r="N22" s="76">
+      <c r="O22" s="76">
         <f>'Bang TH nop'!N21</f>
         <v>0</v>
       </c>
-      <c r="O22" s="76">
+      <c r="P22" s="76">
         <f>+'Bang TH nop'!S21</f>
         <v>0</v>
       </c>
-      <c r="P22" s="87">
+      <c r="Q22" s="87">
         <f>'Bang TH nop'!M21</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="87">
+      <c r="R22" s="87">
         <f>+'Bang TH nop'!Q21+'Bang TH nop'!P21</f>
         <v>0</v>
       </c>
-      <c r="R22" s="59">
-        <f t="shared" ref="R22" si="66">+R21*15000</f>
+      <c r="S22" s="59">
+        <f t="shared" ref="S22" si="55">+S21*15000</f>
         <v>0</v>
       </c>
-      <c r="S22" s="59"/>
-      <c r="T22" s="59">
-        <f>SUM(G22:R22)</f>
+      <c r="T22" s="59"/>
+      <c r="U22" s="59">
+        <f>SUM(G22:S22)</f>
         <v>0</v>
       </c>
-      <c r="U22" s="76">
-        <f>D18*10.5%</f>
+      <c r="V22" s="76"/>
+      <c r="W22" s="76">
+        <f>+ROUND(D22*0.5%,-3)</f>
         <v>0</v>
       </c>
-      <c r="V22" s="76">
-        <f t="shared" ref="V22" si="67">+ROUND(D22*0.5%,-3)</f>
+      <c r="X22" s="59">
+        <f t="shared" ref="X22" si="56">ROUND(U22-V22-W22,-2)</f>
         <v>0</v>
       </c>
-      <c r="W22" s="59">
-        <f t="shared" ref="W22" si="68">ROUND(T22-U22-V22,-2)</f>
-        <v>0</v>
-      </c>
-      <c r="X22" s="105">
+      <c r="Y22" s="105">
         <f>+'Bang TH nop'!F21+'Bang TH nop'!H21+'Bang TH nop'!R21</f>
         <v>0</v>
       </c>
-      <c r="Y22" s="103">
+      <c r="Z22" s="103">
         <f>+IFERROR(VLOOKUP(C21,'[1]Bản gốc T03'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z22" s="75">
+      <c r="AA22" s="75">
         <f>+IFERROR(VLOOKUP(C21,'[1]Bản gốc T03'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
-      <c r="AA22" s="95" t="e">
-        <f t="shared" ref="AA22" si="69">+Z22/Y22</f>
+      <c r="AB22" s="95" t="e">
+        <f t="shared" ref="AB22" si="57">+AA22/Z22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB22" s="95" t="e">
-        <f t="shared" ref="AB22" si="70">AD22/X22</f>
+      <c r="AC22" s="95" t="e">
+        <f t="shared" ref="AC22" si="58">AE22/Y22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC22" s="96" t="e">
-        <f t="shared" ref="AC22" si="71">+AB22/AA22</f>
+      <c r="AD22" s="96" t="e">
+        <f t="shared" ref="AD22" si="59">+AC22/AB22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD22" s="93">
-        <f>+T22-J22</f>
+      <c r="AE22" s="93">
+        <f>+U22-J22</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="15.6" hidden="1" customHeight="1">
-      <c r="A23" s="139"/>
-      <c r="B23" s="138"/>
-      <c r="C23" s="162"/>
-      <c r="D23" s="149"/>
-      <c r="E23" s="140"/>
+    <row r="23" spans="1:31" ht="15.6" hidden="1" customHeight="1">
+      <c r="A23" s="144"/>
+      <c r="B23" s="145"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="149"/>
       <c r="F23" s="109"/>
       <c r="G23" s="34"/>
       <c r="H23" s="38"/>
@@ -45490,67 +45525,69 @@
         <f>+'Bang TH nop'!J23</f>
         <v>0</v>
       </c>
-      <c r="M23" s="33"/>
+      <c r="M23" s="85"/>
       <c r="N23" s="33"/>
       <c r="O23" s="33"/>
-      <c r="P23" s="37"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="37"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="37"/>
+      <c r="R23" s="33"/>
       <c r="S23" s="37"/>
       <c r="T23" s="37"/>
-      <c r="U23" s="59"/>
-      <c r="V23" s="37"/>
+      <c r="U23" s="37"/>
+      <c r="V23" s="59"/>
       <c r="W23" s="37"/>
-      <c r="X23" s="106"/>
-      <c r="Y23" s="103"/>
-      <c r="Z23" s="72"/>
+      <c r="X23" s="37"/>
+      <c r="Y23" s="106"/>
+      <c r="Z23" s="103"/>
+      <c r="AA23" s="72"/>
     </row>
-    <row r="24" spans="1:30" ht="15.6" hidden="1" customHeight="1">
-      <c r="A24" s="139"/>
-      <c r="B24" s="138"/>
-      <c r="C24" s="162"/>
-      <c r="D24" s="140"/>
-      <c r="E24" s="140"/>
+    <row r="24" spans="1:31" ht="15.6" hidden="1" customHeight="1">
+      <c r="A24" s="144"/>
+      <c r="B24" s="145"/>
+      <c r="C24" s="151"/>
+      <c r="D24" s="149"/>
+      <c r="E24" s="149"/>
       <c r="F24" s="109"/>
       <c r="G24" s="39"/>
       <c r="H24" s="38"/>
       <c r="I24" s="40"/>
       <c r="J24" s="40"/>
       <c r="K24" s="81">
-        <f t="shared" ref="K24" si="72">+F24/26*K23*2</f>
+        <f t="shared" ref="K24" si="60">+F24/26*K23*2</f>
         <v>0</v>
       </c>
       <c r="L24" s="79">
-        <f t="shared" ref="L24" si="73">F24*L23/(26)*30%</f>
+        <f>F24*L23/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M24" s="40"/>
-      <c r="N24" s="39"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="40"/>
       <c r="O24" s="39"/>
-      <c r="P24" s="41"/>
+      <c r="P24" s="39"/>
       <c r="Q24" s="41"/>
-      <c r="R24" s="37"/>
+      <c r="R24" s="41"/>
       <c r="S24" s="37"/>
       <c r="T24" s="37"/>
-      <c r="U24" s="39"/>
-      <c r="V24" s="37"/>
+      <c r="U24" s="37"/>
+      <c r="V24" s="39"/>
       <c r="W24" s="37"/>
-      <c r="X24" s="106"/>
-      <c r="Y24" s="103">
+      <c r="X24" s="37"/>
+      <c r="Y24" s="106"/>
+      <c r="Z24" s="103">
         <f>+IFERROR(VLOOKUP(C23,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z24" s="75">
+      <c r="AA24" s="75">
         <f>+IFERROR(VLOOKUP(C23,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="15.6" hidden="1" customHeight="1">
-      <c r="A25" s="139"/>
-      <c r="B25" s="138"/>
-      <c r="C25" s="162"/>
-      <c r="D25" s="149"/>
-      <c r="E25" s="140"/>
+    <row r="25" spans="1:31" ht="15.6" hidden="1" customHeight="1">
+      <c r="A25" s="144"/>
+      <c r="B25" s="145"/>
+      <c r="C25" s="151"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="149"/>
       <c r="F25" s="109"/>
       <c r="G25" s="34"/>
       <c r="H25" s="38"/>
@@ -45564,67 +45601,69 @@
         <f>+'Bang TH nop'!J25</f>
         <v>0</v>
       </c>
-      <c r="M25" s="33"/>
+      <c r="M25" s="85"/>
       <c r="N25" s="33"/>
       <c r="O25" s="33"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="37"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="33"/>
       <c r="S25" s="37"/>
       <c r="T25" s="37"/>
-      <c r="U25" s="59"/>
-      <c r="V25" s="37"/>
+      <c r="U25" s="37"/>
+      <c r="V25" s="59"/>
       <c r="W25" s="37"/>
-      <c r="X25" s="106"/>
-      <c r="Y25" s="103"/>
-      <c r="Z25" s="72"/>
+      <c r="X25" s="37"/>
+      <c r="Y25" s="106"/>
+      <c r="Z25" s="103"/>
+      <c r="AA25" s="72"/>
     </row>
-    <row r="26" spans="1:30" ht="15.6" hidden="1" customHeight="1">
-      <c r="A26" s="139"/>
-      <c r="B26" s="138"/>
-      <c r="C26" s="162"/>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
+    <row r="26" spans="1:31" ht="15.6" hidden="1" customHeight="1">
+      <c r="A26" s="144"/>
+      <c r="B26" s="145"/>
+      <c r="C26" s="151"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
       <c r="F26" s="109"/>
       <c r="G26" s="39"/>
       <c r="H26" s="38"/>
       <c r="I26" s="40"/>
       <c r="J26" s="40"/>
       <c r="K26" s="81">
-        <f t="shared" ref="K26" si="74">+F26/26*K25*2</f>
+        <f t="shared" ref="K26" si="61">+F26/26*K25*2</f>
         <v>0</v>
       </c>
       <c r="L26" s="79">
-        <f t="shared" ref="L26" si="75">F26*L25/(26)*30%</f>
+        <f>F26*L25/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M26" s="40"/>
-      <c r="N26" s="39"/>
+      <c r="M26" s="79"/>
+      <c r="N26" s="40"/>
       <c r="O26" s="39"/>
-      <c r="P26" s="41"/>
+      <c r="P26" s="39"/>
       <c r="Q26" s="41"/>
-      <c r="R26" s="37"/>
+      <c r="R26" s="41"/>
       <c r="S26" s="37"/>
       <c r="T26" s="37"/>
-      <c r="U26" s="39"/>
-      <c r="V26" s="37"/>
+      <c r="U26" s="37"/>
+      <c r="V26" s="39"/>
       <c r="W26" s="37"/>
-      <c r="X26" s="106"/>
-      <c r="Y26" s="103">
+      <c r="X26" s="37"/>
+      <c r="Y26" s="106"/>
+      <c r="Z26" s="103">
         <f>+IFERROR(VLOOKUP(C25,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z26" s="75">
+      <c r="AA26" s="75">
         <f>+IFERROR(VLOOKUP(C25,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A27" s="139"/>
-      <c r="B27" s="138"/>
-      <c r="C27" s="162"/>
-      <c r="D27" s="149"/>
-      <c r="E27" s="140"/>
+    <row r="27" spans="1:31" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A27" s="144"/>
+      <c r="B27" s="145"/>
+      <c r="C27" s="151"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="149"/>
       <c r="F27" s="109"/>
       <c r="G27" s="34"/>
       <c r="H27" s="38"/>
@@ -45638,67 +45677,69 @@
         <f>+'Bang TH nop'!J27</f>
         <v>0</v>
       </c>
-      <c r="M27" s="33"/>
+      <c r="M27" s="85"/>
       <c r="N27" s="33"/>
       <c r="O27" s="33"/>
-      <c r="P27" s="37"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="37"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="37"/>
+      <c r="R27" s="33"/>
       <c r="S27" s="37"/>
       <c r="T27" s="37"/>
-      <c r="U27" s="59"/>
-      <c r="V27" s="37"/>
+      <c r="U27" s="37"/>
+      <c r="V27" s="59"/>
       <c r="W27" s="37"/>
-      <c r="X27" s="106"/>
-      <c r="Y27" s="103"/>
-      <c r="Z27" s="72"/>
+      <c r="X27" s="37"/>
+      <c r="Y27" s="106"/>
+      <c r="Z27" s="103"/>
+      <c r="AA27" s="72"/>
     </row>
-    <row r="28" spans="1:30" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A28" s="139"/>
-      <c r="B28" s="138"/>
-      <c r="C28" s="162"/>
-      <c r="D28" s="140"/>
-      <c r="E28" s="140"/>
+    <row r="28" spans="1:31" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A28" s="144"/>
+      <c r="B28" s="145"/>
+      <c r="C28" s="151"/>
+      <c r="D28" s="149"/>
+      <c r="E28" s="149"/>
       <c r="F28" s="109"/>
       <c r="G28" s="39"/>
       <c r="H28" s="38"/>
       <c r="I28" s="40"/>
       <c r="J28" s="40"/>
       <c r="K28" s="81">
-        <f t="shared" ref="K28" si="76">+F28/26*K27*2</f>
+        <f t="shared" ref="K28" si="62">+F28/26*K27*2</f>
         <v>0</v>
       </c>
       <c r="L28" s="79">
-        <f t="shared" ref="L28" si="77">F28*L27/(26)*30%</f>
+        <f>F28*L27/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M28" s="40"/>
-      <c r="N28" s="39"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="40"/>
       <c r="O28" s="39"/>
-      <c r="P28" s="41"/>
+      <c r="P28" s="39"/>
       <c r="Q28" s="41"/>
-      <c r="R28" s="37"/>
+      <c r="R28" s="41"/>
       <c r="S28" s="37"/>
       <c r="T28" s="37"/>
-      <c r="U28" s="39"/>
-      <c r="V28" s="37"/>
+      <c r="U28" s="37"/>
+      <c r="V28" s="39"/>
       <c r="W28" s="37"/>
-      <c r="X28" s="106"/>
-      <c r="Y28" s="103">
+      <c r="X28" s="37"/>
+      <c r="Y28" s="106"/>
+      <c r="Z28" s="103">
         <f>+IFERROR(VLOOKUP(C27,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z28" s="75">
+      <c r="AA28" s="75">
         <f>+IFERROR(VLOOKUP(C27,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:30" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A29" s="139"/>
-      <c r="B29" s="138"/>
-      <c r="C29" s="162"/>
-      <c r="D29" s="149"/>
-      <c r="E29" s="140"/>
+    <row r="29" spans="1:31" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A29" s="144"/>
+      <c r="B29" s="145"/>
+      <c r="C29" s="151"/>
+      <c r="D29" s="147"/>
+      <c r="E29" s="149"/>
       <c r="F29" s="109"/>
       <c r="G29" s="34"/>
       <c r="H29" s="38"/>
@@ -45712,67 +45753,69 @@
         <f>+'Bang TH nop'!J29</f>
         <v>0</v>
       </c>
-      <c r="M29" s="33"/>
+      <c r="M29" s="85"/>
       <c r="N29" s="33"/>
       <c r="O29" s="33"/>
-      <c r="P29" s="37"/>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="37"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="37"/>
+      <c r="R29" s="33"/>
       <c r="S29" s="37"/>
       <c r="T29" s="37"/>
-      <c r="U29" s="59"/>
-      <c r="V29" s="37"/>
+      <c r="U29" s="37"/>
+      <c r="V29" s="59"/>
       <c r="W29" s="37"/>
-      <c r="X29" s="106"/>
-      <c r="Y29" s="103"/>
-      <c r="Z29" s="72"/>
+      <c r="X29" s="37"/>
+      <c r="Y29" s="106"/>
+      <c r="Z29" s="103"/>
+      <c r="AA29" s="72"/>
     </row>
-    <row r="30" spans="1:30" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A30" s="139"/>
-      <c r="B30" s="138"/>
-      <c r="C30" s="162"/>
-      <c r="D30" s="140"/>
-      <c r="E30" s="140"/>
+    <row r="30" spans="1:31" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A30" s="144"/>
+      <c r="B30" s="145"/>
+      <c r="C30" s="151"/>
+      <c r="D30" s="149"/>
+      <c r="E30" s="149"/>
       <c r="F30" s="109"/>
       <c r="G30" s="39"/>
       <c r="H30" s="38"/>
       <c r="I30" s="40"/>
       <c r="J30" s="40"/>
       <c r="K30" s="81">
-        <f t="shared" ref="K30" si="78">+F30/26*K29*2</f>
+        <f t="shared" ref="K30" si="63">+F30/26*K29*2</f>
         <v>0</v>
       </c>
       <c r="L30" s="79">
-        <f t="shared" ref="L30" si="79">F30*L29/(26)*30%</f>
+        <f>F30*L29/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M30" s="40"/>
-      <c r="N30" s="39"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="40"/>
       <c r="O30" s="39"/>
-      <c r="P30" s="41"/>
+      <c r="P30" s="39"/>
       <c r="Q30" s="41"/>
-      <c r="R30" s="37"/>
+      <c r="R30" s="41"/>
       <c r="S30" s="37"/>
       <c r="T30" s="37"/>
-      <c r="U30" s="39"/>
-      <c r="V30" s="37"/>
+      <c r="U30" s="37"/>
+      <c r="V30" s="39"/>
       <c r="W30" s="37"/>
-      <c r="X30" s="106"/>
-      <c r="Y30" s="103">
+      <c r="X30" s="37"/>
+      <c r="Y30" s="106"/>
+      <c r="Z30" s="103">
         <f>+IFERROR(VLOOKUP(C29,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z30" s="75">
+      <c r="AA30" s="75">
         <f>+IFERROR(VLOOKUP(C29,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:30" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A31" s="139"/>
-      <c r="B31" s="138"/>
-      <c r="C31" s="162"/>
-      <c r="D31" s="149"/>
-      <c r="E31" s="140"/>
+    <row r="31" spans="1:31" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A31" s="144"/>
+      <c r="B31" s="145"/>
+      <c r="C31" s="151"/>
+      <c r="D31" s="147"/>
+      <c r="E31" s="149"/>
       <c r="F31" s="109"/>
       <c r="G31" s="34"/>
       <c r="H31" s="38"/>
@@ -45786,67 +45829,69 @@
         <f>+'Bang TH nop'!J31</f>
         <v>0</v>
       </c>
-      <c r="M31" s="33"/>
+      <c r="M31" s="85"/>
       <c r="N31" s="33"/>
       <c r="O31" s="33"/>
-      <c r="P31" s="37"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="37"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="37"/>
+      <c r="R31" s="33"/>
       <c r="S31" s="37"/>
       <c r="T31" s="37"/>
-      <c r="U31" s="59"/>
-      <c r="V31" s="37"/>
+      <c r="U31" s="37"/>
+      <c r="V31" s="59"/>
       <c r="W31" s="37"/>
-      <c r="X31" s="106"/>
-      <c r="Y31" s="103"/>
-      <c r="Z31" s="72"/>
+      <c r="X31" s="37"/>
+      <c r="Y31" s="106"/>
+      <c r="Z31" s="103"/>
+      <c r="AA31" s="72"/>
     </row>
-    <row r="32" spans="1:30" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A32" s="139"/>
-      <c r="B32" s="138"/>
-      <c r="C32" s="162"/>
-      <c r="D32" s="140"/>
-      <c r="E32" s="140"/>
+    <row r="32" spans="1:31" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A32" s="144"/>
+      <c r="B32" s="145"/>
+      <c r="C32" s="151"/>
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
       <c r="F32" s="109"/>
       <c r="G32" s="39"/>
       <c r="H32" s="38"/>
       <c r="I32" s="40"/>
       <c r="J32" s="40"/>
       <c r="K32" s="81">
-        <f t="shared" ref="K32" si="80">+F32/26*K31*2</f>
+        <f t="shared" ref="K32" si="64">+F32/26*K31*2</f>
         <v>0</v>
       </c>
       <c r="L32" s="79">
-        <f t="shared" ref="L32" si="81">F32*L31/(26)*30%</f>
+        <f>F32*L31/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M32" s="40"/>
-      <c r="N32" s="39"/>
+      <c r="M32" s="79"/>
+      <c r="N32" s="40"/>
       <c r="O32" s="39"/>
-      <c r="P32" s="41"/>
+      <c r="P32" s="39"/>
       <c r="Q32" s="41"/>
-      <c r="R32" s="37"/>
+      <c r="R32" s="41"/>
       <c r="S32" s="37"/>
       <c r="T32" s="37"/>
-      <c r="U32" s="39"/>
-      <c r="V32" s="37"/>
+      <c r="U32" s="37"/>
+      <c r="V32" s="39"/>
       <c r="W32" s="37"/>
-      <c r="X32" s="106"/>
-      <c r="Y32" s="103">
+      <c r="X32" s="37"/>
+      <c r="Y32" s="106"/>
+      <c r="Z32" s="103">
         <f>+IFERROR(VLOOKUP(C31,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z32" s="75">
+      <c r="AA32" s="75">
         <f>+IFERROR(VLOOKUP(C31,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A33" s="139"/>
-      <c r="B33" s="138"/>
-      <c r="C33" s="162"/>
-      <c r="D33" s="149"/>
-      <c r="E33" s="140"/>
+    <row r="33" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A33" s="144"/>
+      <c r="B33" s="145"/>
+      <c r="C33" s="151"/>
+      <c r="D33" s="147"/>
+      <c r="E33" s="149"/>
       <c r="F33" s="109"/>
       <c r="G33" s="34"/>
       <c r="H33" s="38"/>
@@ -45860,67 +45905,69 @@
         <f>+'Bang TH nop'!J33</f>
         <v>0</v>
       </c>
-      <c r="M33" s="33"/>
+      <c r="M33" s="85"/>
       <c r="N33" s="33"/>
       <c r="O33" s="33"/>
-      <c r="P33" s="37"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="37"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="37"/>
+      <c r="R33" s="33"/>
       <c r="S33" s="37"/>
       <c r="T33" s="37"/>
-      <c r="U33" s="59"/>
-      <c r="V33" s="37"/>
+      <c r="U33" s="37"/>
+      <c r="V33" s="59"/>
       <c r="W33" s="37"/>
-      <c r="X33" s="106"/>
-      <c r="Y33" s="103"/>
-      <c r="Z33" s="72"/>
+      <c r="X33" s="37"/>
+      <c r="Y33" s="106"/>
+      <c r="Z33" s="103"/>
+      <c r="AA33" s="72"/>
     </row>
-    <row r="34" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A34" s="139"/>
-      <c r="B34" s="138"/>
-      <c r="C34" s="162"/>
-      <c r="D34" s="140"/>
-      <c r="E34" s="140"/>
+    <row r="34" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A34" s="144"/>
+      <c r="B34" s="145"/>
+      <c r="C34" s="151"/>
+      <c r="D34" s="149"/>
+      <c r="E34" s="149"/>
       <c r="F34" s="109"/>
       <c r="G34" s="39"/>
       <c r="H34" s="38"/>
       <c r="I34" s="40"/>
       <c r="J34" s="40"/>
       <c r="K34" s="81">
-        <f t="shared" ref="K34" si="82">+F34/26*K33*2</f>
+        <f t="shared" ref="K34" si="65">+F34/26*K33*2</f>
         <v>0</v>
       </c>
       <c r="L34" s="79">
-        <f t="shared" ref="L34" si="83">F34*L33/(26)*30%</f>
+        <f>F34*L33/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M34" s="40"/>
-      <c r="N34" s="39"/>
+      <c r="M34" s="79"/>
+      <c r="N34" s="40"/>
       <c r="O34" s="39"/>
-      <c r="P34" s="41"/>
+      <c r="P34" s="39"/>
       <c r="Q34" s="41"/>
-      <c r="R34" s="37"/>
+      <c r="R34" s="41"/>
       <c r="S34" s="37"/>
       <c r="T34" s="37"/>
-      <c r="U34" s="39"/>
-      <c r="V34" s="37"/>
+      <c r="U34" s="37"/>
+      <c r="V34" s="39"/>
       <c r="W34" s="37"/>
-      <c r="X34" s="106"/>
-      <c r="Y34" s="103">
+      <c r="X34" s="37"/>
+      <c r="Y34" s="106"/>
+      <c r="Z34" s="103">
         <f>+IFERROR(VLOOKUP(C33,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z34" s="75">
+      <c r="AA34" s="75">
         <f>+IFERROR(VLOOKUP(C33,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A35" s="139"/>
-      <c r="B35" s="138"/>
-      <c r="C35" s="162"/>
-      <c r="D35" s="149"/>
-      <c r="E35" s="140"/>
+    <row r="35" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A35" s="144"/>
+      <c r="B35" s="145"/>
+      <c r="C35" s="151"/>
+      <c r="D35" s="147"/>
+      <c r="E35" s="149"/>
       <c r="F35" s="109"/>
       <c r="G35" s="34"/>
       <c r="H35" s="38"/>
@@ -45934,67 +45981,69 @@
         <f>+'Bang TH nop'!J35</f>
         <v>0</v>
       </c>
-      <c r="M35" s="33"/>
+      <c r="M35" s="85"/>
       <c r="N35" s="33"/>
       <c r="O35" s="33"/>
-      <c r="P35" s="37"/>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="37"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="37"/>
+      <c r="R35" s="33"/>
       <c r="S35" s="37"/>
       <c r="T35" s="37"/>
-      <c r="U35" s="59"/>
-      <c r="V35" s="37"/>
+      <c r="U35" s="37"/>
+      <c r="V35" s="59"/>
       <c r="W35" s="37"/>
-      <c r="X35" s="106"/>
-      <c r="Y35" s="103"/>
-      <c r="Z35" s="72"/>
+      <c r="X35" s="37"/>
+      <c r="Y35" s="106"/>
+      <c r="Z35" s="103"/>
+      <c r="AA35" s="72"/>
     </row>
-    <row r="36" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A36" s="139"/>
-      <c r="B36" s="138"/>
-      <c r="C36" s="162"/>
-      <c r="D36" s="140"/>
-      <c r="E36" s="140"/>
+    <row r="36" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A36" s="144"/>
+      <c r="B36" s="145"/>
+      <c r="C36" s="151"/>
+      <c r="D36" s="149"/>
+      <c r="E36" s="149"/>
       <c r="F36" s="109"/>
       <c r="G36" s="39"/>
       <c r="H36" s="38"/>
       <c r="I36" s="40"/>
       <c r="J36" s="40"/>
       <c r="K36" s="81">
-        <f t="shared" ref="K36" si="84">+F36/26*K35*2</f>
+        <f t="shared" ref="K36" si="66">+F36/26*K35*2</f>
         <v>0</v>
       </c>
       <c r="L36" s="79">
-        <f t="shared" ref="L36" si="85">F36*L35/(26)*30%</f>
+        <f>F36*L35/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M36" s="40"/>
-      <c r="N36" s="39"/>
+      <c r="M36" s="79"/>
+      <c r="N36" s="40"/>
       <c r="O36" s="39"/>
-      <c r="P36" s="41"/>
+      <c r="P36" s="39"/>
       <c r="Q36" s="41"/>
-      <c r="R36" s="37"/>
+      <c r="R36" s="41"/>
       <c r="S36" s="37"/>
       <c r="T36" s="37"/>
-      <c r="U36" s="39"/>
-      <c r="V36" s="37"/>
+      <c r="U36" s="37"/>
+      <c r="V36" s="39"/>
       <c r="W36" s="37"/>
-      <c r="X36" s="106"/>
-      <c r="Y36" s="103">
+      <c r="X36" s="37"/>
+      <c r="Y36" s="106"/>
+      <c r="Z36" s="103">
         <f>+IFERROR(VLOOKUP(C35,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z36" s="75">
+      <c r="AA36" s="75">
         <f>+IFERROR(VLOOKUP(C35,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A37" s="139"/>
-      <c r="B37" s="138"/>
-      <c r="C37" s="162"/>
-      <c r="D37" s="149"/>
-      <c r="E37" s="140"/>
+    <row r="37" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A37" s="144"/>
+      <c r="B37" s="145"/>
+      <c r="C37" s="151"/>
+      <c r="D37" s="147"/>
+      <c r="E37" s="149"/>
       <c r="F37" s="109"/>
       <c r="G37" s="34"/>
       <c r="H37" s="38"/>
@@ -46008,67 +46057,69 @@
         <f>+'Bang TH nop'!J37</f>
         <v>0</v>
       </c>
-      <c r="M37" s="33"/>
+      <c r="M37" s="85"/>
       <c r="N37" s="33"/>
       <c r="O37" s="33"/>
-      <c r="P37" s="37"/>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="37"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="37"/>
+      <c r="R37" s="33"/>
       <c r="S37" s="37"/>
       <c r="T37" s="37"/>
-      <c r="U37" s="59"/>
-      <c r="V37" s="37"/>
+      <c r="U37" s="37"/>
+      <c r="V37" s="59"/>
       <c r="W37" s="37"/>
-      <c r="X37" s="106"/>
-      <c r="Y37" s="103"/>
-      <c r="Z37" s="72"/>
+      <c r="X37" s="37"/>
+      <c r="Y37" s="106"/>
+      <c r="Z37" s="103"/>
+      <c r="AA37" s="72"/>
     </row>
-    <row r="38" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A38" s="139"/>
-      <c r="B38" s="138"/>
-      <c r="C38" s="162"/>
-      <c r="D38" s="140"/>
-      <c r="E38" s="140"/>
+    <row r="38" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A38" s="144"/>
+      <c r="B38" s="145"/>
+      <c r="C38" s="151"/>
+      <c r="D38" s="149"/>
+      <c r="E38" s="149"/>
       <c r="F38" s="109"/>
       <c r="G38" s="39"/>
       <c r="H38" s="38"/>
       <c r="I38" s="40"/>
       <c r="J38" s="40"/>
       <c r="K38" s="81">
-        <f t="shared" ref="K38" si="86">+F38/26*K37*2</f>
+        <f t="shared" ref="K38" si="67">+F38/26*K37*2</f>
         <v>0</v>
       </c>
       <c r="L38" s="79">
-        <f t="shared" ref="L38" si="87">F38*L37/(26)*30%</f>
+        <f>F38*L37/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M38" s="40"/>
-      <c r="N38" s="39"/>
+      <c r="M38" s="79"/>
+      <c r="N38" s="40"/>
       <c r="O38" s="39"/>
-      <c r="P38" s="41"/>
+      <c r="P38" s="39"/>
       <c r="Q38" s="41"/>
-      <c r="R38" s="37"/>
+      <c r="R38" s="41"/>
       <c r="S38" s="37"/>
       <c r="T38" s="37"/>
-      <c r="U38" s="39"/>
-      <c r="V38" s="37"/>
+      <c r="U38" s="37"/>
+      <c r="V38" s="39"/>
       <c r="W38" s="37"/>
-      <c r="X38" s="106"/>
-      <c r="Y38" s="103">
+      <c r="X38" s="37"/>
+      <c r="Y38" s="106"/>
+      <c r="Z38" s="103">
         <f>+IFERROR(VLOOKUP(C37,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z38" s="75">
+      <c r="AA38" s="75">
         <f>+IFERROR(VLOOKUP(C37,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A39" s="139"/>
-      <c r="B39" s="138"/>
-      <c r="C39" s="162"/>
-      <c r="D39" s="149"/>
-      <c r="E39" s="140"/>
+    <row r="39" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A39" s="144"/>
+      <c r="B39" s="145"/>
+      <c r="C39" s="151"/>
+      <c r="D39" s="147"/>
+      <c r="E39" s="149"/>
       <c r="F39" s="109"/>
       <c r="G39" s="34"/>
       <c r="H39" s="38"/>
@@ -46082,67 +46133,69 @@
         <f>+'Bang TH nop'!J39</f>
         <v>0</v>
       </c>
-      <c r="M39" s="33"/>
+      <c r="M39" s="85"/>
       <c r="N39" s="33"/>
       <c r="O39" s="33"/>
-      <c r="P39" s="37"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="37"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="37"/>
+      <c r="R39" s="33"/>
       <c r="S39" s="37"/>
       <c r="T39" s="37"/>
-      <c r="U39" s="59"/>
-      <c r="V39" s="37"/>
+      <c r="U39" s="37"/>
+      <c r="V39" s="59"/>
       <c r="W39" s="37"/>
-      <c r="X39" s="106"/>
-      <c r="Y39" s="103"/>
-      <c r="Z39" s="72"/>
+      <c r="X39" s="37"/>
+      <c r="Y39" s="106"/>
+      <c r="Z39" s="103"/>
+      <c r="AA39" s="72"/>
     </row>
-    <row r="40" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A40" s="139"/>
-      <c r="B40" s="138"/>
-      <c r="C40" s="162"/>
-      <c r="D40" s="140"/>
-      <c r="E40" s="140"/>
+    <row r="40" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A40" s="144"/>
+      <c r="B40" s="145"/>
+      <c r="C40" s="151"/>
+      <c r="D40" s="149"/>
+      <c r="E40" s="149"/>
       <c r="F40" s="109"/>
       <c r="G40" s="39"/>
       <c r="H40" s="38"/>
       <c r="I40" s="40"/>
       <c r="J40" s="40"/>
       <c r="K40" s="81">
-        <f t="shared" ref="K40" si="88">+F40/26*K39*2</f>
+        <f t="shared" ref="K40" si="68">+F40/26*K39*2</f>
         <v>0</v>
       </c>
       <c r="L40" s="79">
-        <f t="shared" ref="L40" si="89">F40*L39/(26)*30%</f>
+        <f>F40*L39/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M40" s="40"/>
-      <c r="N40" s="39"/>
+      <c r="M40" s="79"/>
+      <c r="N40" s="40"/>
       <c r="O40" s="39"/>
-      <c r="P40" s="41"/>
+      <c r="P40" s="39"/>
       <c r="Q40" s="41"/>
-      <c r="R40" s="37"/>
+      <c r="R40" s="41"/>
       <c r="S40" s="37"/>
       <c r="T40" s="37"/>
-      <c r="U40" s="39"/>
-      <c r="V40" s="37"/>
+      <c r="U40" s="37"/>
+      <c r="V40" s="39"/>
       <c r="W40" s="37"/>
-      <c r="X40" s="106"/>
-      <c r="Y40" s="103">
+      <c r="X40" s="37"/>
+      <c r="Y40" s="106"/>
+      <c r="Z40" s="103">
         <f>+IFERROR(VLOOKUP(C39,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z40" s="75">
+      <c r="AA40" s="75">
         <f>+IFERROR(VLOOKUP(C39,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A41" s="139"/>
-      <c r="B41" s="138"/>
-      <c r="C41" s="162"/>
-      <c r="D41" s="149"/>
-      <c r="E41" s="140"/>
+    <row r="41" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A41" s="144"/>
+      <c r="B41" s="145"/>
+      <c r="C41" s="151"/>
+      <c r="D41" s="147"/>
+      <c r="E41" s="149"/>
       <c r="F41" s="109"/>
       <c r="G41" s="34"/>
       <c r="H41" s="38"/>
@@ -46156,67 +46209,69 @@
         <f>+'Bang TH nop'!J41</f>
         <v>0</v>
       </c>
-      <c r="M41" s="33"/>
+      <c r="M41" s="85"/>
       <c r="N41" s="33"/>
       <c r="O41" s="33"/>
-      <c r="P41" s="37"/>
-      <c r="Q41" s="33"/>
-      <c r="R41" s="37"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="37"/>
+      <c r="R41" s="33"/>
       <c r="S41" s="37"/>
       <c r="T41" s="37"/>
-      <c r="U41" s="59"/>
-      <c r="V41" s="37"/>
+      <c r="U41" s="37"/>
+      <c r="V41" s="59"/>
       <c r="W41" s="37"/>
-      <c r="X41" s="106"/>
-      <c r="Y41" s="103"/>
-      <c r="Z41" s="72"/>
+      <c r="X41" s="37"/>
+      <c r="Y41" s="106"/>
+      <c r="Z41" s="103"/>
+      <c r="AA41" s="72"/>
     </row>
-    <row r="42" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A42" s="139"/>
-      <c r="B42" s="138"/>
-      <c r="C42" s="162"/>
-      <c r="D42" s="140"/>
-      <c r="E42" s="140"/>
+    <row r="42" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A42" s="144"/>
+      <c r="B42" s="145"/>
+      <c r="C42" s="151"/>
+      <c r="D42" s="149"/>
+      <c r="E42" s="149"/>
       <c r="F42" s="109"/>
       <c r="G42" s="39"/>
       <c r="H42" s="38"/>
       <c r="I42" s="40"/>
       <c r="J42" s="40"/>
       <c r="K42" s="81">
-        <f t="shared" ref="K42" si="90">+F42/26*K41*2</f>
+        <f t="shared" ref="K42" si="69">+F42/26*K41*2</f>
         <v>0</v>
       </c>
       <c r="L42" s="79">
-        <f t="shared" ref="L42" si="91">F42*L41/(26)*30%</f>
+        <f>F42*L41/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M42" s="40"/>
-      <c r="N42" s="39"/>
+      <c r="M42" s="79"/>
+      <c r="N42" s="40"/>
       <c r="O42" s="39"/>
-      <c r="P42" s="41"/>
+      <c r="P42" s="39"/>
       <c r="Q42" s="41"/>
-      <c r="R42" s="37"/>
+      <c r="R42" s="41"/>
       <c r="S42" s="37"/>
       <c r="T42" s="37"/>
-      <c r="U42" s="39"/>
-      <c r="V42" s="37"/>
+      <c r="U42" s="37"/>
+      <c r="V42" s="39"/>
       <c r="W42" s="37"/>
-      <c r="X42" s="106"/>
-      <c r="Y42" s="103">
+      <c r="X42" s="37"/>
+      <c r="Y42" s="106"/>
+      <c r="Z42" s="103">
         <f>+IFERROR(VLOOKUP(C41,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z42" s="75">
+      <c r="AA42" s="75">
         <f>+IFERROR(VLOOKUP(C41,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A43" s="139"/>
-      <c r="B43" s="138"/>
-      <c r="C43" s="162"/>
-      <c r="D43" s="149"/>
-      <c r="E43" s="140"/>
+    <row r="43" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A43" s="144"/>
+      <c r="B43" s="145"/>
+      <c r="C43" s="151"/>
+      <c r="D43" s="147"/>
+      <c r="E43" s="149"/>
       <c r="F43" s="109"/>
       <c r="G43" s="34"/>
       <c r="H43" s="38"/>
@@ -46230,67 +46285,69 @@
         <f>+'Bang TH nop'!J43</f>
         <v>0</v>
       </c>
-      <c r="M43" s="33"/>
+      <c r="M43" s="85"/>
       <c r="N43" s="33"/>
       <c r="O43" s="33"/>
-      <c r="P43" s="37"/>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="37"/>
+      <c r="P43" s="33"/>
+      <c r="Q43" s="37"/>
+      <c r="R43" s="33"/>
       <c r="S43" s="37"/>
       <c r="T43" s="37"/>
-      <c r="U43" s="59"/>
-      <c r="V43" s="37"/>
+      <c r="U43" s="37"/>
+      <c r="V43" s="59"/>
       <c r="W43" s="37"/>
-      <c r="X43" s="106"/>
-      <c r="Y43" s="103"/>
-      <c r="Z43" s="72"/>
+      <c r="X43" s="37"/>
+      <c r="Y43" s="106"/>
+      <c r="Z43" s="103"/>
+      <c r="AA43" s="72"/>
     </row>
-    <row r="44" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A44" s="139"/>
-      <c r="B44" s="138"/>
-      <c r="C44" s="162"/>
-      <c r="D44" s="140"/>
-      <c r="E44" s="140"/>
+    <row r="44" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A44" s="144"/>
+      <c r="B44" s="145"/>
+      <c r="C44" s="151"/>
+      <c r="D44" s="149"/>
+      <c r="E44" s="149"/>
       <c r="F44" s="109"/>
       <c r="G44" s="39"/>
       <c r="H44" s="38"/>
       <c r="I44" s="40"/>
       <c r="J44" s="40"/>
       <c r="K44" s="81">
-        <f t="shared" ref="K44" si="92">+F44/26*K43*2</f>
+        <f t="shared" ref="K44" si="70">+F44/26*K43*2</f>
         <v>0</v>
       </c>
       <c r="L44" s="79">
-        <f t="shared" ref="L44" si="93">F44*L43/(26)*30%</f>
+        <f>F44*L43/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M44" s="40"/>
-      <c r="N44" s="39"/>
+      <c r="M44" s="79"/>
+      <c r="N44" s="40"/>
       <c r="O44" s="39"/>
-      <c r="P44" s="41"/>
+      <c r="P44" s="39"/>
       <c r="Q44" s="41"/>
-      <c r="R44" s="37"/>
+      <c r="R44" s="41"/>
       <c r="S44" s="37"/>
       <c r="T44" s="37"/>
-      <c r="U44" s="39"/>
-      <c r="V44" s="37"/>
+      <c r="U44" s="37"/>
+      <c r="V44" s="39"/>
       <c r="W44" s="37"/>
-      <c r="X44" s="106"/>
-      <c r="Y44" s="103">
+      <c r="X44" s="37"/>
+      <c r="Y44" s="106"/>
+      <c r="Z44" s="103">
         <f>+IFERROR(VLOOKUP(C43,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z44" s="75">
+      <c r="AA44" s="75">
         <f>+IFERROR(VLOOKUP(C43,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A45" s="139"/>
-      <c r="B45" s="138"/>
-      <c r="C45" s="162"/>
-      <c r="D45" s="149"/>
-      <c r="E45" s="140"/>
+    <row r="45" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A45" s="144"/>
+      <c r="B45" s="145"/>
+      <c r="C45" s="151"/>
+      <c r="D45" s="147"/>
+      <c r="E45" s="149"/>
       <c r="F45" s="109"/>
       <c r="G45" s="34"/>
       <c r="H45" s="38"/>
@@ -46304,67 +46361,69 @@
         <f>+'Bang TH nop'!J45</f>
         <v>0</v>
       </c>
-      <c r="M45" s="33"/>
+      <c r="M45" s="85"/>
       <c r="N45" s="33"/>
       <c r="O45" s="33"/>
-      <c r="P45" s="37"/>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="37"/>
+      <c r="P45" s="33"/>
+      <c r="Q45" s="37"/>
+      <c r="R45" s="33"/>
       <c r="S45" s="37"/>
       <c r="T45" s="37"/>
-      <c r="U45" s="59"/>
-      <c r="V45" s="37"/>
+      <c r="U45" s="37"/>
+      <c r="V45" s="59"/>
       <c r="W45" s="37"/>
-      <c r="X45" s="106"/>
-      <c r="Y45" s="103"/>
-      <c r="Z45" s="72"/>
+      <c r="X45" s="37"/>
+      <c r="Y45" s="106"/>
+      <c r="Z45" s="103"/>
+      <c r="AA45" s="72"/>
     </row>
-    <row r="46" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A46" s="139"/>
-      <c r="B46" s="138"/>
-      <c r="C46" s="162"/>
-      <c r="D46" s="140"/>
-      <c r="E46" s="140"/>
+    <row r="46" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A46" s="144"/>
+      <c r="B46" s="145"/>
+      <c r="C46" s="151"/>
+      <c r="D46" s="149"/>
+      <c r="E46" s="149"/>
       <c r="F46" s="109"/>
       <c r="G46" s="39"/>
       <c r="H46" s="38"/>
       <c r="I46" s="40"/>
       <c r="J46" s="40"/>
       <c r="K46" s="81">
-        <f t="shared" ref="K46" si="94">+F46/26*K45*2</f>
+        <f t="shared" ref="K46" si="71">+F46/26*K45*2</f>
         <v>0</v>
       </c>
       <c r="L46" s="79">
-        <f t="shared" ref="L46" si="95">F46*L45/(26)*30%</f>
+        <f>F46*L45/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M46" s="40"/>
-      <c r="N46" s="39"/>
+      <c r="M46" s="79"/>
+      <c r="N46" s="40"/>
       <c r="O46" s="39"/>
-      <c r="P46" s="41"/>
+      <c r="P46" s="39"/>
       <c r="Q46" s="41"/>
-      <c r="R46" s="37"/>
+      <c r="R46" s="41"/>
       <c r="S46" s="37"/>
       <c r="T46" s="37"/>
-      <c r="U46" s="39"/>
-      <c r="V46" s="37"/>
+      <c r="U46" s="37"/>
+      <c r="V46" s="39"/>
       <c r="W46" s="37"/>
-      <c r="X46" s="106"/>
-      <c r="Y46" s="103">
+      <c r="X46" s="37"/>
+      <c r="Y46" s="106"/>
+      <c r="Z46" s="103">
         <f>+IFERROR(VLOOKUP(C45,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z46" s="75">
+      <c r="AA46" s="75">
         <f>+IFERROR(VLOOKUP(C45,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A47" s="139"/>
-      <c r="B47" s="138"/>
-      <c r="C47" s="162"/>
-      <c r="D47" s="149"/>
-      <c r="E47" s="140"/>
+    <row r="47" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A47" s="144"/>
+      <c r="B47" s="145"/>
+      <c r="C47" s="151"/>
+      <c r="D47" s="147"/>
+      <c r="E47" s="149"/>
       <c r="F47" s="109"/>
       <c r="G47" s="34"/>
       <c r="H47" s="38"/>
@@ -46378,67 +46437,69 @@
         <f>+'Bang TH nop'!J47</f>
         <v>0</v>
       </c>
-      <c r="M47" s="33"/>
+      <c r="M47" s="85"/>
       <c r="N47" s="33"/>
       <c r="O47" s="33"/>
-      <c r="P47" s="37"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="37"/>
+      <c r="P47" s="33"/>
+      <c r="Q47" s="37"/>
+      <c r="R47" s="33"/>
       <c r="S47" s="37"/>
       <c r="T47" s="37"/>
-      <c r="U47" s="59"/>
-      <c r="V47" s="37"/>
+      <c r="U47" s="37"/>
+      <c r="V47" s="59"/>
       <c r="W47" s="37"/>
-      <c r="X47" s="106"/>
-      <c r="Y47" s="103"/>
-      <c r="Z47" s="72"/>
+      <c r="X47" s="37"/>
+      <c r="Y47" s="106"/>
+      <c r="Z47" s="103"/>
+      <c r="AA47" s="72"/>
     </row>
-    <row r="48" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A48" s="139"/>
-      <c r="B48" s="138"/>
-      <c r="C48" s="162"/>
-      <c r="D48" s="140"/>
-      <c r="E48" s="140"/>
+    <row r="48" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A48" s="144"/>
+      <c r="B48" s="145"/>
+      <c r="C48" s="151"/>
+      <c r="D48" s="149"/>
+      <c r="E48" s="149"/>
       <c r="F48" s="109"/>
       <c r="G48" s="39"/>
       <c r="H48" s="38"/>
       <c r="I48" s="40"/>
       <c r="J48" s="40"/>
       <c r="K48" s="81">
-        <f t="shared" ref="K48" si="96">+F48/26*K47*2</f>
+        <f t="shared" ref="K48" si="72">+F48/26*K47*2</f>
         <v>0</v>
       </c>
       <c r="L48" s="79">
-        <f t="shared" ref="L48" si="97">F48*L47/(26)*30%</f>
+        <f>F48*L47/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M48" s="40"/>
-      <c r="N48" s="39"/>
+      <c r="M48" s="79"/>
+      <c r="N48" s="40"/>
       <c r="O48" s="39"/>
-      <c r="P48" s="41"/>
+      <c r="P48" s="39"/>
       <c r="Q48" s="41"/>
-      <c r="R48" s="37"/>
+      <c r="R48" s="41"/>
       <c r="S48" s="37"/>
       <c r="T48" s="37"/>
-      <c r="U48" s="39"/>
-      <c r="V48" s="37"/>
+      <c r="U48" s="37"/>
+      <c r="V48" s="39"/>
       <c r="W48" s="37"/>
-      <c r="X48" s="106"/>
-      <c r="Y48" s="103">
+      <c r="X48" s="37"/>
+      <c r="Y48" s="106"/>
+      <c r="Z48" s="103">
         <f>+IFERROR(VLOOKUP(C47,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z48" s="75">
+      <c r="AA48" s="75">
         <f>+IFERROR(VLOOKUP(C47,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A49" s="139"/>
-      <c r="B49" s="138"/>
-      <c r="C49" s="162"/>
-      <c r="D49" s="149"/>
-      <c r="E49" s="140"/>
+    <row r="49" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A49" s="144"/>
+      <c r="B49" s="145"/>
+      <c r="C49" s="151"/>
+      <c r="D49" s="147"/>
+      <c r="E49" s="149"/>
       <c r="F49" s="109"/>
       <c r="G49" s="34"/>
       <c r="H49" s="38"/>
@@ -46452,67 +46513,69 @@
         <f>+'Bang TH nop'!J49</f>
         <v>0</v>
       </c>
-      <c r="M49" s="33"/>
+      <c r="M49" s="85"/>
       <c r="N49" s="33"/>
       <c r="O49" s="33"/>
-      <c r="P49" s="37"/>
-      <c r="Q49" s="33"/>
-      <c r="R49" s="37"/>
+      <c r="P49" s="33"/>
+      <c r="Q49" s="37"/>
+      <c r="R49" s="33"/>
       <c r="S49" s="37"/>
       <c r="T49" s="37"/>
-      <c r="U49" s="59"/>
-      <c r="V49" s="37"/>
+      <c r="U49" s="37"/>
+      <c r="V49" s="59"/>
       <c r="W49" s="37"/>
-      <c r="X49" s="106"/>
-      <c r="Y49" s="103"/>
-      <c r="Z49" s="72"/>
+      <c r="X49" s="37"/>
+      <c r="Y49" s="106"/>
+      <c r="Z49" s="103"/>
+      <c r="AA49" s="72"/>
     </row>
-    <row r="50" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A50" s="139"/>
-      <c r="B50" s="138"/>
-      <c r="C50" s="162"/>
-      <c r="D50" s="140"/>
-      <c r="E50" s="140"/>
+    <row r="50" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A50" s="144"/>
+      <c r="B50" s="145"/>
+      <c r="C50" s="151"/>
+      <c r="D50" s="149"/>
+      <c r="E50" s="149"/>
       <c r="F50" s="109"/>
       <c r="G50" s="39"/>
       <c r="H50" s="38"/>
       <c r="I50" s="40"/>
       <c r="J50" s="40"/>
       <c r="K50" s="81">
-        <f t="shared" ref="K50" si="98">+F50/26*K49*2</f>
+        <f t="shared" ref="K50" si="73">+F50/26*K49*2</f>
         <v>0</v>
       </c>
       <c r="L50" s="79">
-        <f t="shared" ref="L50" si="99">F50*L49/(26)*30%</f>
+        <f>F50*L49/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M50" s="40"/>
-      <c r="N50" s="39"/>
+      <c r="M50" s="79"/>
+      <c r="N50" s="40"/>
       <c r="O50" s="39"/>
-      <c r="P50" s="41"/>
+      <c r="P50" s="39"/>
       <c r="Q50" s="41"/>
-      <c r="R50" s="37"/>
+      <c r="R50" s="41"/>
       <c r="S50" s="37"/>
       <c r="T50" s="37"/>
-      <c r="U50" s="39"/>
-      <c r="V50" s="37"/>
+      <c r="U50" s="37"/>
+      <c r="V50" s="39"/>
       <c r="W50" s="37"/>
-      <c r="X50" s="106"/>
-      <c r="Y50" s="103">
+      <c r="X50" s="37"/>
+      <c r="Y50" s="106"/>
+      <c r="Z50" s="103">
         <f>+IFERROR(VLOOKUP(C49,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z50" s="75">
+      <c r="AA50" s="75">
         <f>+IFERROR(VLOOKUP(C49,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A51" s="139"/>
-      <c r="B51" s="138"/>
-      <c r="C51" s="162"/>
-      <c r="D51" s="140"/>
-      <c r="E51" s="140"/>
+    <row r="51" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A51" s="144"/>
+      <c r="B51" s="145"/>
+      <c r="C51" s="151"/>
+      <c r="D51" s="149"/>
+      <c r="E51" s="149"/>
       <c r="F51" s="109"/>
       <c r="G51" s="34"/>
       <c r="H51" s="38"/>
@@ -46526,67 +46589,69 @@
         <f>+'Bang TH nop'!J51</f>
         <v>0</v>
       </c>
-      <c r="M51" s="33"/>
+      <c r="M51" s="85"/>
       <c r="N51" s="33"/>
       <c r="O51" s="33"/>
-      <c r="P51" s="37"/>
-      <c r="Q51" s="33"/>
-      <c r="R51" s="37"/>
+      <c r="P51" s="33"/>
+      <c r="Q51" s="37"/>
+      <c r="R51" s="33"/>
       <c r="S51" s="37"/>
       <c r="T51" s="37"/>
-      <c r="U51" s="59"/>
-      <c r="V51" s="37"/>
+      <c r="U51" s="37"/>
+      <c r="V51" s="59"/>
       <c r="W51" s="37"/>
-      <c r="X51" s="106"/>
-      <c r="Y51" s="103"/>
-      <c r="Z51" s="72"/>
+      <c r="X51" s="37"/>
+      <c r="Y51" s="106"/>
+      <c r="Z51" s="103"/>
+      <c r="AA51" s="72"/>
     </row>
-    <row r="52" spans="1:26" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A52" s="139"/>
-      <c r="B52" s="138"/>
-      <c r="C52" s="162"/>
-      <c r="D52" s="140"/>
-      <c r="E52" s="140"/>
+    <row r="52" spans="1:27" ht="15.6" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A52" s="144"/>
+      <c r="B52" s="145"/>
+      <c r="C52" s="151"/>
+      <c r="D52" s="149"/>
+      <c r="E52" s="149"/>
       <c r="F52" s="109"/>
       <c r="G52" s="39"/>
       <c r="H52" s="38"/>
       <c r="I52" s="40"/>
       <c r="J52" s="40"/>
       <c r="K52" s="81">
-        <f t="shared" ref="K52" si="100">+F52/26*K51*2</f>
+        <f t="shared" ref="K52" si="74">+F52/26*K51*2</f>
         <v>0</v>
       </c>
       <c r="L52" s="79">
-        <f t="shared" ref="L52" si="101">F52*L51/(26)*30%</f>
+        <f>F52*L51/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M52" s="40"/>
-      <c r="N52" s="39"/>
+      <c r="M52" s="79"/>
+      <c r="N52" s="40"/>
       <c r="O52" s="39"/>
-      <c r="P52" s="41"/>
+      <c r="P52" s="39"/>
       <c r="Q52" s="41"/>
-      <c r="R52" s="37"/>
+      <c r="R52" s="41"/>
       <c r="S52" s="37"/>
       <c r="T52" s="37"/>
-      <c r="U52" s="39"/>
-      <c r="V52" s="37"/>
+      <c r="U52" s="37"/>
+      <c r="V52" s="39"/>
       <c r="W52" s="37"/>
-      <c r="X52" s="106"/>
-      <c r="Y52" s="103">
+      <c r="X52" s="37"/>
+      <c r="Y52" s="106"/>
+      <c r="Z52" s="103">
         <f>+IFERROR(VLOOKUP(C51,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z52" s="75">
+      <c r="AA52" s="75">
         <f>+IFERROR(VLOOKUP(C51,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A53" s="139"/>
-      <c r="B53" s="138"/>
-      <c r="C53" s="162"/>
-      <c r="D53" s="140"/>
-      <c r="E53" s="140"/>
+    <row r="53" spans="1:27" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A53" s="144"/>
+      <c r="B53" s="145"/>
+      <c r="C53" s="151"/>
+      <c r="D53" s="149"/>
+      <c r="E53" s="149"/>
       <c r="F53" s="109"/>
       <c r="G53" s="34"/>
       <c r="H53" s="38"/>
@@ -46600,67 +46665,69 @@
         <f>+'Bang TH nop'!J53</f>
         <v>0</v>
       </c>
-      <c r="M53" s="33"/>
+      <c r="M53" s="85"/>
       <c r="N53" s="33"/>
       <c r="O53" s="33"/>
-      <c r="P53" s="37"/>
-      <c r="Q53" s="33"/>
-      <c r="R53" s="37"/>
+      <c r="P53" s="33"/>
+      <c r="Q53" s="37"/>
+      <c r="R53" s="33"/>
       <c r="S53" s="37"/>
       <c r="T53" s="37"/>
-      <c r="U53" s="59"/>
-      <c r="V53" s="37"/>
+      <c r="U53" s="37"/>
+      <c r="V53" s="59"/>
       <c r="W53" s="37"/>
-      <c r="X53" s="106"/>
-      <c r="Y53" s="103"/>
-      <c r="Z53" s="72"/>
+      <c r="X53" s="37"/>
+      <c r="Y53" s="106"/>
+      <c r="Z53" s="103"/>
+      <c r="AA53" s="72"/>
     </row>
-    <row r="54" spans="1:26" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A54" s="139"/>
-      <c r="B54" s="138"/>
-      <c r="C54" s="162"/>
-      <c r="D54" s="140"/>
-      <c r="E54" s="140"/>
+    <row r="54" spans="1:27" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A54" s="144"/>
+      <c r="B54" s="145"/>
+      <c r="C54" s="151"/>
+      <c r="D54" s="149"/>
+      <c r="E54" s="149"/>
       <c r="F54" s="109"/>
       <c r="G54" s="39"/>
       <c r="H54" s="38"/>
       <c r="I54" s="40"/>
       <c r="J54" s="40"/>
       <c r="K54" s="81">
-        <f t="shared" ref="K54" si="102">+F54/26*K53*2</f>
+        <f t="shared" ref="K54" si="75">+F54/26*K53*2</f>
         <v>0</v>
       </c>
       <c r="L54" s="79">
-        <f t="shared" ref="L54" si="103">F54*L53/(26)*30%</f>
+        <f>F54*L53/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M54" s="40"/>
-      <c r="N54" s="39"/>
+      <c r="M54" s="79"/>
+      <c r="N54" s="40"/>
       <c r="O54" s="39"/>
-      <c r="P54" s="41"/>
+      <c r="P54" s="39"/>
       <c r="Q54" s="41"/>
-      <c r="R54" s="37"/>
+      <c r="R54" s="41"/>
       <c r="S54" s="37"/>
       <c r="T54" s="37"/>
-      <c r="U54" s="39"/>
-      <c r="V54" s="37"/>
+      <c r="U54" s="37"/>
+      <c r="V54" s="39"/>
       <c r="W54" s="37"/>
-      <c r="X54" s="106"/>
-      <c r="Y54" s="103">
+      <c r="X54" s="37"/>
+      <c r="Y54" s="106"/>
+      <c r="Z54" s="103">
         <f>+IFERROR(VLOOKUP(C53,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z54" s="75">
+      <c r="AA54" s="75">
         <f>+IFERROR(VLOOKUP(C53,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A55" s="139"/>
-      <c r="B55" s="138"/>
-      <c r="C55" s="162"/>
-      <c r="D55" s="140"/>
-      <c r="E55" s="140"/>
+    <row r="55" spans="1:27" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A55" s="144"/>
+      <c r="B55" s="145"/>
+      <c r="C55" s="151"/>
+      <c r="D55" s="149"/>
+      <c r="E55" s="149"/>
       <c r="F55" s="109"/>
       <c r="G55" s="34"/>
       <c r="H55" s="38"/>
@@ -46674,67 +46741,69 @@
         <f>+'Bang TH nop'!J55</f>
         <v>0</v>
       </c>
-      <c r="M55" s="33"/>
+      <c r="M55" s="85"/>
       <c r="N55" s="33"/>
       <c r="O55" s="33"/>
-      <c r="P55" s="37"/>
-      <c r="Q55" s="33"/>
-      <c r="R55" s="37"/>
+      <c r="P55" s="33"/>
+      <c r="Q55" s="37"/>
+      <c r="R55" s="33"/>
       <c r="S55" s="37"/>
       <c r="T55" s="37"/>
-      <c r="U55" s="59"/>
-      <c r="V55" s="37"/>
+      <c r="U55" s="37"/>
+      <c r="V55" s="59"/>
       <c r="W55" s="37"/>
-      <c r="X55" s="106"/>
-      <c r="Y55" s="103"/>
-      <c r="Z55" s="72"/>
+      <c r="X55" s="37"/>
+      <c r="Y55" s="106"/>
+      <c r="Z55" s="103"/>
+      <c r="AA55" s="72"/>
     </row>
-    <row r="56" spans="1:26" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A56" s="139"/>
-      <c r="B56" s="138"/>
-      <c r="C56" s="162"/>
-      <c r="D56" s="140"/>
-      <c r="E56" s="140"/>
+    <row r="56" spans="1:27" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A56" s="144"/>
+      <c r="B56" s="145"/>
+      <c r="C56" s="151"/>
+      <c r="D56" s="149"/>
+      <c r="E56" s="149"/>
       <c r="F56" s="109"/>
       <c r="G56" s="39"/>
       <c r="H56" s="38"/>
       <c r="I56" s="40"/>
       <c r="J56" s="40"/>
       <c r="K56" s="81">
-        <f t="shared" ref="K56" si="104">+F56/26*K55*2</f>
+        <f t="shared" ref="K56" si="76">+F56/26*K55*2</f>
         <v>0</v>
       </c>
       <c r="L56" s="79">
-        <f t="shared" ref="L56" si="105">F56*L55/(26)*30%</f>
+        <f>F56*L55/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M56" s="40"/>
-      <c r="N56" s="39"/>
+      <c r="M56" s="79"/>
+      <c r="N56" s="40"/>
       <c r="O56" s="39"/>
-      <c r="P56" s="41"/>
+      <c r="P56" s="39"/>
       <c r="Q56" s="41"/>
-      <c r="R56" s="37"/>
+      <c r="R56" s="41"/>
       <c r="S56" s="37"/>
       <c r="T56" s="37"/>
-      <c r="U56" s="39"/>
-      <c r="V56" s="37"/>
+      <c r="U56" s="37"/>
+      <c r="V56" s="39"/>
       <c r="W56" s="37"/>
-      <c r="X56" s="106"/>
-      <c r="Y56" s="103">
+      <c r="X56" s="37"/>
+      <c r="Y56" s="106"/>
+      <c r="Z56" s="103">
         <f>+IFERROR(VLOOKUP(C55,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z56" s="75">
+      <c r="AA56" s="75">
         <f>+IFERROR(VLOOKUP(C55,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A57" s="139"/>
-      <c r="B57" s="138"/>
-      <c r="C57" s="162"/>
-      <c r="D57" s="140"/>
-      <c r="E57" s="140"/>
+    <row r="57" spans="1:27" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A57" s="144"/>
+      <c r="B57" s="145"/>
+      <c r="C57" s="151"/>
+      <c r="D57" s="149"/>
+      <c r="E57" s="149"/>
       <c r="F57" s="109"/>
       <c r="G57" s="34"/>
       <c r="H57" s="38"/>
@@ -46748,67 +46817,69 @@
         <f>+'Bang TH nop'!J57</f>
         <v>0</v>
       </c>
-      <c r="M57" s="33"/>
+      <c r="M57" s="85"/>
       <c r="N57" s="33"/>
       <c r="O57" s="33"/>
-      <c r="P57" s="37"/>
-      <c r="Q57" s="33"/>
-      <c r="R57" s="37"/>
+      <c r="P57" s="33"/>
+      <c r="Q57" s="37"/>
+      <c r="R57" s="33"/>
       <c r="S57" s="37"/>
       <c r="T57" s="37"/>
-      <c r="U57" s="59"/>
-      <c r="V57" s="37"/>
+      <c r="U57" s="37"/>
+      <c r="V57" s="59"/>
       <c r="W57" s="37"/>
-      <c r="X57" s="106"/>
-      <c r="Y57" s="103"/>
-      <c r="Z57" s="72"/>
+      <c r="X57" s="37"/>
+      <c r="Y57" s="106"/>
+      <c r="Z57" s="103"/>
+      <c r="AA57" s="72"/>
     </row>
-    <row r="58" spans="1:26" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A58" s="139"/>
-      <c r="B58" s="138"/>
-      <c r="C58" s="162"/>
-      <c r="D58" s="140"/>
-      <c r="E58" s="140"/>
+    <row r="58" spans="1:27" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A58" s="144"/>
+      <c r="B58" s="145"/>
+      <c r="C58" s="151"/>
+      <c r="D58" s="149"/>
+      <c r="E58" s="149"/>
       <c r="F58" s="109"/>
       <c r="G58" s="39"/>
       <c r="H58" s="38"/>
       <c r="I58" s="40"/>
       <c r="J58" s="40"/>
       <c r="K58" s="81">
-        <f t="shared" ref="K58" si="106">+F58/26*K57*2</f>
+        <f t="shared" ref="K58" si="77">+F58/26*K57*2</f>
         <v>0</v>
       </c>
       <c r="L58" s="79">
-        <f t="shared" ref="L58" si="107">F58*L57/(26)*30%</f>
+        <f>F58*L57/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M58" s="40"/>
-      <c r="N58" s="39"/>
+      <c r="M58" s="79"/>
+      <c r="N58" s="40"/>
       <c r="O58" s="39"/>
-      <c r="P58" s="41"/>
+      <c r="P58" s="39"/>
       <c r="Q58" s="41"/>
-      <c r="R58" s="37"/>
+      <c r="R58" s="41"/>
       <c r="S58" s="37"/>
       <c r="T58" s="37"/>
-      <c r="U58" s="39"/>
-      <c r="V58" s="37"/>
+      <c r="U58" s="37"/>
+      <c r="V58" s="39"/>
       <c r="W58" s="37"/>
-      <c r="X58" s="106"/>
-      <c r="Y58" s="103">
+      <c r="X58" s="37"/>
+      <c r="Y58" s="106"/>
+      <c r="Z58" s="103">
         <f>+IFERROR(VLOOKUP(C57,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z58" s="75">
+      <c r="AA58" s="75">
         <f>+IFERROR(VLOOKUP(C57,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:26" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A59" s="139"/>
-      <c r="B59" s="138"/>
-      <c r="C59" s="162"/>
-      <c r="D59" s="140"/>
-      <c r="E59" s="140"/>
+    <row r="59" spans="1:27" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A59" s="144"/>
+      <c r="B59" s="145"/>
+      <c r="C59" s="151"/>
+      <c r="D59" s="149"/>
+      <c r="E59" s="149"/>
       <c r="F59" s="109"/>
       <c r="G59" s="34"/>
       <c r="H59" s="38"/>
@@ -46822,67 +46893,69 @@
         <f>+'Bang TH nop'!J59</f>
         <v>0</v>
       </c>
-      <c r="M59" s="33"/>
+      <c r="M59" s="85"/>
       <c r="N59" s="33"/>
       <c r="O59" s="33"/>
-      <c r="P59" s="37"/>
-      <c r="Q59" s="33"/>
-      <c r="R59" s="37"/>
+      <c r="P59" s="33"/>
+      <c r="Q59" s="37"/>
+      <c r="R59" s="33"/>
       <c r="S59" s="37"/>
       <c r="T59" s="37"/>
-      <c r="U59" s="59"/>
-      <c r="V59" s="37"/>
+      <c r="U59" s="37"/>
+      <c r="V59" s="59"/>
       <c r="W59" s="37"/>
-      <c r="X59" s="106"/>
-      <c r="Y59" s="103"/>
-      <c r="Z59" s="72"/>
+      <c r="X59" s="37"/>
+      <c r="Y59" s="106"/>
+      <c r="Z59" s="103"/>
+      <c r="AA59" s="72"/>
     </row>
-    <row r="60" spans="1:26" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A60" s="139"/>
-      <c r="B60" s="138"/>
-      <c r="C60" s="162"/>
-      <c r="D60" s="140"/>
-      <c r="E60" s="140"/>
+    <row r="60" spans="1:27" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A60" s="144"/>
+      <c r="B60" s="145"/>
+      <c r="C60" s="151"/>
+      <c r="D60" s="149"/>
+      <c r="E60" s="149"/>
       <c r="F60" s="109"/>
       <c r="G60" s="39"/>
       <c r="H60" s="38"/>
       <c r="I60" s="40"/>
       <c r="J60" s="40"/>
       <c r="K60" s="81">
-        <f t="shared" ref="K60" si="108">+F60/26*K59*2</f>
+        <f t="shared" ref="K60" si="78">+F60/26*K59*2</f>
         <v>0</v>
       </c>
       <c r="L60" s="79">
-        <f t="shared" ref="L60" si="109">F60*L59/(26)*30%</f>
+        <f>F60*L59/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M60" s="40"/>
-      <c r="N60" s="39"/>
+      <c r="M60" s="79"/>
+      <c r="N60" s="40"/>
       <c r="O60" s="39"/>
-      <c r="P60" s="41"/>
+      <c r="P60" s="39"/>
       <c r="Q60" s="41"/>
-      <c r="R60" s="37"/>
+      <c r="R60" s="41"/>
       <c r="S60" s="37"/>
       <c r="T60" s="37"/>
-      <c r="U60" s="39"/>
-      <c r="V60" s="37"/>
+      <c r="U60" s="37"/>
+      <c r="V60" s="39"/>
       <c r="W60" s="37"/>
-      <c r="X60" s="106"/>
-      <c r="Y60" s="103">
+      <c r="X60" s="37"/>
+      <c r="Y60" s="106"/>
+      <c r="Z60" s="103">
         <f>+IFERROR(VLOOKUP(C59,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z60" s="75">
+      <c r="AA60" s="75">
         <f>+IFERROR(VLOOKUP(C59,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:26" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A61" s="139"/>
-      <c r="B61" s="138"/>
-      <c r="C61" s="162"/>
-      <c r="D61" s="140"/>
-      <c r="E61" s="140"/>
+    <row r="61" spans="1:27" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A61" s="144"/>
+      <c r="B61" s="145"/>
+      <c r="C61" s="151"/>
+      <c r="D61" s="149"/>
+      <c r="E61" s="149"/>
       <c r="F61" s="109"/>
       <c r="G61" s="34"/>
       <c r="H61" s="38"/>
@@ -46896,67 +46969,69 @@
         <f>+'Bang TH nop'!J61</f>
         <v>0</v>
       </c>
-      <c r="M61" s="33"/>
+      <c r="M61" s="85"/>
       <c r="N61" s="33"/>
       <c r="O61" s="33"/>
-      <c r="P61" s="37"/>
-      <c r="Q61" s="33"/>
-      <c r="R61" s="37"/>
+      <c r="P61" s="33"/>
+      <c r="Q61" s="37"/>
+      <c r="R61" s="33"/>
       <c r="S61" s="37"/>
       <c r="T61" s="37"/>
-      <c r="U61" s="59"/>
-      <c r="V61" s="37"/>
+      <c r="U61" s="37"/>
+      <c r="V61" s="59"/>
       <c r="W61" s="37"/>
-      <c r="X61" s="106"/>
-      <c r="Y61" s="103"/>
-      <c r="Z61" s="72"/>
+      <c r="X61" s="37"/>
+      <c r="Y61" s="106"/>
+      <c r="Z61" s="103"/>
+      <c r="AA61" s="72"/>
     </row>
-    <row r="62" spans="1:26" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A62" s="139"/>
-      <c r="B62" s="138"/>
-      <c r="C62" s="162"/>
-      <c r="D62" s="140"/>
-      <c r="E62" s="140"/>
+    <row r="62" spans="1:27" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A62" s="144"/>
+      <c r="B62" s="145"/>
+      <c r="C62" s="151"/>
+      <c r="D62" s="149"/>
+      <c r="E62" s="149"/>
       <c r="F62" s="109"/>
       <c r="G62" s="39"/>
       <c r="H62" s="38"/>
       <c r="I62" s="40"/>
       <c r="J62" s="40"/>
       <c r="K62" s="81">
-        <f t="shared" ref="K62" si="110">+F62/26*K61*2</f>
+        <f t="shared" ref="K62" si="79">+F62/26*K61*2</f>
         <v>0</v>
       </c>
       <c r="L62" s="79">
-        <f t="shared" ref="L62" si="111">F62*L61/(26)*30%</f>
+        <f>F62*L61/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M62" s="40"/>
-      <c r="N62" s="39"/>
+      <c r="M62" s="79"/>
+      <c r="N62" s="40"/>
       <c r="O62" s="39"/>
-      <c r="P62" s="41"/>
+      <c r="P62" s="39"/>
       <c r="Q62" s="41"/>
-      <c r="R62" s="37"/>
+      <c r="R62" s="41"/>
       <c r="S62" s="37"/>
       <c r="T62" s="37"/>
-      <c r="U62" s="39"/>
-      <c r="V62" s="37"/>
+      <c r="U62" s="37"/>
+      <c r="V62" s="39"/>
       <c r="W62" s="37"/>
-      <c r="X62" s="106"/>
-      <c r="Y62" s="103">
+      <c r="X62" s="37"/>
+      <c r="Y62" s="106"/>
+      <c r="Z62" s="103">
         <f>+IFERROR(VLOOKUP(C61,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z62" s="75">
+      <c r="AA62" s="75">
         <f>+IFERROR(VLOOKUP(C61,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:26" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A63" s="139"/>
-      <c r="B63" s="138"/>
-      <c r="C63" s="139"/>
-      <c r="D63" s="140"/>
-      <c r="E63" s="140"/>
+    <row r="63" spans="1:27" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A63" s="144"/>
+      <c r="B63" s="145"/>
+      <c r="C63" s="144"/>
+      <c r="D63" s="149"/>
+      <c r="E63" s="149"/>
       <c r="F63" s="109"/>
       <c r="G63" s="34"/>
       <c r="H63" s="38"/>
@@ -46970,67 +47045,69 @@
         <f>+'Bang TH nop'!J63</f>
         <v>0</v>
       </c>
-      <c r="M63" s="33"/>
+      <c r="M63" s="85"/>
       <c r="N63" s="33"/>
       <c r="O63" s="33"/>
-      <c r="P63" s="37"/>
-      <c r="Q63" s="33"/>
-      <c r="R63" s="37"/>
+      <c r="P63" s="33"/>
+      <c r="Q63" s="37"/>
+      <c r="R63" s="33"/>
       <c r="S63" s="37"/>
       <c r="T63" s="37"/>
-      <c r="U63" s="59"/>
-      <c r="V63" s="37"/>
+      <c r="U63" s="37"/>
+      <c r="V63" s="59"/>
       <c r="W63" s="37"/>
-      <c r="X63" s="106"/>
-      <c r="Y63" s="103"/>
-      <c r="Z63" s="72"/>
+      <c r="X63" s="37"/>
+      <c r="Y63" s="106"/>
+      <c r="Z63" s="103"/>
+      <c r="AA63" s="72"/>
     </row>
-    <row r="64" spans="1:26" ht="15" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A64" s="139"/>
-      <c r="B64" s="138"/>
-      <c r="C64" s="139"/>
-      <c r="D64" s="140"/>
-      <c r="E64" s="140"/>
+    <row r="64" spans="1:27" ht="15" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A64" s="144"/>
+      <c r="B64" s="145"/>
+      <c r="C64" s="144"/>
+      <c r="D64" s="149"/>
+      <c r="E64" s="149"/>
       <c r="F64" s="109"/>
       <c r="G64" s="39"/>
       <c r="H64" s="38"/>
       <c r="I64" s="40"/>
       <c r="J64" s="40"/>
       <c r="K64" s="81">
-        <f t="shared" ref="K64" si="112">+F64/26*K63*2</f>
+        <f t="shared" ref="K64" si="80">+F64/26*K63*2</f>
         <v>0</v>
       </c>
       <c r="L64" s="79">
-        <f t="shared" ref="L64" si="113">F64*L63/(26)*30%</f>
+        <f>F64*L63/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M64" s="40"/>
-      <c r="N64" s="39"/>
+      <c r="M64" s="79"/>
+      <c r="N64" s="40"/>
       <c r="O64" s="39"/>
-      <c r="P64" s="41"/>
+      <c r="P64" s="39"/>
       <c r="Q64" s="41"/>
-      <c r="R64" s="37"/>
+      <c r="R64" s="41"/>
       <c r="S64" s="37"/>
       <c r="T64" s="37"/>
-      <c r="U64" s="39"/>
-      <c r="V64" s="37"/>
+      <c r="U64" s="37"/>
+      <c r="V64" s="39"/>
       <c r="W64" s="37"/>
-      <c r="X64" s="106"/>
-      <c r="Y64" s="103">
+      <c r="X64" s="37"/>
+      <c r="Y64" s="106"/>
+      <c r="Z64" s="103">
         <f>+IFERROR(VLOOKUP(C63,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z64" s="75">
+      <c r="AA64" s="75">
         <f>+IFERROR(VLOOKUP(C63,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:30 11518:16381" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A65" s="139"/>
-      <c r="B65" s="138"/>
-      <c r="C65" s="139"/>
-      <c r="D65" s="140"/>
-      <c r="E65" s="140"/>
+    <row r="65" spans="1:31 11519:16382" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A65" s="144"/>
+      <c r="B65" s="145"/>
+      <c r="C65" s="144"/>
+      <c r="D65" s="149"/>
+      <c r="E65" s="149"/>
       <c r="F65" s="109"/>
       <c r="G65" s="34"/>
       <c r="H65" s="38"/>
@@ -47044,67 +47121,69 @@
         <f>+'Bang TH nop'!J65</f>
         <v>0</v>
       </c>
-      <c r="M65" s="33"/>
+      <c r="M65" s="85"/>
       <c r="N65" s="33"/>
       <c r="O65" s="33"/>
-      <c r="P65" s="37"/>
-      <c r="Q65" s="33"/>
-      <c r="R65" s="37"/>
+      <c r="P65" s="33"/>
+      <c r="Q65" s="37"/>
+      <c r="R65" s="33"/>
       <c r="S65" s="37"/>
       <c r="T65" s="37"/>
-      <c r="U65" s="59"/>
-      <c r="V65" s="37"/>
+      <c r="U65" s="37"/>
+      <c r="V65" s="59"/>
       <c r="W65" s="37"/>
-      <c r="X65" s="106"/>
-      <c r="Y65" s="103"/>
-      <c r="Z65" s="72"/>
+      <c r="X65" s="37"/>
+      <c r="Y65" s="106"/>
+      <c r="Z65" s="103"/>
+      <c r="AA65" s="72"/>
     </row>
-    <row r="66" spans="1:30 11518:16381" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="A66" s="139"/>
-      <c r="B66" s="138"/>
-      <c r="C66" s="139"/>
-      <c r="D66" s="140"/>
-      <c r="E66" s="140"/>
+    <row r="66" spans="1:31 11519:16382" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
+      <c r="A66" s="144"/>
+      <c r="B66" s="145"/>
+      <c r="C66" s="144"/>
+      <c r="D66" s="149"/>
+      <c r="E66" s="149"/>
       <c r="F66" s="109"/>
       <c r="G66" s="39"/>
       <c r="H66" s="38"/>
       <c r="I66" s="40"/>
       <c r="J66" s="40"/>
       <c r="K66" s="81">
-        <f t="shared" ref="K66" si="114">+F66/26*K65*2</f>
+        <f t="shared" ref="K66" si="81">+F66/26*K65*2</f>
         <v>0</v>
       </c>
       <c r="L66" s="79">
-        <f t="shared" ref="L66" si="115">F66*L65/(26)*30%</f>
+        <f>F66*L65/(26)*30%</f>
         <v>0</v>
       </c>
-      <c r="M66" s="40"/>
-      <c r="N66" s="39"/>
+      <c r="M66" s="79"/>
+      <c r="N66" s="40"/>
       <c r="O66" s="39"/>
-      <c r="P66" s="41"/>
+      <c r="P66" s="39"/>
       <c r="Q66" s="41"/>
-      <c r="R66" s="37"/>
+      <c r="R66" s="41"/>
       <c r="S66" s="37"/>
       <c r="T66" s="37"/>
-      <c r="U66" s="39"/>
-      <c r="V66" s="37"/>
+      <c r="U66" s="37"/>
+      <c r="V66" s="39"/>
       <c r="W66" s="37"/>
-      <c r="X66" s="106"/>
-      <c r="Y66" s="103">
+      <c r="X66" s="37"/>
+      <c r="Y66" s="106"/>
+      <c r="Z66" s="103">
         <f>+IFERROR(VLOOKUP(C65,'[2]Bản gốc T10'!$C$1:$J$1000,8,0),0)</f>
         <v>0</v>
       </c>
-      <c r="Z66" s="75">
+      <c r="AA66" s="75">
         <f>+IFERROR(VLOOKUP(C65,'[2]Bản gốc T10'!$C$1:$F$1000,4,0),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:30 11518:16381" collapsed="1">
-      <c r="A67" s="139"/>
-      <c r="B67" s="160" t="s">
+    <row r="67" spans="1:31 11519:16382" collapsed="1">
+      <c r="A67" s="144"/>
+      <c r="B67" s="152" t="s">
         <v>31</v>
       </c>
-      <c r="C67" s="161"/>
+      <c r="C67" s="153"/>
       <c r="D67" s="42"/>
       <c r="E67" s="42"/>
       <c r="F67" s="42"/>
@@ -47117,11 +47196,11 @@
         <v>0</v>
       </c>
       <c r="I67" s="42">
-        <f t="shared" ref="G67:W68" si="116">I9+I11+I13+I15+I17+I19+I21+I23+I25+I27+I29+I31+I33+I35+I37+I39+I41+I43+I45+I47+I49+I51</f>
+        <f t="shared" ref="G67:X68" si="82">I9+I11+I13+I15+I17+I19+I21+I23+I25+I27+I29+I31+I33+I35+I37+I39+I41+I43+I45+I47+I49+I51</f>
         <v>0</v>
       </c>
       <c r="J67" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="K67" s="80">
@@ -47133,57 +47212,61 @@
         <v>0</v>
       </c>
       <c r="M67" s="42">
-        <f t="shared" si="116"/>
+        <f>M9+M11+M13+M15+M17+M19+M21+M23+M25+M27+M29+M31+M33+M35+M37+M39+M41+M43+M45+M47+M49+M51</f>
         <v>0</v>
       </c>
       <c r="N67" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="O67" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="P67" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="Q67" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
-      <c r="R67" s="43">
-        <f t="shared" si="116"/>
+      <c r="R67" s="42">
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
-      <c r="S67" s="43"/>
-      <c r="T67" s="42">
-        <f t="shared" si="116"/>
+      <c r="S67" s="43">
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
+      <c r="T67" s="43"/>
       <c r="U67" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="V67" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="W67" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
-      <c r="X67" s="107"/>
+      <c r="X67" s="42">
+        <f t="shared" si="82"/>
+        <v>0</v>
+      </c>
+      <c r="Y67" s="107"/>
     </row>
-    <row r="68" spans="1:30 11518:16381" ht="21.75" customHeight="1">
-      <c r="A68" s="139"/>
-      <c r="B68" s="160"/>
-      <c r="C68" s="161"/>
+    <row r="68" spans="1:31 11519:16382" ht="21.75" customHeight="1">
+      <c r="A68" s="144"/>
+      <c r="B68" s="152"/>
+      <c r="C68" s="153"/>
       <c r="D68" s="42"/>
       <c r="E68" s="42"/>
       <c r="F68" s="42"/>
       <c r="G68" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="H68" s="42">
@@ -47191,11 +47274,11 @@
         <v>0</v>
       </c>
       <c r="I68" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="J68" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="K68" s="42">
@@ -47211,72 +47294,76 @@
         <v>0</v>
       </c>
       <c r="N68" s="42">
-        <f t="shared" si="116"/>
+        <f>N10+N12+N14+N16+N18+N20+N22+N24+N26+N28+N30+N32+N34+N36+N38+N40+N42+N44+N46+N48+N50+N52</f>
         <v>0</v>
       </c>
       <c r="O68" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="P68" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="Q68" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
-      <c r="R68" s="43">
-        <f t="shared" si="116"/>
+      <c r="R68" s="42">
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
-      <c r="S68" s="43"/>
-      <c r="T68" s="42">
-        <f t="shared" si="116"/>
+      <c r="S68" s="43">
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
+      <c r="T68" s="43"/>
       <c r="U68" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="V68" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="W68" s="42">
-        <f t="shared" si="116"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
-      <c r="X68" s="108">
-        <f>X10+X12+X14+X16+X18+X20+X22+X24+X26+X28+X30+X32+X34+X36+X38+X40+X42+X44+X46+X48+X50+X52</f>
+      <c r="X68" s="42">
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
-      <c r="Y68" s="61" t="e">
-        <f>+T68/X68*26</f>
+      <c r="Y68" s="108">
+        <f>Y10+Y12+Y14+Y16+Y18+Y20+Y22+Y24+Y26+Y28+Y30+Y32+Y34+Y36+Y38+Y40+Y42+Y44+Y46+Y48+Y50+Y52</f>
+        <v>0</v>
+      </c>
+      <c r="Z68" s="61" t="e">
+        <f>+U68/Y68*26</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z68" s="61" t="e">
-        <f>+AD68/X68*26</f>
+      <c r="AA68" s="61" t="e">
+        <f>+AE68/Y68*26</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA68" s="97"/>
-      <c r="AB68" s="98"/>
-      <c r="AD68" s="42">
-        <f t="shared" ref="AD68" si="117">AD10+AD12+AD14+AD16+AD18+AD20+AD22+AD24+AD26+AD28+AD30+AD32+AD34+AD36+AD38+AD40+AD42+AD44+AD46+AD48+AD50+AD52</f>
+      <c r="AB68" s="97"/>
+      <c r="AC68" s="98"/>
+      <c r="AE68" s="42">
+        <f t="shared" ref="AE68" si="83">AE10+AE12+AE14+AE16+AE18+AE20+AE22+AE24+AE26+AE28+AE30+AE32+AE34+AE36+AE38+AE40+AE42+AE44+AE46+AE48+AE50+AE52</f>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:30 11518:16381" ht="17.25" hidden="1">
+    <row r="69" spans="1:31 11519:16382" ht="17.25" hidden="1">
       <c r="D69" s="45">
-        <f t="shared" ref="D69:X70" si="118">D9+D11+D13+D15+D17+D19+D21+D23+D25+D27+D29+D31+D33+D35+D37+D3</f>
+        <f t="shared" ref="D69:Y70" si="84">D9+D11+D13+D15+D17+D19+D21+D23+D25+D27+D29+D31+D33+D35+D37+D3</f>
         <v>0</v>
       </c>
       <c r="E69" s="45">
-        <f t="shared" si="118"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="G69" s="45">
-        <f t="shared" si="118"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="H69" s="45">
@@ -47284,11 +47371,11 @@
         <v>0</v>
       </c>
       <c r="I69" s="45">
-        <f t="shared" si="118"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="J69" s="45">
-        <f t="shared" si="118"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="K69" s="45">
@@ -47299,65 +47386,65 @@
         <f>L9+L11+L13+L15+L17+L19+L21+L23+L25+L27+L29+L31+L33+L35+L37+L3</f>
         <v>0</v>
       </c>
-      <c r="M69" s="45">
-        <f t="shared" si="118"/>
+      <c r="N69" s="45">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="N69" s="45" t="e">
-        <f t="shared" si="118"/>
+      <c r="O69" s="45" t="e">
+        <f t="shared" si="84"/>
         <v>#VALUE!</v>
       </c>
-      <c r="O69" s="45">
-        <f t="shared" si="118"/>
+      <c r="P69" s="45">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="P69" s="50">
-        <f t="shared" si="118"/>
+      <c r="Q69" s="50">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="Q69" s="45">
-        <f t="shared" si="118"/>
+      <c r="R69" s="45">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="R69" s="54">
-        <f t="shared" si="118"/>
+      <c r="S69" s="54">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="T69" s="54">
-        <f t="shared" si="118"/>
+      <c r="U69" s="54">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="U69" s="54">
-        <f t="shared" si="118"/>
+      <c r="V69" s="54">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="V69" s="54">
-        <f t="shared" si="118"/>
+      <c r="W69" s="54">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="W69" s="54">
-        <f t="shared" si="118"/>
+      <c r="X69" s="54">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="X69" s="57">
-        <f t="shared" si="118"/>
+      <c r="Y69" s="57">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="Y69" s="62"/>
-      <c r="Z69" s="61"/>
-      <c r="AA69" s="97"/>
+      <c r="Z69" s="62"/>
+      <c r="AA69" s="61"/>
+      <c r="AB69" s="97"/>
     </row>
-    <row r="70" spans="1:30 11518:16381" ht="17.25" hidden="1">
+    <row r="70" spans="1:31 11519:16382" ht="17.25" hidden="1">
       <c r="D70" s="45">
-        <f t="shared" si="118"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="E70" s="45">
-        <f t="shared" si="118"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="G70" s="45">
-        <f t="shared" si="118"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="H70" s="45">
@@ -47365,11 +47452,11 @@
         <v>0</v>
       </c>
       <c r="I70" s="45">
-        <f t="shared" si="118"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="J70" s="45">
-        <f t="shared" si="118"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="K70" s="45">
@@ -47380,87 +47467,86 @@
         <f>L10+L12+L14+L16+L18+L20+L22+L24+L26+L28+L30+L32+L34+L36+L38+L4</f>
         <v>0</v>
       </c>
-      <c r="M70" s="45">
-        <f t="shared" si="118"/>
+      <c r="N70" s="45">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="N70" s="45">
-        <f t="shared" si="118"/>
+      <c r="O70" s="45">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="O70" s="45">
-        <f t="shared" si="118"/>
+      <c r="P70" s="45">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="P70" s="50">
-        <f t="shared" si="118"/>
+      <c r="Q70" s="50">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="Q70" s="45">
-        <f t="shared" si="118"/>
+      <c r="R70" s="45">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="R70" s="54">
-        <f t="shared" si="118"/>
+      <c r="S70" s="54">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="T70" s="54">
-        <f t="shared" si="118"/>
+      <c r="U70" s="54">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="U70" s="54">
-        <f t="shared" si="118"/>
+      <c r="V70" s="54">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="V70" s="54">
-        <f t="shared" si="118"/>
+      <c r="W70" s="54">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="W70" s="54">
-        <f t="shared" si="118"/>
+      <c r="X70" s="54">
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="X70" s="57">
-        <f>X10+X12+X14+X16+X18+X20+X22+X24+X26+X28+X30+X32+X34+X36+X38+X40+X42+X44+X46+X48+X50+X52+X54+X56+X58+X60+X62</f>
+      <c r="Y70" s="57">
+        <f>Y10+Y12+Y14+Y16+Y18+Y20+Y22+Y24+Y26+Y28+Y30+Y32+Y34+Y36+Y38+Y40+Y42+Y44+Y46+Y48+Y50+Y52+Y54+Y56+Y58+Y60+Y62</f>
         <v>0</v>
       </c>
-      <c r="Y70" s="62"/>
-      <c r="Z70" s="61"/>
-      <c r="AA70" s="97"/>
+      <c r="Z70" s="62"/>
+      <c r="AA70" s="61"/>
+      <c r="AB70" s="97"/>
     </row>
-    <row r="71" spans="1:30 11518:16381" ht="17.25">
-      <c r="Y71" s="61" t="e">
-        <f>+Y68/26</f>
-        <v>#DIV/0!</v>
-      </c>
+    <row r="71" spans="1:31 11519:16382" ht="17.25">
       <c r="Z71" s="61" t="e">
         <f>+Z68/26</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA71" s="97"/>
+      <c r="AA71" s="61" t="e">
+        <f>+AA68/26</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB71" s="97"/>
     </row>
-    <row r="72" spans="1:30 11518:16381" hidden="1"/>
-    <row r="73" spans="1:30 11518:16381" hidden="1"/>
-    <row r="74" spans="1:30 11518:16381" s="89" customFormat="1" ht="15.75">
-      <c r="D74" s="148" t="s">
+    <row r="72" spans="1:31 11519:16382" hidden="1"/>
+    <row r="73" spans="1:31 11519:16382" hidden="1"/>
+    <row r="74" spans="1:31 11519:16382" s="89" customFormat="1" ht="15.75">
+      <c r="D74" s="157" t="s">
         <v>36</v>
       </c>
-      <c r="E74" s="148"/>
-      <c r="F74" s="148"/>
-      <c r="G74" s="148"/>
+      <c r="E74" s="157"/>
+      <c r="F74" s="157"/>
+      <c r="G74" s="157"/>
       <c r="K74" s="90" t="e" cm="1">
-        <f t="array" aca="1" ref="K74" ca="1">+_xll.VND(W68)</f>
+        <f t="array" aca="1" ref="K74" ca="1">+_xll.VND(X68)</f>
         <v>#NAME?</v>
       </c>
-      <c r="P74" s="91"/>
-      <c r="R74" s="117"/>
+      <c r="Q74" s="91"/>
       <c r="S74" s="117"/>
       <c r="T74" s="117"/>
       <c r="U74" s="117"/>
       <c r="V74" s="117"/>
       <c r="W74" s="117"/>
-      <c r="X74" s="92"/>
-      <c r="PZZ74"/>
+      <c r="X74" s="117"/>
+      <c r="Y74" s="92"/>
       <c r="QAA74"/>
       <c r="QAB74"/>
       <c r="QAC74"/>
@@ -52324,23 +52410,24 @@
       <c r="XEY74"/>
       <c r="XEZ74"/>
       <c r="XFA74"/>
+      <c r="XFB74"/>
     </row>
-    <row r="75" spans="1:30 11518:16381" ht="17.25" customHeight="1">
-      <c r="R75" s="142" t="s">
+    <row r="75" spans="1:31 11519:16382" ht="17.25" customHeight="1">
+      <c r="S75" s="167" t="s">
         <v>63</v>
       </c>
-      <c r="S75" s="142"/>
-      <c r="T75" s="142"/>
-      <c r="U75" s="142"/>
-      <c r="V75" s="142"/>
-      <c r="W75" s="142"/>
+      <c r="T75" s="167"/>
+      <c r="U75" s="167"/>
+      <c r="V75" s="167"/>
+      <c r="W75" s="167"/>
+      <c r="X75" s="167"/>
     </row>
-    <row r="76" spans="1:30 11518:16381" ht="14.45" customHeight="1">
+    <row r="76" spans="1:31 11519:16382" ht="14.45" customHeight="1">
       <c r="A76" s="63"/>
-      <c r="B76" s="144" t="s">
+      <c r="B76" s="169" t="s">
         <v>32</v>
       </c>
-      <c r="C76" s="144"/>
+      <c r="C76" s="169"/>
       <c r="D76" s="62"/>
       <c r="E76" s="62"/>
       <c r="F76" s="62"/>
@@ -52350,214 +52437,215 @@
       <c r="J76" s="62"/>
       <c r="K76" s="62"/>
       <c r="L76" s="62"/>
-      <c r="M76" s="46"/>
+      <c r="M76" s="62"/>
       <c r="N76" s="46"/>
-      <c r="O76" s="65"/>
-      <c r="P76" s="66"/>
-      <c r="Q76" s="62"/>
-      <c r="R76" s="48"/>
+      <c r="O76" s="46"/>
+      <c r="P76" s="65"/>
+      <c r="Q76" s="66"/>
+      <c r="R76" s="62"/>
       <c r="S76" s="48"/>
-      <c r="T76" s="141" t="s">
+      <c r="T76" s="48"/>
+      <c r="U76" s="166" t="s">
         <v>43</v>
       </c>
-      <c r="U76" s="141"/>
-      <c r="V76" s="141"/>
-      <c r="W76" s="141"/>
-      <c r="X76" s="64"/>
+      <c r="V76" s="166"/>
+      <c r="W76" s="166"/>
+      <c r="X76" s="166"/>
+      <c r="Y76" s="64"/>
     </row>
-    <row r="77" spans="1:30 11518:16381">
+    <row r="77" spans="1:31 11519:16382">
       <c r="A77" s="56"/>
       <c r="B77" s="101"/>
       <c r="C77" s="101"/>
-      <c r="T77" s="100"/>
       <c r="U77" s="100"/>
       <c r="V77" s="100"/>
       <c r="W77" s="100"/>
+      <c r="X77" s="100"/>
     </row>
-    <row r="78" spans="1:30 11518:16381">
+    <row r="78" spans="1:31 11519:16382">
       <c r="A78" s="56"/>
       <c r="B78" s="101"/>
       <c r="C78" s="101"/>
-      <c r="T78" s="100"/>
       <c r="U78" s="100"/>
       <c r="V78" s="100"/>
       <c r="W78" s="100"/>
+      <c r="X78" s="100"/>
     </row>
-    <row r="79" spans="1:30 11518:16381">
+    <row r="79" spans="1:31 11519:16382">
       <c r="A79" s="56"/>
       <c r="B79" s="101"/>
       <c r="C79" s="101"/>
       <c r="E79" s="67"/>
       <c r="F79" s="67"/>
-      <c r="T79" s="100"/>
       <c r="U79" s="100"/>
       <c r="V79" s="100"/>
       <c r="W79" s="100"/>
+      <c r="X79" s="100"/>
     </row>
-    <row r="80" spans="1:30 11518:16381">
-      <c r="B80" s="136" t="s">
+    <row r="80" spans="1:31 11519:16382">
+      <c r="B80" s="164" t="s">
         <v>41</v>
       </c>
-      <c r="C80" s="136"/>
-      <c r="T80" s="143" t="s">
+      <c r="C80" s="164"/>
+      <c r="U80" s="168" t="s">
         <v>44</v>
       </c>
-      <c r="U80" s="143"/>
-      <c r="V80" s="143"/>
-      <c r="W80" s="143"/>
+      <c r="V80" s="168"/>
+      <c r="W80" s="168"/>
+      <c r="X80" s="168"/>
     </row>
-    <row r="82" spans="18:23" ht="14.45" customHeight="1"/>
-    <row r="84" spans="18:23">
-      <c r="R84" s="68"/>
+    <row r="82" spans="19:24" ht="14.45" customHeight="1"/>
+    <row r="84" spans="19:24">
       <c r="S84" s="68"/>
       <c r="T84" s="68"/>
       <c r="U84" s="68"/>
       <c r="V84" s="68"/>
       <c r="W84" s="68"/>
+      <c r="X84" s="68"/>
     </row>
-    <row r="85" spans="18:23">
-      <c r="R85" s="68"/>
+    <row r="85" spans="19:24">
       <c r="S85" s="68"/>
       <c r="T85" s="68"/>
       <c r="U85" s="68"/>
       <c r="V85" s="68"/>
       <c r="W85" s="68"/>
+      <c r="X85" s="68"/>
     </row>
-    <row r="86" spans="18:23">
-      <c r="R86" s="68"/>
+    <row r="86" spans="19:24">
       <c r="S86" s="68"/>
       <c r="T86" s="68"/>
       <c r="U86" s="68"/>
       <c r="V86" s="68"/>
       <c r="W86" s="68"/>
+      <c r="X86" s="68"/>
     </row>
-    <row r="87" spans="18:23">
-      <c r="R87" s="68"/>
+    <row r="87" spans="19:24">
       <c r="S87" s="68"/>
       <c r="T87" s="68"/>
       <c r="U87" s="68"/>
       <c r="V87" s="68"/>
       <c r="W87" s="68"/>
+      <c r="X87" s="68"/>
     </row>
-    <row r="88" spans="18:23">
-      <c r="R88" s="68"/>
+    <row r="88" spans="19:24">
       <c r="S88" s="68"/>
       <c r="T88" s="68"/>
       <c r="U88" s="68"/>
       <c r="V88" s="68"/>
       <c r="W88" s="68"/>
+      <c r="X88" s="68"/>
     </row>
-    <row r="89" spans="18:23">
-      <c r="R89" s="68"/>
+    <row r="89" spans="19:24">
       <c r="S89" s="68"/>
       <c r="T89" s="68"/>
       <c r="U89" s="68"/>
       <c r="V89" s="68"/>
       <c r="W89" s="68"/>
+      <c r="X89" s="68"/>
     </row>
-    <row r="90" spans="18:23">
-      <c r="R90" s="68"/>
+    <row r="90" spans="19:24">
       <c r="S90" s="68"/>
       <c r="T90" s="68"/>
       <c r="U90" s="68"/>
       <c r="V90" s="68"/>
       <c r="W90" s="68"/>
+      <c r="X90" s="68"/>
     </row>
-    <row r="91" spans="18:23">
-      <c r="R91" s="68"/>
+    <row r="91" spans="19:24">
       <c r="S91" s="68"/>
       <c r="T91" s="68"/>
       <c r="U91" s="68"/>
       <c r="V91" s="68"/>
       <c r="W91" s="68"/>
+      <c r="X91" s="68"/>
     </row>
-    <row r="92" spans="18:23">
-      <c r="R92" s="68"/>
+    <row r="92" spans="19:24">
       <c r="S92" s="68"/>
       <c r="T92" s="68"/>
       <c r="U92" s="68"/>
       <c r="V92" s="68"/>
       <c r="W92" s="68"/>
+      <c r="X92" s="68"/>
     </row>
-    <row r="93" spans="18:23">
-      <c r="R93" s="68"/>
+    <row r="93" spans="19:24">
       <c r="S93" s="68"/>
       <c r="T93" s="68"/>
       <c r="U93" s="68"/>
       <c r="V93" s="68"/>
       <c r="W93" s="68"/>
+      <c r="X93" s="68"/>
     </row>
-    <row r="94" spans="18:23">
-      <c r="R94" s="68"/>
+    <row r="94" spans="19:24">
       <c r="S94" s="68"/>
       <c r="T94" s="68"/>
       <c r="U94" s="68"/>
       <c r="V94" s="68"/>
       <c r="W94" s="68"/>
+      <c r="X94" s="68"/>
     </row>
-    <row r="95" spans="18:23">
-      <c r="R95" s="68"/>
+    <row r="95" spans="19:24">
       <c r="S95" s="68"/>
       <c r="T95" s="68"/>
       <c r="U95" s="68"/>
       <c r="V95" s="68"/>
       <c r="W95" s="68"/>
+      <c r="X95" s="68"/>
     </row>
-    <row r="96" spans="18:23">
-      <c r="R96" s="68"/>
+    <row r="96" spans="19:24">
       <c r="S96" s="68"/>
       <c r="T96" s="68"/>
       <c r="U96" s="68"/>
       <c r="V96" s="68"/>
       <c r="W96" s="68"/>
+      <c r="X96" s="68"/>
     </row>
-    <row r="97" spans="18:23">
-      <c r="R97" s="68"/>
+    <row r="97" spans="19:24">
       <c r="S97" s="68"/>
       <c r="T97" s="68"/>
       <c r="U97" s="68"/>
       <c r="V97" s="68"/>
       <c r="W97" s="68"/>
+      <c r="X97" s="68"/>
     </row>
-    <row r="98" spans="18:23">
-      <c r="R98" s="68"/>
+    <row r="98" spans="19:24">
       <c r="S98" s="68"/>
       <c r="T98" s="68"/>
       <c r="U98" s="68"/>
       <c r="V98" s="68"/>
       <c r="W98" s="68"/>
+      <c r="X98" s="68"/>
     </row>
-    <row r="99" spans="18:23">
-      <c r="R99" s="68"/>
+    <row r="99" spans="19:24">
       <c r="S99" s="68"/>
       <c r="T99" s="68"/>
       <c r="U99" s="68"/>
       <c r="V99" s="68"/>
       <c r="W99" s="68"/>
+      <c r="X99" s="68"/>
     </row>
-    <row r="100" spans="18:23">
-      <c r="R100" s="68"/>
+    <row r="100" spans="19:24">
       <c r="S100" s="68"/>
       <c r="T100" s="68"/>
       <c r="U100" s="68"/>
       <c r="V100" s="68"/>
       <c r="W100" s="68"/>
+      <c r="X100" s="68"/>
     </row>
-    <row r="101" spans="18:23">
-      <c r="R101" s="68"/>
+    <row r="101" spans="19:24">
       <c r="S101" s="68"/>
       <c r="T101" s="68"/>
       <c r="U101" s="68"/>
       <c r="V101" s="68"/>
       <c r="W101" s="68"/>
+      <c r="X101" s="68"/>
     </row>
-    <row r="102" spans="18:23">
-      <c r="R102" s="68"/>
+    <row r="102" spans="19:24">
       <c r="S102" s="68"/>
       <c r="T102" s="68"/>
       <c r="U102" s="68"/>
       <c r="V102" s="68"/>
       <c r="W102" s="68"/>
+      <c r="X102" s="68"/>
     </row>
     <row r="121" spans="2:2">
       <c r="B121" s="45" t="s">
@@ -52576,144 +52664,34 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="187">
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:E7"/>
+  <mergeCells count="188">
+    <mergeCell ref="B80:C80"/>
     <mergeCell ref="Y5:Y7"/>
-    <mergeCell ref="Z5:Z7"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="U76:X76"/>
+    <mergeCell ref="S75:X75"/>
+    <mergeCell ref="U80:X80"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="AE5:AE7"/>
+    <mergeCell ref="D74:G74"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="V6:V7"/>
-    <mergeCell ref="T5:T7"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:W7"/>
-    <mergeCell ref="M5:S5"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:C34"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="C59:C60"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="AB5:AB7"/>
+    <mergeCell ref="AC5:AC7"/>
+    <mergeCell ref="AD5:AD7"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="B67:B68"/>
     <mergeCell ref="C67:C68"/>
@@ -52738,37 +52716,148 @@
     <mergeCell ref="D63:E63"/>
     <mergeCell ref="D64:E64"/>
     <mergeCell ref="A65:A66"/>
-    <mergeCell ref="AD5:AD7"/>
-    <mergeCell ref="D74:G74"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:E7"/>
+    <mergeCell ref="Z5:Z7"/>
     <mergeCell ref="AA5:AA7"/>
-    <mergeCell ref="AB5:AB7"/>
-    <mergeCell ref="AC5:AC7"/>
-    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="V6:V7"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="U5:U7"/>
+    <mergeCell ref="V5:W5"/>
     <mergeCell ref="X5:X7"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="T76:W76"/>
-    <mergeCell ref="R75:W75"/>
-    <mergeCell ref="T80:W80"/>
-    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="N5:T5"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="F5:F7"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
-    <brk id="24" max="1048575" man="1"/>
+    <brk id="25" max="1048575" man="1"/>
   </colBreaks>
 </worksheet>
 </file>